--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F86C74-0976-402F-9CFD-ED91783869A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F3F5C0-3490-43C3-8877-8A4444AB859E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="339">
   <si>
     <t>nlay</t>
   </si>
@@ -1012,9 +1012,6 @@
     <t>14k - 11k BP</t>
   </si>
   <si>
-    <t>11kBP - present - 39kAP</t>
-  </si>
-  <si>
     <t>Transient recharge step change experiment</t>
   </si>
   <si>
@@ -1034,13 +1031,43 @@
   </si>
   <si>
     <t>One thousand years</t>
+  </si>
+  <si>
+    <t>UncAq</t>
+  </si>
+  <si>
+    <t>Aqt 1</t>
+  </si>
+  <si>
+    <t>Caq 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqt 2 </t>
+  </si>
+  <si>
+    <t>Caq 2</t>
+  </si>
+  <si>
+    <t>Caq 1 outcrop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEAD </t>
+  </si>
+  <si>
+    <t>WELL_07</t>
+  </si>
+  <si>
+    <t>WELL_08</t>
+  </si>
+  <si>
+    <t>WELL_09</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1057,13 +1084,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1154,11 +1174,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1504,19 +1524,19 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>4500</v>
       </c>
       <c r="C2">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>450000</v>
       </c>
       <c r="E2">
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G2">
         <v>1000</v>
@@ -2959,7 +2979,7 @@
         <v>36000</v>
       </c>
       <c r="K18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R18" t="s">
         <v>123</v>
@@ -3081,20 +3101,23 @@
       <c r="I20">
         <v>36000</v>
       </c>
-      <c r="K20" t="s">
-        <v>24</v>
-      </c>
-      <c r="L20" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" t="s">
-        <v>26</v>
-      </c>
-      <c r="N20" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" t="s">
-        <v>28</v>
+      <c r="K20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="U20">
         <v>1968</v>
@@ -3150,20 +3173,23 @@
       <c r="I21">
         <v>36000</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="6">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21" t="s">
-        <v>29</v>
+      <c r="L21" s="1">
+        <v>3.0000000000000003E-4</v>
+      </c>
+      <c r="M21" s="1">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="N21" s="1">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="O21" s="1">
+        <v>3.0000000000000001E-6</v>
+      </c>
+      <c r="P21" s="1">
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="U21">
         <v>1969</v>
@@ -3219,20 +3245,23 @@
       <c r="I22">
         <v>36000</v>
       </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <v>2520000</v>
-      </c>
-      <c r="M22">
-        <v>10</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22" t="s">
-        <v>320</v>
+      <c r="K22" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1.5E-5</v>
+      </c>
+      <c r="M22" s="1">
+        <v>1.4999999999999999E-7</v>
+      </c>
+      <c r="N22" s="1">
+        <v>1.4999999999999999E-5</v>
+      </c>
+      <c r="O22" s="1">
+        <v>1.4999999999999999E-7</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1.4999999999999999E-5</v>
       </c>
       <c r="U22">
         <v>1970</v>
@@ -3288,20 +3317,23 @@
       <c r="I23">
         <v>36000</v>
       </c>
-      <c r="K23">
-        <v>2</v>
-      </c>
-      <c r="L23">
-        <v>1080000</v>
-      </c>
-      <c r="M23">
-        <v>20</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23" t="s">
-        <v>321</v>
+      <c r="K23" s="6">
+        <v>400000000</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1.4999999999999999E-5</v>
+      </c>
+      <c r="M23" s="1">
+        <v>1.4999999999999999E-7</v>
+      </c>
+      <c r="N23" s="1">
+        <v>1.4999999999999999E-5</v>
+      </c>
+      <c r="O23" s="1">
+        <v>1.4999999999999999E-7</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1.4999999999999999E-5</v>
       </c>
       <c r="U23">
         <v>1971</v>
@@ -3357,21 +3389,6 @@
       <c r="I24">
         <v>36000</v>
       </c>
-      <c r="K24">
-        <v>3</v>
-      </c>
-      <c r="L24">
-        <v>18000000</v>
-      </c>
-      <c r="M24">
-        <v>1000</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24" t="s">
-        <v>322</v>
-      </c>
       <c r="U24">
         <v>1972</v>
       </c>
@@ -3426,6 +3443,21 @@
       <c r="I25">
         <v>36000</v>
       </c>
+      <c r="K25" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" t="s">
+        <v>28</v>
+      </c>
       <c r="U25">
         <v>1973</v>
       </c>
@@ -3480,23 +3512,20 @@
       <c r="I26">
         <v>36000</v>
       </c>
-      <c r="K26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L26" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" t="s">
-        <v>33</v>
-      </c>
-      <c r="N26" t="s">
-        <v>34</v>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
       </c>
       <c r="O26" t="s">
-        <v>35</v>
-      </c>
-      <c r="P26" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="U26">
         <v>1974</v>
@@ -3553,22 +3582,19 @@
         <v>36000</v>
       </c>
       <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="M27" s="1">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="N27" s="1">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="O27" s="1">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="P27" s="1">
-        <v>1.1999999999999999E-3</v>
+        <v>1</v>
+      </c>
+      <c r="L27">
+        <v>2520000</v>
+      </c>
+      <c r="M27">
+        <v>100</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="s">
+        <v>320</v>
       </c>
       <c r="U27">
         <v>1975</v>
@@ -3625,22 +3651,19 @@
         <v>36000</v>
       </c>
       <c r="K28">
-        <v>2520000</v>
-      </c>
-      <c r="L28" s="1">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="M28" s="1">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="N28" s="1">
-        <v>1.1999999999999999E-3</v>
-      </c>
-      <c r="O28" s="1">
-        <v>1.9999999999999999E-6</v>
-      </c>
-      <c r="P28" s="1">
-        <v>1.1999999999999999E-3</v>
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>1080000</v>
+      </c>
+      <c r="M28">
+        <v>200</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" t="s">
+        <v>321</v>
       </c>
       <c r="U28">
         <v>1976</v>
@@ -3697,22 +3720,19 @@
         <v>36000</v>
       </c>
       <c r="K29">
-        <v>3600000</v>
-      </c>
-      <c r="L29" s="1">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="M29" s="1">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="N29" s="1">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="O29" s="1">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="P29" s="1">
-        <v>2.9999999999999997E-4</v>
+        <v>3</v>
+      </c>
+      <c r="L29">
+        <v>180000</v>
+      </c>
+      <c r="M29">
+        <v>500</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29" t="s">
+        <v>323</v>
       </c>
       <c r="U29">
         <v>1977</v>
@@ -3769,22 +3789,19 @@
         <v>36000</v>
       </c>
       <c r="K30">
-        <v>30000000</v>
-      </c>
-      <c r="L30" s="6">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="M30" s="6">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="N30" s="6">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="O30" s="6">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="P30" s="6">
-        <v>2.9999999999999997E-4</v>
+        <v>4</v>
+      </c>
+      <c r="L30">
+        <v>17820000</v>
+      </c>
+      <c r="M30">
+        <v>495</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>324</v>
       </c>
       <c r="U30">
         <v>1978</v>
@@ -3840,6 +3857,21 @@
       <c r="I31">
         <v>36000</v>
       </c>
+      <c r="K31">
+        <v>5</v>
+      </c>
+      <c r="L31">
+        <v>360000000</v>
+      </c>
+      <c r="M31">
+        <v>100</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31" t="s">
+        <v>328</v>
+      </c>
       <c r="U31">
         <v>1979</v>
       </c>
@@ -3894,12 +3926,6 @@
       <c r="I32">
         <v>36000</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L32" s="6">
-        <v>2.9999999999999997E-4</v>
-      </c>
       <c r="U32">
         <v>1980</v>
       </c>
@@ -3954,12 +3980,6 @@
       <c r="I33">
         <v>36000</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L33" s="6">
-        <v>4.9999999999999998E-7</v>
-      </c>
       <c r="U33">
         <v>1981</v>
       </c>
@@ -4014,12 +4034,6 @@
       <c r="I34">
         <v>36000</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L34" s="6">
-        <v>2.9999999999999997E-4</v>
-      </c>
       <c r="U34">
         <v>1982</v>
       </c>
@@ -4074,12 +4088,6 @@
       <c r="I35">
         <v>36000</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L35" s="6">
-        <v>4.9999999999999998E-7</v>
-      </c>
       <c r="U35">
         <v>1983</v>
       </c>
@@ -4133,12 +4141,6 @@
       </c>
       <c r="I36">
         <v>36000</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="L36" s="6">
-        <v>2.9999999999999997E-4</v>
       </c>
       <c r="U36">
         <v>1984</v>
@@ -16662,7 +16664,7 @@
         <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
@@ -16684,8 +16686,8 @@
       <c r="F2">
         <v>300</v>
       </c>
-      <c r="G2">
-        <v>300</v>
+      <c r="G2" s="8">
+        <v>225</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -16710,8 +16712,8 @@
       <c r="F3">
         <v>150</v>
       </c>
-      <c r="G3">
-        <v>250</v>
+      <c r="G3" s="8">
+        <v>187.5</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -16736,8 +16738,8 @@
       <c r="F4">
         <v>200</v>
       </c>
-      <c r="G4">
-        <v>150</v>
+      <c r="G4" s="8">
+        <v>112.5</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -16762,8 +16764,8 @@
       <c r="F5">
         <v>150</v>
       </c>
-      <c r="G5">
-        <v>100</v>
+      <c r="G5" s="8">
+        <v>75</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -16788,7 +16790,7 @@
       <c r="F6">
         <v>200</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="8">
         <v>0</v>
       </c>
       <c r="H6">
@@ -16850,7 +16852,7 @@
         <v>2520000</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -16867,7 +16869,7 @@
         <v>1080000</v>
       </c>
       <c r="C4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -16890,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -16907,24 +16909,7 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>360000000</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -18008,114 +17993,119 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G363"/>
+  <dimension ref="A1:L363"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="7">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>3.0000000000000003E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C2" s="1">
-        <v>3.0000000000000001E-6</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="D2" s="1">
-        <v>2.9999999999999997E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>3.0000000000000001E-6</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="F2" s="1">
-        <v>2.9999999999999997E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
         <v>3600000</v>
       </c>
       <c r="B3" s="1">
-        <v>1.5E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="C3" s="1">
-        <v>1.4999999999999999E-7</v>
+        <v>5.5555555555555558E-6</v>
       </c>
       <c r="D3" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="E3" s="1">
-        <v>1.4999999999999999E-7</v>
+        <v>5.5555555555555558E-6</v>
       </c>
       <c r="F3" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
         <v>400000000</v>
       </c>
       <c r="B4" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="C4" s="1">
-        <v>1.4999999999999999E-7</v>
+        <v>5.5555555555555558E-6</v>
       </c>
       <c r="D4" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="E4" s="1">
-        <v>1.4999999999999999E-7</v>
+        <v>5.5555555555555558E-6</v>
       </c>
       <c r="F4" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B7" s="1"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -18123,7 +18113,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -18131,7 +18121,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -18139,7 +18129,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -18147,7 +18137,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -18155,7 +18145,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -18163,7 +18153,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -18171,7 +18161,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -18179,7 +18169,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -21376,7 +21366,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="C22">
         <v>3.1154231364886891E-4</v>
@@ -21402,7 +21392,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="1">
-        <v>1.4999999999999999E-7</v>
+        <v>5.5555555555555558E-6</v>
       </c>
       <c r="C23">
         <v>3.1154231364886891E-5</v>
@@ -21428,7 +21418,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="C24">
         <v>3.1154231364886891E-4</v>
@@ -21454,7 +21444,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1">
-        <v>1.4999999999999999E-7</v>
+        <v>5.5555555555555558E-6</v>
       </c>
       <c r="C25">
         <v>3.1154231364886891E-5</v>
@@ -21480,7 +21470,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="1">
-        <v>1.4999999999999999E-5</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="C26">
         <v>3.1154231364886891E-4</v>
@@ -21632,8 +21622,8 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A32" s="8" t="s">
-        <v>327</v>
+      <c r="A32" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
@@ -21654,18 +21644,18 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -21689,37 +21679,105 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>329</v>
       </c>
       <c r="B2" t="s">
         <v>83</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E2">
-        <v>597</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>4</v>
+      <c r="A3" t="s">
+        <v>330</v>
       </c>
       <c r="B3" t="s">
         <v>83</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E3">
-        <v>596</v>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>225</v>
+      </c>
+      <c r="E4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>225</v>
+      </c>
+      <c r="E5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>225</v>
+      </c>
+      <c r="E6">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>225</v>
+      </c>
+      <c r="E7">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -21729,7 +21787,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.73046875" bestFit="1" customWidth="1"/>
@@ -21766,10 +21824,10 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E2">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -21779,17 +21837,17 @@
       <c r="A3" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>3600000</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E3">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -21806,10 +21864,10 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E4">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -21826,10 +21884,10 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E5">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -21839,17 +21897,17 @@
       <c r="A6" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>3600000</v>
       </c>
       <c r="C6">
         <v>12</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E6">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -21866,10 +21924,10 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E7">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -21886,10 +21944,10 @@
         <v>12</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E8">
-        <v>401</v>
+        <v>301</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -21899,17 +21957,17 @@
       <c r="A9" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>3600000</v>
       </c>
       <c r="C9">
         <v>12</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E9">
-        <v>401</v>
+        <v>301</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -21926,10 +21984,10 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="E10">
-        <v>401</v>
+        <v>301</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -21946,10 +22004,10 @@
         <v>12</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E11">
-        <v>402</v>
+        <v>299</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -21959,17 +22017,17 @@
       <c r="A12" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>3600000</v>
       </c>
       <c r="C12">
         <v>12</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E12">
-        <v>402</v>
+        <v>299</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -21986,10 +22044,10 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E13">
-        <v>402</v>
+        <v>299</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -22006,10 +22064,10 @@
         <v>12</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E14">
-        <v>398</v>
+        <v>300</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -22019,17 +22077,17 @@
       <c r="A15" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>3600000</v>
       </c>
       <c r="C15">
         <v>12</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="E15">
-        <v>398</v>
+        <v>300</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -22046,12 +22104,252 @@
         <v>12</v>
       </c>
       <c r="D16">
+        <v>225</v>
+      </c>
+      <c r="E16">
+        <v>300</v>
+      </c>
+      <c r="F16">
         <v>0</v>
       </c>
-      <c r="E16">
-        <v>398</v>
-      </c>
-      <c r="F16">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>225</v>
+      </c>
+      <c r="E17">
+        <v>301</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>225</v>
+      </c>
+      <c r="E18">
+        <v>301</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19">
+        <v>400000000</v>
+      </c>
+      <c r="C19">
+        <v>12</v>
+      </c>
+      <c r="D19">
+        <v>225</v>
+      </c>
+      <c r="E19">
+        <v>301</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>12</v>
+      </c>
+      <c r="D20">
+        <v>226</v>
+      </c>
+      <c r="E20">
+        <v>299</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C21">
+        <v>12</v>
+      </c>
+      <c r="D21">
+        <v>226</v>
+      </c>
+      <c r="E21">
+        <v>299</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22">
+        <v>400000000</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+      <c r="D22">
+        <v>226</v>
+      </c>
+      <c r="E22">
+        <v>299</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>12</v>
+      </c>
+      <c r="D23">
+        <v>226</v>
+      </c>
+      <c r="E23">
+        <v>300</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C24">
+        <v>12</v>
+      </c>
+      <c r="D24">
+        <v>226</v>
+      </c>
+      <c r="E24">
+        <v>300</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25">
+        <v>400000000</v>
+      </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>226</v>
+      </c>
+      <c r="E25">
+        <v>300</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
+      <c r="D26">
+        <v>226</v>
+      </c>
+      <c r="E26">
+        <v>301</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>338</v>
+      </c>
+      <c r="B27" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C27">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>226</v>
+      </c>
+      <c r="E27">
+        <v>301</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B28">
+        <v>400000000</v>
+      </c>
+      <c r="C28">
+        <v>12</v>
+      </c>
+      <c r="D28">
+        <v>226</v>
+      </c>
+      <c r="E28">
+        <v>301</v>
+      </c>
+      <c r="F28">
         <v>0</v>
       </c>
     </row>
@@ -22062,7 +22360,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -22262,14 +22560,147 @@
         <v>-30</v>
       </c>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" ref="C7:C10" si="0">D7/2</f>
+        <v>-1</v>
+      </c>
+      <c r="D7">
+        <v>-2</v>
+      </c>
+      <c r="E7">
+        <v>-4</v>
+      </c>
+      <c r="F7">
+        <v>-6</v>
+      </c>
+      <c r="G7">
+        <v>-8</v>
+      </c>
+      <c r="H7">
+        <v>-10</v>
+      </c>
+      <c r="I7">
+        <v>-20</v>
+      </c>
+      <c r="J7">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>336</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="D8">
+        <v>-2</v>
+      </c>
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8">
+        <v>-6</v>
+      </c>
+      <c r="G8">
+        <v>-8</v>
+      </c>
+      <c r="H8">
+        <v>-10</v>
+      </c>
+      <c r="I8">
+        <v>-20</v>
+      </c>
+      <c r="J8">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="D9">
+        <v>-2</v>
+      </c>
+      <c r="E9">
+        <v>-4</v>
+      </c>
+      <c r="F9">
+        <v>-6</v>
+      </c>
+      <c r="G9">
+        <v>-8</v>
+      </c>
+      <c r="H9">
+        <v>-10</v>
+      </c>
+      <c r="I9">
+        <v>-20</v>
+      </c>
+      <c r="J9">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="D10">
+        <v>-2</v>
+      </c>
+      <c r="E10">
+        <v>-4</v>
+      </c>
+      <c r="F10">
+        <v>-6</v>
+      </c>
+      <c r="G10">
+        <v>-8</v>
+      </c>
+      <c r="H10">
+        <v>-10</v>
+      </c>
+      <c r="I10">
+        <v>-20</v>
+      </c>
+      <c r="J10">
+        <v>-30</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -22346,8 +22777,8 @@
       <c r="A3" t="s">
         <v>86</v>
       </c>
-      <c r="B3">
-        <v>7578000</v>
+      <c r="B3" s="6">
+        <v>3600000</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -22382,7 +22813,7 @@
         <v>86</v>
       </c>
       <c r="B4">
-        <v>30000000</v>
+        <v>400000000</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -22451,8 +22882,8 @@
       <c r="A6" t="s">
         <v>87</v>
       </c>
-      <c r="B6">
-        <v>7578000</v>
+      <c r="B6" s="6">
+        <v>3600000</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -22487,7 +22918,7 @@
         <v>87</v>
       </c>
       <c r="B7">
-        <v>30000000</v>
+        <v>400000000</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -22556,8 +22987,8 @@
       <c r="A9" t="s">
         <v>88</v>
       </c>
-      <c r="B9">
-        <v>7578000</v>
+      <c r="B9" s="6">
+        <v>3600000</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -22592,7 +23023,7 @@
         <v>88</v>
       </c>
       <c r="B10">
-        <v>30000000</v>
+        <v>400000000</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -22661,8 +23092,8 @@
       <c r="A12" t="s">
         <v>89</v>
       </c>
-      <c r="B12">
-        <v>7578000</v>
+      <c r="B12" s="6">
+        <v>3600000</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -22697,7 +23128,7 @@
         <v>89</v>
       </c>
       <c r="B13">
-        <v>30000000</v>
+        <v>400000000</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -22766,8 +23197,8 @@
       <c r="A15" t="s">
         <v>90</v>
       </c>
-      <c r="B15">
-        <v>7578000</v>
+      <c r="B15" s="6">
+        <v>3600000</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -22802,7 +23233,7 @@
         <v>90</v>
       </c>
       <c r="B16">
-        <v>30000000</v>
+        <v>400000000</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -22829,6 +23260,426 @@
         <v>-20</v>
       </c>
       <c r="K16">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>-1</v>
+      </c>
+      <c r="E18">
+        <v>-2</v>
+      </c>
+      <c r="F18">
+        <v>-4</v>
+      </c>
+      <c r="G18">
+        <v>-6</v>
+      </c>
+      <c r="H18">
+        <v>-8</v>
+      </c>
+      <c r="I18">
+        <v>-10</v>
+      </c>
+      <c r="J18">
+        <v>-20</v>
+      </c>
+      <c r="K18">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19">
+        <v>400000000</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>-1</v>
+      </c>
+      <c r="E19">
+        <v>-2</v>
+      </c>
+      <c r="F19">
+        <v>-4</v>
+      </c>
+      <c r="G19">
+        <v>-6</v>
+      </c>
+      <c r="H19">
+        <v>-8</v>
+      </c>
+      <c r="I19">
+        <v>-10</v>
+      </c>
+      <c r="J19">
+        <v>-20</v>
+      </c>
+      <c r="K19">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>336</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>-1</v>
+      </c>
+      <c r="E21">
+        <v>-2</v>
+      </c>
+      <c r="F21">
+        <v>-4</v>
+      </c>
+      <c r="G21">
+        <v>-6</v>
+      </c>
+      <c r="H21">
+        <v>-8</v>
+      </c>
+      <c r="I21">
+        <v>-10</v>
+      </c>
+      <c r="J21">
+        <v>-20</v>
+      </c>
+      <c r="K21">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>336</v>
+      </c>
+      <c r="B22">
+        <v>400000000</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>-1</v>
+      </c>
+      <c r="E22">
+        <v>-2</v>
+      </c>
+      <c r="F22">
+        <v>-4</v>
+      </c>
+      <c r="G22">
+        <v>-6</v>
+      </c>
+      <c r="H22">
+        <v>-8</v>
+      </c>
+      <c r="I22">
+        <v>-10</v>
+      </c>
+      <c r="J22">
+        <v>-20</v>
+      </c>
+      <c r="K22">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>337</v>
+      </c>
+      <c r="B24" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>-1</v>
+      </c>
+      <c r="E24">
+        <v>-2</v>
+      </c>
+      <c r="F24">
+        <v>-4</v>
+      </c>
+      <c r="G24">
+        <v>-6</v>
+      </c>
+      <c r="H24">
+        <v>-8</v>
+      </c>
+      <c r="I24">
+        <v>-10</v>
+      </c>
+      <c r="J24">
+        <v>-20</v>
+      </c>
+      <c r="K24">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>337</v>
+      </c>
+      <c r="B25">
+        <v>400000000</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>-1</v>
+      </c>
+      <c r="E25">
+        <v>-2</v>
+      </c>
+      <c r="F25">
+        <v>-4</v>
+      </c>
+      <c r="G25">
+        <v>-6</v>
+      </c>
+      <c r="H25">
+        <v>-8</v>
+      </c>
+      <c r="I25">
+        <v>-10</v>
+      </c>
+      <c r="J25">
+        <v>-20</v>
+      </c>
+      <c r="K25">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>338</v>
+      </c>
+      <c r="B27" s="6">
+        <v>3600000</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>-1</v>
+      </c>
+      <c r="E27">
+        <v>-2</v>
+      </c>
+      <c r="F27">
+        <v>-4</v>
+      </c>
+      <c r="G27">
+        <v>-6</v>
+      </c>
+      <c r="H27">
+        <v>-8</v>
+      </c>
+      <c r="I27">
+        <v>-10</v>
+      </c>
+      <c r="J27">
+        <v>-20</v>
+      </c>
+      <c r="K27">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>338</v>
+      </c>
+      <c r="B28">
+        <v>400000000</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>-1</v>
+      </c>
+      <c r="E28">
+        <v>-2</v>
+      </c>
+      <c r="F28">
+        <v>-4</v>
+      </c>
+      <c r="G28">
+        <v>-6</v>
+      </c>
+      <c r="H28">
+        <v>-8</v>
+      </c>
+      <c r="I28">
+        <v>-10</v>
+      </c>
+      <c r="J28">
+        <v>-20</v>
+      </c>
+      <c r="K28">
         <v>-30</v>
       </c>
     </row>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F3F5C0-3490-43C3-8877-8A4444AB859E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AE2BAB-31CC-4A5A-83D6-6F02B28D292E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="341">
   <si>
     <t>nlay</t>
   </si>
@@ -1061,6 +1061,12 @@
   </si>
   <si>
     <t>WELL_09</t>
+  </si>
+  <si>
+    <t>transition_cells</t>
+  </si>
+  <si>
+    <t>epsilon</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1530,7 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>4500</v>
+        <v>450</v>
       </c>
       <c r="C2">
         <v>450</v>
@@ -16629,7 +16635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="5.9296875" bestFit="1" customWidth="1"/>
@@ -16641,7 +16647,7 @@
     <col min="9" max="9" width="8.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -16666,8 +16672,14 @@
       <c r="H1" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -16690,10 +16702,16 @@
         <v>225</v>
       </c>
       <c r="H2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>52</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -16716,10 +16734,16 @@
         <v>187.5</v>
       </c>
       <c r="H3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>52</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -16742,10 +16766,16 @@
         <v>112.5</v>
       </c>
       <c r="H4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="I4">
+        <v>52</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -16768,10 +16798,16 @@
         <v>75</v>
       </c>
       <c r="H5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>3</v>
+      </c>
+      <c r="I5">
+        <v>52</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -16794,7 +16830,13 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>52</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21703,7 +21745,7 @@
         <v>83</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>225</v>
@@ -21720,7 +21762,7 @@
         <v>83</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>225</v>
@@ -21737,7 +21779,7 @@
         <v>83</v>
       </c>
       <c r="C5">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>225</v>
@@ -21754,7 +21796,7 @@
         <v>83</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>225</v>
@@ -21771,7 +21813,7 @@
         <v>335</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>225</v>
@@ -21821,7 +21863,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>224</v>
@@ -21841,7 +21883,7 @@
         <v>3600000</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>224</v>
@@ -21861,7 +21903,7 @@
         <v>400000000</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>224</v>
@@ -21881,7 +21923,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>224</v>
@@ -21901,7 +21943,7 @@
         <v>3600000</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>224</v>
@@ -21921,7 +21963,7 @@
         <v>400000000</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>224</v>
@@ -21941,7 +21983,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>224</v>
@@ -21961,7 +22003,7 @@
         <v>3600000</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>224</v>
@@ -21981,7 +22023,7 @@
         <v>400000000</v>
       </c>
       <c r="C10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>224</v>
@@ -22001,7 +22043,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>225</v>
@@ -22021,7 +22063,7 @@
         <v>3600000</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>225</v>
@@ -22041,7 +22083,7 @@
         <v>400000000</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>225</v>
@@ -22061,7 +22103,7 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>225</v>
@@ -22081,7 +22123,7 @@
         <v>3600000</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>225</v>
@@ -22101,7 +22143,7 @@
         <v>400000000</v>
       </c>
       <c r="C16">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>225</v>
@@ -22121,7 +22163,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>225</v>
@@ -22141,7 +22183,7 @@
         <v>3600000</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>225</v>
@@ -22161,7 +22203,7 @@
         <v>400000000</v>
       </c>
       <c r="C19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>225</v>
@@ -22181,7 +22223,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>226</v>
@@ -22201,7 +22243,7 @@
         <v>3600000</v>
       </c>
       <c r="C21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>226</v>
@@ -22221,7 +22263,7 @@
         <v>400000000</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>226</v>
@@ -22241,7 +22283,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>226</v>
@@ -22261,7 +22303,7 @@
         <v>3600000</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>226</v>
@@ -22281,7 +22323,7 @@
         <v>400000000</v>
       </c>
       <c r="C25">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>226</v>
@@ -22301,7 +22343,7 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>226</v>
@@ -22321,7 +22363,7 @@
         <v>3600000</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>226</v>
@@ -22341,7 +22383,7 @@
         <v>400000000</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>226</v>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AE2BAB-31CC-4A5A-83D6-6F02B28D292E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A7D49A-AAD6-45E3-A045-8B734DDF89A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -1500,9 +1500,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1525,15 +1525,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="D2">
         <v>450000</v>
@@ -1542,10 +1542,10 @@
         <v>450000</v>
       </c>
       <c r="F2">
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>4500</v>
       </c>
     </row>
   </sheetData>
@@ -1556,9 +1556,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>37</v>
       </c>
@@ -1575,7 +1575,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>48</v>
       </c>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1655,12 +1655,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:AK364"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.46484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>104</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>106</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>108</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>110</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>112</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>113</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>115</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>116</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>117</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>119</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>120</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>121</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>122</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>124</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>27000</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>125</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>126</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>5.5502136001665456E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>127</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>7.1790398823913721E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>128</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>6.247710440845614E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>129</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>7.1853251477000421E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>130</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>6.9554227893998163E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>5.7253061645059339E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>7.5562383814068183E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>4.7956646402789609E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>3.77861344903145E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>135</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>6.3076157488416986E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>136</v>
       </c>
@@ -3766,7 +3766,7 @@
         <v>5.3573866388844803E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>137</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>5.1650487503666432E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>138</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>6.206520086059846E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>7.195322821158302E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>140</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>2.9134882445236649E-4</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>141</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>5.0209969717145185E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>142</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>7.4802277554614563E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>143</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>5.6061012672548299E-4</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>144</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>8.2964178446747177E-4</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>145</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>5.5192525783438826E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>146</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>2.594301690595899E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>147</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>5.8758806918154829E-4</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>148</v>
       </c>
@@ -4444,7 +4444,7 @@
         <v>7.1827862361545337E-4</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>149</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>6.3964240766474305E-4</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>150</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>6.4218380286974329E-4</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>151</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>7.9556383137322937E-4</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>4.7143997174482332E-4</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>153</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>6.1579065355337435E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>154</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>6.1124317251300023E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>155</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>8.2762994075904659E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>156</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>6.7528242245754738E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -4930,7 +4930,7 @@
         <v>8.1609027804714629E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>3.4945422270553399E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>159</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>5.5916517295822666E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>160</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>7.3867228076687178E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -5146,7 +5146,7 @@
         <v>7.4209417307762092E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>4.6396100700759078E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>163</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>4.5068228800443209E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>164</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>3.7507530034252027E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>165</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>5.0388556352573002E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>166</v>
       </c>
@@ -5416,7 +5416,7 @@
         <v>8.0294967571109023E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>167</v>
       </c>
@@ -5470,7 +5470,7 @@
         <v>7.0007171819925801E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>168</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>5.6649151685696242E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>169</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>4.2985466508481168E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>170</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>3.0854060773305718E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>171</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>5.7701883542728865E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>172</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>8.4426260266278266E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>173</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>9.552168804465085E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>174</v>
       </c>
@@ -5848,7 +5848,7 @@
         <v>3.5786093692759128E-4</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>175</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>9.5065057852621645E-4</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>176</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>4.7094307374518279E-4</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>177</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>7.0474477053287924E-4</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>178</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>6.47540851284781E-4</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>179</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>9.4119160098010126E-4</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>180</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>5.0662494239123103E-4</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>181</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>5.5343966107292586E-4</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>182</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>6.3697425558412722E-4</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>183</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>7.291229427225874E-4</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>184</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>6.4225139746381982E-4</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>185</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>4.8630228955171201E-4</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>186</v>
       </c>
@@ -6496,7 +6496,7 @@
         <v>7.8134219163826664E-4</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>5.8506117777726231E-4</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>188</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>6.370758623671785E-4</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>189</v>
       </c>
@@ -6658,7 +6658,7 @@
         <v>8.0515352214514436E-4</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>190</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>5.750724982417129E-4</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>191</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>6.7040596663695798E-4</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>192</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>6.6752831004103605E-4</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>193</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>6.8681608077582183E-4</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>194</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>8.5098987706838051E-4</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>195</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>6.7755654381398901E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>196</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>9.4339543613295384E-4</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>197</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>5.8085408169564559E-4</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>198</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>3.6120501290660029E-4</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>199</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>6.2975536923403231E-4</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>200</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>7.228323272845125E-4</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>201</v>
       </c>
@@ -7306,7 +7306,7 @@
         <v>4.6803677487896461E-4</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>202</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>7.7336905885629418E-4</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>203</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>5.6237098746364077E-4</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>204</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>8.1362777910270177E-4</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>205</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>4.356087488178263E-4</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>206</v>
       </c>
@@ -7576,7 +7576,7 @@
         <v>1.0028195602172999E-3</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>207</v>
       </c>
@@ -7630,7 +7630,7 @@
         <v>5.0364788225881177E-4</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>208</v>
       </c>
@@ -7684,7 +7684,7 @@
         <v>7.9643019829107138E-4</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -7738,7 +7738,7 @@
         <v>4.7180228576033662E-4</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>210</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>6.1373542849109256E-4</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>211</v>
       </c>
@@ -7846,7 +7846,7 @@
         <v>6.4311012308476624E-4</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>212</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>6.2770310871303756E-4</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>213</v>
       </c>
@@ -7954,7 +7954,7 @@
         <v>5.7559569640524308E-4</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>214</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>5.3332641124062639E-4</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>215</v>
       </c>
@@ -8062,7 +8062,7 @@
         <v>8.2728508003655082E-4</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>216</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>9.7268368705790624E-4</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>217</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>4.8961483057842047E-4</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>218</v>
       </c>
@@ -8224,7 +8224,7 @@
         <v>5.6725746685323385E-4</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>219</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>5.7586134556664864E-4</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>220</v>
       </c>
@@ -8332,7 +8332,7 @@
         <v>6.64750588599489E-4</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>221</v>
       </c>
@@ -8386,7 +8386,7 @@
         <v>9.4712108096549959E-4</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>222</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>5.5438130895789643E-4</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>223</v>
       </c>
@@ -8494,7 +8494,7 @@
         <v>9.0184342071178349E-4</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>224</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>6.2612911789142764E-4</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>225</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>7.5873173424928584E-4</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>226</v>
       </c>
@@ -8656,7 +8656,7 @@
         <v>6.1259290710490542E-4</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>227</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>6.9084118394068103E-4</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>228</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>6.6669851278469488E-4</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>229</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>8.2045218583240757E-4</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>230</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>5.2081387235738941E-4</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>231</v>
       </c>
@@ -8926,7 +8926,7 @@
         <v>5.7189465431413248E-4</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>232</v>
       </c>
@@ -8980,7 +8980,7 @@
         <v>9.1233097501937279E-4</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>233</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>5.1138621680753824E-4</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>234</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>5.834401472729541E-4</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>235</v>
       </c>
@@ -9142,7 +9142,7 @@
         <v>7.1160228947361758E-4</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>236</v>
       </c>
@@ -9196,7 +9196,7 @@
         <v>6.7192904177343729E-4</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>237</v>
       </c>
@@ -9250,7 +9250,7 @@
         <v>6.8402164621609858E-4</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>238</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>7.3510433221211555E-4</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>239</v>
       </c>
@@ -9358,7 +9358,7 @@
         <v>6.8958168854050443E-4</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>240</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>7.0175093423377206E-4</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>241</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>9.24392529713391E-4</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>242</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>4.2679489394130968E-4</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>243</v>
       </c>
@@ -9574,7 +9574,7 @@
         <v>7.0492044974188462E-4</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -9628,7 +9628,7 @@
         <v>6.0317831663807579E-4</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>245</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>5.3431529879549361E-4</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>246</v>
       </c>
@@ -9736,7 +9736,7 @@
         <v>9.2650687165257131E-4</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>247</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>4.9093461376614072E-4</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>248</v>
       </c>
@@ -9844,7 +9844,7 @@
         <v>4.6471042769603648E-4</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>249</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>3.9116170433328728E-4</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>250</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>4.0431038289007962E-4</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>251</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>6.785411243790979E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>252</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>7.2348983877483703E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>253</v>
       </c>
@@ -10114,7 +10114,7 @@
         <v>6.5532909863160892E-4</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>254</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>7.5474341979737567E-4</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>255</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>5.7669688744116539E-4</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>256</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>8.0697176066542612E-4</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>257</v>
       </c>
@@ -10330,7 +10330,7 @@
         <v>6.0999509381094925E-4</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>258</v>
       </c>
@@ -10384,7 +10384,7 @@
         <v>5.3117803129513444E-4</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>259</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>6.8402085428227407E-4</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>260</v>
       </c>
@@ -10492,7 +10492,7 @@
         <v>5.6115552392589597E-4</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>261</v>
       </c>
@@ -10546,7 +10546,7 @@
         <v>5.6175108458420442E-4</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>262</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>263</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>264</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>265</v>
       </c>
@@ -10662,7 +10662,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>266</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>267</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>268</v>
       </c>
@@ -10749,7 +10749,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>269</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>270</v>
       </c>
@@ -10807,7 +10807,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>271</v>
       </c>
@@ -10836,7 +10836,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>272</v>
       </c>
@@ -10865,7 +10865,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>273</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>274</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>275</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>276</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>277</v>
       </c>
@@ -11010,7 +11010,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>278</v>
       </c>
@@ -11039,7 +11039,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>279</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>280</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>281</v>
       </c>
@@ -11126,7 +11126,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>282</v>
       </c>
@@ -11155,7 +11155,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>283</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>284</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>285</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>286</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>287</v>
       </c>
@@ -11300,7 +11300,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>288</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>289</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>290</v>
       </c>
@@ -11387,7 +11387,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>291</v>
       </c>
@@ -11416,7 +11416,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>292</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>293</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>294</v>
       </c>
@@ -11503,7 +11503,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>295</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>296</v>
       </c>
@@ -11561,7 +11561,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>297</v>
       </c>
@@ -11590,7 +11590,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>298</v>
       </c>
@@ -11619,7 +11619,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>299</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>300</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>301</v>
       </c>
@@ -11706,7 +11706,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>302</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>303</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>304</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>305</v>
       </c>
@@ -11822,7 +11822,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>306</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>307</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>308</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>309</v>
       </c>
@@ -11938,7 +11938,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>310</v>
       </c>
@@ -11967,7 +11967,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>311</v>
       </c>
@@ -11996,7 +11996,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>312</v>
       </c>
@@ -12025,7 +12025,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>313</v>
       </c>
@@ -12054,7 +12054,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>314</v>
       </c>
@@ -12083,7 +12083,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>315</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>316</v>
       </c>
@@ -12141,7 +12141,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>317</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>318</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>1950</v>
       </c>
@@ -12228,7 +12228,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>1951</v>
       </c>
@@ -12257,7 +12257,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>1952</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>1953</v>
       </c>
@@ -12315,7 +12315,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>1954</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>1955</v>
       </c>
@@ -12373,7 +12373,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>1956</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>1957</v>
       </c>
@@ -12431,7 +12431,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>1958</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>1959</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>1960</v>
       </c>
@@ -12518,7 +12518,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>1961</v>
       </c>
@@ -12547,7 +12547,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>1962</v>
       </c>
@@ -12576,7 +12576,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>1963</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>1964</v>
       </c>
@@ -12634,7 +12634,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>1965</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>1966</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>1967</v>
       </c>
@@ -12721,7 +12721,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>1968</v>
       </c>
@@ -12750,7 +12750,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>1969</v>
       </c>
@@ -12779,7 +12779,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>1970</v>
       </c>
@@ -12808,7 +12808,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>1971</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>1972</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>1973</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>1974</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>1975</v>
       </c>
@@ -12953,7 +12953,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>1976</v>
       </c>
@@ -12982,7 +12982,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>1977</v>
       </c>
@@ -13011,7 +13011,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>1978</v>
       </c>
@@ -13040,7 +13040,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>1979</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>1980</v>
       </c>
@@ -13098,7 +13098,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>1981</v>
       </c>
@@ -13127,7 +13127,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>1982</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>1983</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>1984</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>1985</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>1986</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>1987</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>1988</v>
       </c>
@@ -13330,7 +13330,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>1989</v>
       </c>
@@ -13359,7 +13359,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>1990</v>
       </c>
@@ -13388,7 +13388,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>1991</v>
       </c>
@@ -13417,7 +13417,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>1992</v>
       </c>
@@ -13446,7 +13446,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>1993</v>
       </c>
@@ -13475,7 +13475,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>1994</v>
       </c>
@@ -13504,7 +13504,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>1995</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>1996</v>
       </c>
@@ -13562,7 +13562,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>1997</v>
       </c>
@@ -13591,7 +13591,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>1998</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>1999</v>
       </c>
@@ -13649,7 +13649,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>2000</v>
       </c>
@@ -13678,7 +13678,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>2001</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>2002</v>
       </c>
@@ -13736,7 +13736,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>2003</v>
       </c>
@@ -13765,7 +13765,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>2004</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>2005</v>
       </c>
@@ -13823,7 +13823,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>2006</v>
       </c>
@@ -13852,7 +13852,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>2007</v>
       </c>
@@ -13881,7 +13881,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>2008</v>
       </c>
@@ -13910,7 +13910,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>2009</v>
       </c>
@@ -13939,7 +13939,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>2010</v>
       </c>
@@ -13968,7 +13968,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>2011</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>2012</v>
       </c>
@@ -14026,7 +14026,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>2013</v>
       </c>
@@ -14055,7 +14055,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>2014</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>2015</v>
       </c>
@@ -14113,7 +14113,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>2016</v>
       </c>
@@ -14142,7 +14142,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>2017</v>
       </c>
@@ -14171,7 +14171,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>2018</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>2019</v>
       </c>
@@ -14229,7 +14229,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>2020</v>
       </c>
@@ -14258,7 +14258,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>2021</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>2022</v>
       </c>
@@ -14316,7 +14316,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>2023</v>
       </c>
@@ -14345,7 +14345,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>2024</v>
       </c>
@@ -14374,7 +14374,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>2025</v>
       </c>
@@ -14403,7 +14403,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>2026</v>
       </c>
@@ -14432,7 +14432,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>2027</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>2028</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>2029</v>
       </c>
@@ -14519,7 +14519,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>2030</v>
       </c>
@@ -14548,7 +14548,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>2031</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>2032</v>
       </c>
@@ -14606,7 +14606,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>2033</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>2034</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>2035</v>
       </c>
@@ -14693,7 +14693,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>2036</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>2037</v>
       </c>
@@ -14751,7 +14751,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>2038</v>
       </c>
@@ -14780,7 +14780,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>2039</v>
       </c>
@@ -14809,7 +14809,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>2040</v>
       </c>
@@ -14838,7 +14838,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>2041</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>2042</v>
       </c>
@@ -14896,7 +14896,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>2043</v>
       </c>
@@ -14925,7 +14925,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>2044</v>
       </c>
@@ -14954,7 +14954,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>2045</v>
       </c>
@@ -14983,7 +14983,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>2046</v>
       </c>
@@ -15012,7 +15012,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>2047</v>
       </c>
@@ -15041,7 +15041,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>2048</v>
       </c>
@@ -15070,7 +15070,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>2049</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>2050</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>2051</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>2052</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>2053</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>2054</v>
       </c>
@@ -15244,7 +15244,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>2055</v>
       </c>
@@ -15273,7 +15273,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>2056</v>
       </c>
@@ -15302,7 +15302,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>2057</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>2058</v>
       </c>
@@ -15360,7 +15360,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>2059</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>2060</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>2061</v>
       </c>
@@ -15447,7 +15447,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>2062</v>
       </c>
@@ -15476,7 +15476,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>2063</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>2064</v>
       </c>
@@ -15534,7 +15534,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>2065</v>
       </c>
@@ -15563,7 +15563,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>2066</v>
       </c>
@@ -15592,7 +15592,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>2067</v>
       </c>
@@ -15621,7 +15621,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>2068</v>
       </c>
@@ -15650,7 +15650,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>2069</v>
       </c>
@@ -15679,7 +15679,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>2070</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>2071</v>
       </c>
@@ -15737,7 +15737,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>2072</v>
       </c>
@@ -15766,7 +15766,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>2073</v>
       </c>
@@ -15795,7 +15795,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>2074</v>
       </c>
@@ -15824,7 +15824,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>2075</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>2076</v>
       </c>
@@ -15882,7 +15882,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>2077</v>
       </c>
@@ -15911,7 +15911,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>2078</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>2079</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>2080</v>
       </c>
@@ -15998,7 +15998,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>2081</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>2082</v>
       </c>
@@ -16056,7 +16056,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>2083</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>2084</v>
       </c>
@@ -16114,7 +16114,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>2085</v>
       </c>
@@ -16143,7 +16143,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>2086</v>
       </c>
@@ -16172,7 +16172,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>2087</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>2088</v>
       </c>
@@ -16230,7 +16230,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>2089</v>
       </c>
@@ -16259,7 +16259,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>2090</v>
       </c>
@@ -16288,7 +16288,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>2091</v>
       </c>
@@ -16317,7 +16317,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>2092</v>
       </c>
@@ -16346,7 +16346,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>2093</v>
       </c>
@@ -16375,7 +16375,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>2094</v>
       </c>
@@ -16404,7 +16404,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>2095</v>
       </c>
@@ -16433,7 +16433,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>2096</v>
       </c>
@@ -16462,7 +16462,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>2097</v>
       </c>
@@ -16491,7 +16491,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>2098</v>
       </c>
@@ -16520,7 +16520,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>2099</v>
       </c>
@@ -16549,7 +16549,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>2100</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>319</v>
       </c>
@@ -16607,7 +16607,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B364">
         <v>20000000</v>
       </c>
@@ -16636,18 +16636,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="5.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.53125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.46484375" customWidth="1"/>
+    <col min="2" max="2" width="5.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -16679,7 +16679,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -16699,19 +16699,19 @@
         <v>300</v>
       </c>
       <c r="G2" s="8">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>3</v>
       </c>
       <c r="I2">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -16731,19 +16731,19 @@
         <v>150</v>
       </c>
       <c r="G3" s="8">
-        <v>187.5</v>
+        <v>42</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -16763,19 +16763,19 @@
         <v>200</v>
       </c>
       <c r="G4" s="8">
-        <v>112.5</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -16795,19 +16795,19 @@
         <v>150</v>
       </c>
       <c r="G5" s="8">
-        <v>75</v>
+        <v>17</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
       <c r="I5">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -16833,7 +16833,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -16847,12 +16847,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E365"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="40.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -16869,7 +16869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -16886,7 +16886,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -16903,7 +16903,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -16920,7 +16920,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -16937,7 +16937,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -16954,1078 +16954,1078 @@
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="3"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="3"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="3"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="3"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136" s="3"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137" s="3"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138" s="3"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139" s="3"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140" s="3"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141" s="3"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142" s="3"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143" s="3"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144" s="3"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" s="3"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150" s="3"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151" s="3"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152" s="3"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153" s="3"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154" s="3"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155" s="3"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156" s="3"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157" s="3"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158" s="3"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159" s="3"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160" s="3"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161" s="3"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162" s="3"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163" s="3"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164" s="3"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165" s="3"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166" s="3"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167" s="3"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168" s="3"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169" s="3"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170" s="3"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171" s="3"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172" s="3"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173" s="3"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174" s="3"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175" s="3"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176" s="3"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177" s="3"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178" s="3"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179" s="3"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180" s="3"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181" s="3"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182" s="3"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183" s="3"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184" s="3"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185" s="3"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186" s="3"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187" s="3"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188" s="3"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189" s="3"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190" s="3"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191" s="3"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192" s="3"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193" s="3"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194" s="3"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195" s="3"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196" s="3"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197" s="3"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198" s="3"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199" s="3"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200" s="3"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201" s="3"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202" s="3"/>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203" s="3"/>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204" s="3"/>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205" s="3"/>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206" s="3"/>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207" s="3"/>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208" s="3"/>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209" s="3"/>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210" s="3"/>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211" s="3"/>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212" s="3"/>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213" s="3"/>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214" s="3"/>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215" s="3"/>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216" s="3"/>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217" s="3"/>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218" s="3"/>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219" s="3"/>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220" s="3"/>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221" s="3"/>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222" s="3"/>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223" s="3"/>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224" s="3"/>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225" s="3"/>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226" s="3"/>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227" s="3"/>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228" s="3"/>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229" s="3"/>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230" s="3"/>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231" s="3"/>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232" s="3"/>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233" s="3"/>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234" s="3"/>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235" s="3"/>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236" s="3"/>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237" s="3"/>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238" s="3"/>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239" s="3"/>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240" s="3"/>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241" s="3"/>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242" s="3"/>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243" s="3"/>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244" s="3"/>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245" s="3"/>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246" s="3"/>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247" s="3"/>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248" s="3"/>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249" s="3"/>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250" s="3"/>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251" s="3"/>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252" s="3"/>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253" s="3"/>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254" s="3"/>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255" s="3"/>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256" s="3"/>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257" s="3"/>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258" s="3"/>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259" s="3"/>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260" s="3"/>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261" s="3"/>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262" s="3"/>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263" s="3"/>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264" s="3"/>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265" s="3"/>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266" s="3"/>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267" s="3"/>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268" s="3"/>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269" s="3"/>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270" s="3"/>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271" s="3"/>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272" s="3"/>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273" s="3"/>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274" s="3"/>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275" s="3"/>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276" s="3"/>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277" s="3"/>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278" s="3"/>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279" s="3"/>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A280" s="3"/>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281" s="3"/>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A282" s="3"/>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283" s="3"/>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A284" s="3"/>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A285" s="3"/>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A286" s="3"/>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A287" s="3"/>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A288" s="3"/>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A289" s="3"/>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A290" s="3"/>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A291" s="3"/>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A292" s="3"/>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A293" s="3"/>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A294" s="3"/>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A295" s="3"/>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A296" s="3"/>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A297" s="3"/>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A298" s="3"/>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A299" s="3"/>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A300" s="3"/>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A301" s="3"/>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A302" s="3"/>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A303" s="3"/>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A304" s="3"/>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A305" s="3"/>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A306" s="3"/>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A307" s="3"/>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A308" s="3"/>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A309" s="3"/>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A310" s="3"/>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A311" s="3"/>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A312" s="3"/>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A313" s="3"/>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A314" s="3"/>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A315" s="3"/>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A316" s="3"/>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A317" s="3"/>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A318" s="3"/>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A319" s="3"/>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A320" s="3"/>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A321" s="3"/>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A322" s="3"/>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A323" s="3"/>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A324" s="3"/>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A325" s="3"/>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A326" s="3"/>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A327" s="3"/>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A328" s="3"/>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A329" s="3"/>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A330" s="3"/>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A331" s="3"/>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A332" s="3"/>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A333" s="3"/>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A334" s="3"/>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A335" s="3"/>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A336" s="3"/>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A337" s="3"/>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A338" s="3"/>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A339" s="3"/>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A340" s="3"/>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A341" s="3"/>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A342" s="3"/>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A343" s="3"/>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A344" s="3"/>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A345" s="3"/>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A346" s="3"/>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A347" s="3"/>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A348" s="3"/>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A349" s="3"/>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A350" s="3"/>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A351" s="3"/>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A352" s="3"/>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A353" s="3"/>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A354" s="3"/>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A355" s="3"/>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A356" s="3"/>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A357" s="3"/>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A358" s="3"/>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A359" s="3"/>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A360" s="3"/>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A361" s="3"/>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A362" s="3"/>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A363" s="3"/>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A364" s="3"/>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A365" s="3"/>
     </row>
   </sheetData>
@@ -18036,9 +18036,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L363"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -18058,28 +18058,33 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>5.5555555555555556E-4</v>
+        <v>5.5555555555555558E-5</v>
       </c>
       <c r="C2" s="1">
+        <v>5.5555555555555558E-6</v>
+      </c>
+      <c r="D2" s="1">
         <v>5.5555555555555558E-5</v>
       </c>
-      <c r="D2" s="1">
-        <v>5.5555555555555556E-4</v>
-      </c>
       <c r="E2" s="1">
+        <v>5.5555555555555558E-6</v>
+      </c>
+      <c r="F2" s="1">
         <v>5.5555555555555558E-5</v>
       </c>
-      <c r="F2" s="1">
-        <v>5.5555555555555556E-4</v>
-      </c>
       <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>3600000</v>
       </c>
@@ -18105,7 +18110,7 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>400000000</v>
       </c>
@@ -18126,28 +18131,28 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -18155,7 +18160,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -18163,7 +18168,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -18171,7 +18176,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -18179,7 +18184,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -18187,7 +18192,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -18195,7 +18200,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -18203,7 +18208,7 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -18211,7 +18216,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -18219,7 +18224,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -18227,7 +18232,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -18235,7 +18240,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -18243,7 +18248,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -18251,7 +18256,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -18259,7 +18264,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -18267,7 +18272,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -18275,7 +18280,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -18283,7 +18288,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -18291,7 +18296,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -18299,7 +18304,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -18307,7 +18312,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -18315,7 +18320,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -18323,7 +18328,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -18331,7 +18336,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -18339,7 +18344,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -18347,7 +18352,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -18355,7 +18360,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -18363,7 +18368,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -18371,7 +18376,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -18379,7 +18384,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -18387,7 +18392,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -18395,7 +18400,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -18403,7 +18408,7 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -18411,7 +18416,7 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -18419,7 +18424,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -18427,7 +18432,7 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -18435,7 +18440,7 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -18443,7 +18448,7 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -18451,7 +18456,7 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -18459,7 +18464,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -18467,7 +18472,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -18475,7 +18480,7 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -18483,7 +18488,7 @@
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -18491,7 +18496,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -18499,7 +18504,7 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -18507,7 +18512,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -18515,7 +18520,7 @@
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -18523,7 +18528,7 @@
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -18531,7 +18536,7 @@
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -18539,7 +18544,7 @@
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -18547,7 +18552,7 @@
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -18555,7 +18560,7 @@
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -18563,7 +18568,7 @@
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -18571,7 +18576,7 @@
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -18579,7 +18584,7 @@
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -18587,7 +18592,7 @@
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -18595,7 +18600,7 @@
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -18603,7 +18608,7 @@
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -18611,7 +18616,7 @@
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -18619,7 +18624,7 @@
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -18627,7 +18632,7 @@
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -18635,7 +18640,7 @@
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -18643,7 +18648,7 @@
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -18651,7 +18656,7 @@
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -18659,7 +18664,7 @@
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -18667,7 +18672,7 @@
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -18675,7 +18680,7 @@
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -18683,7 +18688,7 @@
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -18691,7 +18696,7 @@
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -18699,7 +18704,7 @@
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -18707,7 +18712,7 @@
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -18715,7 +18720,7 @@
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -18723,7 +18728,7 @@
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -18731,7 +18736,7 @@
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -18739,7 +18744,7 @@
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -18747,7 +18752,7 @@
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -18755,7 +18760,7 @@
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -18763,7 +18768,7 @@
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -18771,7 +18776,7 @@
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -18779,7 +18784,7 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -18787,7 +18792,7 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -18795,7 +18800,7 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -18803,7 +18808,7 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -18811,7 +18816,7 @@
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -18819,7 +18824,7 @@
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -18827,7 +18832,7 @@
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -18835,7 +18840,7 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -18843,7 +18848,7 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -18851,7 +18856,7 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -18859,7 +18864,7 @@
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -18867,7 +18872,7 @@
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -18875,7 +18880,7 @@
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -18883,7 +18888,7 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
@@ -18891,7 +18896,7 @@
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
@@ -18899,7 +18904,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
@@ -18907,7 +18912,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
@@ -18915,7 +18920,7 @@
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
@@ -18923,7 +18928,7 @@
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
@@ -18931,7 +18936,7 @@
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
@@ -18939,7 +18944,7 @@
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
@@ -18947,7 +18952,7 @@
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
@@ -18955,7 +18960,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
@@ -18963,7 +18968,7 @@
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
@@ -18971,7 +18976,7 @@
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
@@ -18979,7 +18984,7 @@
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
@@ -18987,7 +18992,7 @@
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
@@ -18995,7 +19000,7 @@
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
@@ -19003,7 +19008,7 @@
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
@@ -19011,7 +19016,7 @@
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
@@ -19019,7 +19024,7 @@
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
@@ -19027,7 +19032,7 @@
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
@@ -19035,7 +19040,7 @@
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
@@ -19043,7 +19048,7 @@
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
@@ -19051,7 +19056,7 @@
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
@@ -19059,7 +19064,7 @@
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
@@ -19067,7 +19072,7 @@
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
@@ -19075,7 +19080,7 @@
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
@@ -19083,7 +19088,7 @@
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
     </row>
-    <row r="125" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
@@ -19091,7 +19096,7 @@
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
     </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
@@ -19099,7 +19104,7 @@
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
@@ -19107,7 +19112,7 @@
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
@@ -19115,7 +19120,7 @@
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -19123,7 +19128,7 @@
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
     </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
@@ -19131,7 +19136,7 @@
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
@@ -19139,7 +19144,7 @@
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
@@ -19147,7 +19152,7 @@
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
     </row>
-    <row r="133" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
@@ -19155,7 +19160,7 @@
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
     </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
@@ -19163,7 +19168,7 @@
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
-    <row r="135" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
@@ -19171,7 +19176,7 @@
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
     </row>
-    <row r="136" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
@@ -19179,7 +19184,7 @@
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
@@ -19187,7 +19192,7 @@
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -19195,7 +19200,7 @@
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
     </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
@@ -19203,7 +19208,7 @@
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
@@ -19211,7 +19216,7 @@
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
@@ -19219,7 +19224,7 @@
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
     </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
@@ -19227,7 +19232,7 @@
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
     </row>
-    <row r="143" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
@@ -19235,7 +19240,7 @@
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
     </row>
-    <row r="144" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -19243,7 +19248,7 @@
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
     </row>
-    <row r="145" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
@@ -19251,7 +19256,7 @@
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
     </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
@@ -19259,7 +19264,7 @@
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
     </row>
-    <row r="147" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
@@ -19267,7 +19272,7 @@
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
     </row>
-    <row r="148" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
@@ -19275,7 +19280,7 @@
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
     </row>
-    <row r="149" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
@@ -19283,7 +19288,7 @@
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
     </row>
-    <row r="150" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
@@ -19291,7 +19296,7 @@
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
     </row>
-    <row r="151" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
@@ -19299,7 +19304,7 @@
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
     </row>
-    <row r="152" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
@@ -19307,7 +19312,7 @@
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
     </row>
-    <row r="153" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
@@ -19315,7 +19320,7 @@
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
     </row>
-    <row r="154" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
@@ -19323,7 +19328,7 @@
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
     </row>
-    <row r="155" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
@@ -19331,7 +19336,7 @@
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
     </row>
-    <row r="156" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
@@ -19339,7 +19344,7 @@
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
     </row>
-    <row r="157" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
@@ -19347,7 +19352,7 @@
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
     </row>
-    <row r="158" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
@@ -19355,7 +19360,7 @@
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
     </row>
-    <row r="159" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
@@ -19363,7 +19368,7 @@
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
     </row>
-    <row r="160" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
@@ -19371,7 +19376,7 @@
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
     </row>
-    <row r="161" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
@@ -19379,7 +19384,7 @@
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
     </row>
-    <row r="162" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
@@ -19387,7 +19392,7 @@
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
     </row>
-    <row r="163" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
@@ -19395,7 +19400,7 @@
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
     </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
@@ -19403,7 +19408,7 @@
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
     </row>
-    <row r="165" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
@@ -19411,7 +19416,7 @@
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
     </row>
-    <row r="166" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
@@ -19419,7 +19424,7 @@
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
     </row>
-    <row r="167" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
@@ -19427,7 +19432,7 @@
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
     </row>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
@@ -19435,7 +19440,7 @@
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
     </row>
-    <row r="169" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
@@ -19443,7 +19448,7 @@
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
     </row>
-    <row r="170" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
@@ -19451,7 +19456,7 @@
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
     </row>
-    <row r="171" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
@@ -19459,7 +19464,7 @@
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
     </row>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
@@ -19467,7 +19472,7 @@
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
     </row>
-    <row r="173" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
@@ -19475,7 +19480,7 @@
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
     </row>
-    <row r="174" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
@@ -19483,7 +19488,7 @@
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
     </row>
-    <row r="175" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
@@ -19491,7 +19496,7 @@
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
     </row>
-    <row r="176" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
@@ -19499,7 +19504,7 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
     </row>
-    <row r="177" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
@@ -19507,7 +19512,7 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
     </row>
-    <row r="178" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
@@ -19515,7 +19520,7 @@
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
     </row>
-    <row r="179" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
@@ -19523,7 +19528,7 @@
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
     </row>
-    <row r="180" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
@@ -19531,7 +19536,7 @@
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
     </row>
-    <row r="181" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
@@ -19539,7 +19544,7 @@
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
     </row>
-    <row r="182" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
@@ -19547,7 +19552,7 @@
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
     </row>
-    <row r="183" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
@@ -19555,7 +19560,7 @@
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
     </row>
-    <row r="184" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
@@ -19563,7 +19568,7 @@
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
     </row>
-    <row r="185" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
@@ -19571,7 +19576,7 @@
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
     </row>
-    <row r="186" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
@@ -19579,7 +19584,7 @@
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
     </row>
-    <row r="187" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
@@ -19587,7 +19592,7 @@
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
     </row>
-    <row r="188" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
@@ -19595,7 +19600,7 @@
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
     </row>
-    <row r="189" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
@@ -19603,7 +19608,7 @@
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
     </row>
-    <row r="190" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
@@ -19611,7 +19616,7 @@
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
@@ -19619,7 +19624,7 @@
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
     </row>
-    <row r="192" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
@@ -19627,7 +19632,7 @@
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
     </row>
-    <row r="193" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
@@ -19635,7 +19640,7 @@
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
     </row>
-    <row r="194" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
@@ -19643,7 +19648,7 @@
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
     </row>
-    <row r="195" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
@@ -19651,7 +19656,7 @@
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
     </row>
-    <row r="196" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
@@ -19659,7 +19664,7 @@
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
     </row>
-    <row r="197" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
@@ -19667,7 +19672,7 @@
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
@@ -19675,7 +19680,7 @@
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
     </row>
-    <row r="199" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
@@ -19683,7 +19688,7 @@
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
     </row>
-    <row r="200" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
@@ -19691,7 +19696,7 @@
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
@@ -19699,7 +19704,7 @@
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
     </row>
-    <row r="202" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
@@ -19707,7 +19712,7 @@
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
     </row>
-    <row r="203" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
@@ -19715,7 +19720,7 @@
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
     </row>
-    <row r="204" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
@@ -19723,7 +19728,7 @@
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
     </row>
-    <row r="205" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
@@ -19731,7 +19736,7 @@
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
@@ -19739,7 +19744,7 @@
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
     </row>
-    <row r="207" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
@@ -19747,7 +19752,7 @@
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
     </row>
-    <row r="208" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
@@ -19755,7 +19760,7 @@
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
@@ -19763,7 +19768,7 @@
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
     </row>
-    <row r="210" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
@@ -19771,7 +19776,7 @@
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
     </row>
-    <row r="211" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
@@ -19779,1064 +19784,1064 @@
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
     </row>
-    <row r="212" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
     </row>
-    <row r="213" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
     </row>
-    <row r="215" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
     </row>
-    <row r="216" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
     </row>
-    <row r="217" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
     </row>
-    <row r="219" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
     </row>
-    <row r="220" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
     </row>
-    <row r="221" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
     </row>
-    <row r="223" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
     </row>
-    <row r="225" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="225" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
     </row>
-    <row r="226" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="226" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
     </row>
-    <row r="227" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="227" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
     </row>
-    <row r="228" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="228" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
     </row>
-    <row r="229" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="229" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
     </row>
-    <row r="230" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="230" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
     </row>
-    <row r="231" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="231" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
     </row>
-    <row r="232" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="232" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
     </row>
-    <row r="233" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="233" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
     </row>
-    <row r="234" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="234" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
     </row>
-    <row r="235" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="235" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
-    <row r="236" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="236" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
     </row>
-    <row r="237" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="237" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
     </row>
-    <row r="238" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="238" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
     </row>
-    <row r="239" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="239" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
     </row>
-    <row r="240" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="240" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
     </row>
-    <row r="241" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="241" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
     </row>
-    <row r="242" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="242" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
     </row>
-    <row r="243" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="243" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
     </row>
-    <row r="244" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="244" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
     </row>
-    <row r="245" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="245" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
     </row>
-    <row r="246" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="246" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
     </row>
-    <row r="247" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="247" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
-    <row r="248" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="248" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
     </row>
-    <row r="249" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="249" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
     </row>
-    <row r="250" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="250" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
     </row>
-    <row r="251" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="251" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
     </row>
-    <row r="252" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="252" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
     </row>
-    <row r="253" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="253" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
     </row>
-    <row r="254" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="254" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="1"/>
     </row>
-    <row r="255" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="255" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
     </row>
-    <row r="256" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="256" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
     </row>
-    <row r="257" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="257" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
     </row>
-    <row r="258" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="258" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
     </row>
-    <row r="259" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="259" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
     </row>
-    <row r="260" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="260" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
     </row>
-    <row r="261" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="261" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
     </row>
-    <row r="262" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="262" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
     </row>
-    <row r="263" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="263" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
     </row>
-    <row r="264" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="264" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
     </row>
-    <row r="265" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="265" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
     </row>
-    <row r="266" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="266" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
     </row>
-    <row r="267" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="267" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
     </row>
-    <row r="268" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="268" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
     </row>
-    <row r="269" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="269" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
     </row>
-    <row r="270" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="270" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
     </row>
-    <row r="271" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="271" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
     </row>
-    <row r="272" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="272" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
     </row>
-    <row r="273" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="273" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
     </row>
-    <row r="274" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="274" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
     </row>
-    <row r="275" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="275" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
     </row>
-    <row r="276" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="276" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
     </row>
-    <row r="277" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="277" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
     </row>
-    <row r="278" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="278" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
     </row>
-    <row r="279" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="279" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
     </row>
-    <row r="280" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="280" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
     </row>
-    <row r="281" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="281" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1"/>
     </row>
-    <row r="282" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="282" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="1"/>
     </row>
-    <row r="283" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="283" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
     </row>
-    <row r="284" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="284" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
     </row>
-    <row r="285" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="285" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
     </row>
-    <row r="286" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="286" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
     </row>
-    <row r="287" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="287" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
     </row>
-    <row r="288" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="288" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
     </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="289" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
     </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="290" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
     </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="291" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
     </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="292" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
     </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="293" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
     </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="294" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="1"/>
     </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="295" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
     </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="296" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
     </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="297" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
     </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="298" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
     </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="299" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
     </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="300" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
     </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="301" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
     </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="302" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="1"/>
     </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="303" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
     </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="304" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
     </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="305" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
     </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="306" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
     </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="307" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
     </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="308" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
     </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="309" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
     </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="310" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
     </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="311" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
     </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="312" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
     </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="313" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
     </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="314" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
     </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="315" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
     </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="316" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
     </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="317" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
     </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="318" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
     </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="319" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
     </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="320" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
     </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="321" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
     </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="322" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
     </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="323" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
     </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="324" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
     </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="325" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
     </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="326" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
     </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="327" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
     </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="328" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
     </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="329" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
     </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="330" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
     </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="331" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
     </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="332" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
     </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="333" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
     </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="334" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
     </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="335" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
     </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="336" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
     </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="337" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
     </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="338" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
     </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="339" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
     </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="340" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
     </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="341" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
     </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="342" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
     </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="343" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
     </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="344" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
     </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="345" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
     </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="346" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
     </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="347" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
     </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="348" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
     </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="349" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
     </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="350" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
     </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="351" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
     </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="352" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
     </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="353" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
     </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="354" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
     </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="355" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
     </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="356" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
     </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="357" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
     </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="358" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
     </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="359" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
     </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="360" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
     </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="361" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
     </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="362" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
     </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="363" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -20852,12 +20857,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>37</v>
       </c>
@@ -20883,7 +20888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>44</v>
       </c>
@@ -20909,7 +20914,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>48</v>
       </c>
@@ -20935,7 +20940,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -20961,7 +20966,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
@@ -20987,7 +20992,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>54</v>
       </c>
@@ -21013,7 +21018,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -21039,7 +21044,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>57</v>
       </c>
@@ -21065,7 +21070,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>58</v>
       </c>
@@ -21091,7 +21096,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
@@ -21117,7 +21122,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>60</v>
       </c>
@@ -21143,7 +21148,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>61</v>
       </c>
@@ -21169,7 +21174,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>63</v>
       </c>
@@ -21195,7 +21200,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>64</v>
       </c>
@@ -21221,7 +21226,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>65</v>
       </c>
@@ -21247,7 +21252,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -21273,7 +21278,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
@@ -21299,7 +21304,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
@@ -21325,7 +21330,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>69</v>
       </c>
@@ -21351,7 +21356,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>70</v>
       </c>
@@ -21377,7 +21382,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>71</v>
       </c>
@@ -21403,7 +21408,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -21429,7 +21434,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
@@ -21455,7 +21460,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
@@ -21481,7 +21486,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>35</v>
       </c>
@@ -21507,7 +21512,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
@@ -21533,7 +21538,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>73</v>
       </c>
@@ -21559,7 +21564,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>74</v>
       </c>
@@ -21585,7 +21590,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>75</v>
       </c>
@@ -21611,7 +21616,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>76</v>
       </c>
@@ -21637,7 +21642,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>77</v>
       </c>
@@ -21663,12 +21668,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
         <v>326</v>
       </c>
       <c r="B32" s="1">
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="C32">
         <v>3.1154231364886891E-4</v>
@@ -21698,12 +21703,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>78</v>
       </c>
@@ -21720,7 +21725,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>329</v>
       </c>
@@ -21731,13 +21736,13 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>330</v>
       </c>
@@ -21748,13 +21753,13 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>331</v>
       </c>
@@ -21765,13 +21770,13 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>332</v>
       </c>
@@ -21782,13 +21787,13 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E5">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>333</v>
       </c>
@@ -21799,13 +21804,13 @@
         <v>13</v>
       </c>
       <c r="D6">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E6">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>334</v>
       </c>
@@ -21816,10 +21821,10 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E7">
-        <v>112</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -21830,12 +21835,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>84</v>
       </c>
@@ -21855,7 +21860,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -21866,16 +21871,16 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E2">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -21886,16 +21891,16 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -21906,16 +21911,16 @@
         <v>7</v>
       </c>
       <c r="D4">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -21926,16 +21931,16 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E5">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -21946,16 +21951,16 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -21966,16 +21971,16 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E7">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -21986,16 +21991,16 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E8">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -22006,16 +22011,16 @@
         <v>7</v>
       </c>
       <c r="D9">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E9">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -22026,16 +22031,16 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>224</v>
+        <v>49</v>
       </c>
       <c r="E10">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -22046,16 +22051,16 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E11">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -22066,16 +22071,16 @@
         <v>7</v>
       </c>
       <c r="D12">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E12">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -22086,16 +22091,16 @@
         <v>7</v>
       </c>
       <c r="D13">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E13">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -22106,16 +22111,16 @@
         <v>7</v>
       </c>
       <c r="D14">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E14">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>90</v>
       </c>
@@ -22126,16 +22131,16 @@
         <v>7</v>
       </c>
       <c r="D15">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E15">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -22146,16 +22151,16 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E16">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -22166,16 +22171,16 @@
         <v>7</v>
       </c>
       <c r="D17">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E17">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -22186,16 +22191,16 @@
         <v>7</v>
       </c>
       <c r="D18">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E18">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>123</v>
       </c>
@@ -22206,16 +22211,16 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>225</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>336</v>
       </c>
@@ -22226,16 +22231,16 @@
         <v>7</v>
       </c>
       <c r="D20">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E20">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>336</v>
       </c>
@@ -22246,16 +22251,16 @@
         <v>7</v>
       </c>
       <c r="D21">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E21">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>336</v>
       </c>
@@ -22266,16 +22271,16 @@
         <v>7</v>
       </c>
       <c r="D22">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E22">
-        <v>299</v>
+        <v>66</v>
       </c>
       <c r="F22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>337</v>
       </c>
@@ -22286,16 +22291,16 @@
         <v>7</v>
       </c>
       <c r="D23">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E23">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>337</v>
       </c>
@@ -22306,16 +22311,16 @@
         <v>7</v>
       </c>
       <c r="D24">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E24">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>337</v>
       </c>
@@ -22326,16 +22331,16 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E25">
-        <v>300</v>
+        <v>67</v>
       </c>
       <c r="F25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>338</v>
       </c>
@@ -22346,16 +22351,16 @@
         <v>7</v>
       </c>
       <c r="D26">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E26">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>338</v>
       </c>
@@ -22366,16 +22371,16 @@
         <v>7</v>
       </c>
       <c r="D27">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E27">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>338</v>
       </c>
@@ -22386,13 +22391,13 @@
         <v>7</v>
       </c>
       <c r="D28">
-        <v>226</v>
+        <v>51</v>
       </c>
       <c r="E28">
-        <v>301</v>
+        <v>68</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>-50000</v>
       </c>
     </row>
   </sheetData>
@@ -22403,9 +22408,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -22437,7 +22442,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -22470,7 +22475,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -22503,7 +22508,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>88</v>
       </c>
@@ -22536,7 +22541,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -22569,7 +22574,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>90</v>
       </c>
@@ -22602,7 +22607,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>123</v>
       </c>
@@ -22635,7 +22640,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>336</v>
       </c>
@@ -22668,7 +22673,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>337</v>
       </c>
@@ -22701,7 +22706,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>338</v>
       </c>
@@ -22743,9 +22748,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>84</v>
       </c>
@@ -22780,7 +22785,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -22815,7 +22820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>86</v>
       </c>
@@ -22850,7 +22855,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -22885,7 +22890,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -22920,7 +22925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -22955,7 +22960,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -22990,7 +22995,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>88</v>
       </c>
@@ -23025,7 +23030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -23060,7 +23065,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>88</v>
       </c>
@@ -23095,7 +23100,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>89</v>
       </c>
@@ -23130,7 +23135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -23165,7 +23170,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -23200,7 +23205,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>90</v>
       </c>
@@ -23235,7 +23240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>90</v>
       </c>
@@ -23270,7 +23275,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -23305,7 +23310,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -23340,7 +23345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>123</v>
       </c>
@@ -23375,7 +23380,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>123</v>
       </c>
@@ -23410,7 +23415,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>336</v>
       </c>
@@ -23445,7 +23450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>336</v>
       </c>
@@ -23480,7 +23485,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>336</v>
       </c>
@@ -23515,7 +23520,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>337</v>
       </c>
@@ -23550,7 +23555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>337</v>
       </c>
@@ -23585,7 +23590,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>337</v>
       </c>
@@ -23620,7 +23625,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>338</v>
       </c>
@@ -23655,7 +23660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>338</v>
       </c>
@@ -23690,7 +23695,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>338</v>
       </c>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A7D49A-AAD6-45E3-A045-8B734DDF89A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDBCA2E-14E4-4EED-84CD-DEACA90F24F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="339">
   <si>
     <t>nlay</t>
   </si>
@@ -1054,19 +1054,13 @@
     <t xml:space="preserve">HEAD </t>
   </si>
   <si>
-    <t>WELL_07</t>
-  </si>
-  <si>
-    <t>WELL_08</t>
-  </si>
-  <si>
-    <t>WELL_09</t>
-  </si>
-  <si>
     <t>transition_cells</t>
   </si>
   <si>
     <t>epsilon</t>
+  </si>
+  <si>
+    <t>Caq 2 outcrop</t>
   </si>
 </sst>
 </file>
@@ -1530,22 +1524,22 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="D2">
-        <v>450000</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>450000</v>
       </c>
       <c r="F2">
-        <v>4500</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>4500</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -16642,7 +16636,7 @@
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.453125" customWidth="1"/>
   </cols>
@@ -16673,10 +16667,10 @@
         <v>325</v>
       </c>
       <c r="I1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -16690,7 +16684,7 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -16699,13 +16693,13 @@
         <v>300</v>
       </c>
       <c r="G2" s="8">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -16725,19 +16719,19 @@
         <v>100</v>
       </c>
       <c r="E3">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F3">
         <v>150</v>
       </c>
       <c r="G3" s="8">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -16754,22 +16748,22 @@
         <v>200</v>
       </c>
       <c r="D4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E4">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="F4">
         <v>200</v>
       </c>
       <c r="G4" s="8">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -16786,22 +16780,22 @@
         <v>250</v>
       </c>
       <c r="D5">
+        <v>225</v>
+      </c>
+      <c r="E5">
         <v>300</v>
-      </c>
-      <c r="E5">
-        <v>400</v>
       </c>
       <c r="F5">
         <v>150</v>
       </c>
       <c r="G5" s="8">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -16818,10 +16812,10 @@
         <v>350</v>
       </c>
       <c r="D6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E6">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="F6">
         <v>200</v>
@@ -16830,10 +16824,10 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -16846,7 +16840,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E365"/>
+  <dimension ref="A1:E364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="40.90625" bestFit="1" customWidth="1"/>
@@ -16891,7 +16885,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2520000</v>
+        <v>3600000</v>
       </c>
       <c r="C3">
         <v>100</v>
@@ -16908,16 +16902,16 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>1080000</v>
+        <v>180000</v>
       </c>
       <c r="C4">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -16925,34 +16919,20 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>180000</v>
+        <v>17820000</v>
       </c>
       <c r="C5">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>17820000</v>
-      </c>
-      <c r="C6">
-        <v>495</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
         <v>324</v>
       </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
@@ -18024,9 +18004,6 @@
     </row>
     <row r="364" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A364" s="3"/>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A365" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18063,21 +18040,21 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="C2" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="D2" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="F2" s="1">
-        <v>5.5555555555555558E-5</v>
-      </c>
-      <c r="G2" s="3"/>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -18089,21 +18066,21 @@
         <v>3600000</v>
       </c>
       <c r="B3" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C3" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="D3" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="E3" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="F3" s="1">
-        <v>5.5555555555555558E-5</v>
-      </c>
-      <c r="G3" s="3"/>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -18115,21 +18092,21 @@
         <v>400000000</v>
       </c>
       <c r="B4" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C4" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="D4" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="E4" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="F4" s="1">
-        <v>5.5555555555555558E-5</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="1"/>
@@ -18137,6 +18114,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="1"/>
@@ -20893,7 +20871,7 @@
         <v>44</v>
       </c>
       <c r="B2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>225</v>
@@ -20919,7 +20897,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="1">
-        <v>9.9999999999999995E-7</v>
+        <v>0.1</v>
       </c>
       <c r="C3">
         <v>9.0000000000000002E-6</v>
@@ -20945,7 +20923,7 @@
         <v>50</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>22.5</v>
@@ -20971,7 +20949,7 @@
         <v>52</v>
       </c>
       <c r="B5" s="1">
-        <v>9.9999999999999995E-7</v>
+        <v>0.1</v>
       </c>
       <c r="C5">
         <v>9.0000000000000002E-6</v>
@@ -20997,7 +20975,7 @@
         <v>54</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>22.5</v>
@@ -21049,7 +21027,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="1">
-        <v>9.9999999999999995E-8</v>
+        <v>0.01</v>
       </c>
       <c r="C8">
         <v>9.0000000000000017E-7</v>
@@ -21101,7 +21079,7 @@
         <v>59</v>
       </c>
       <c r="B10" s="1">
-        <v>9.9999999999999995E-8</v>
+        <v>0.01</v>
       </c>
       <c r="C10">
         <v>9.0000000000000017E-7</v>
@@ -21413,7 +21391,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C22">
         <v>3.1154231364886891E-4</v>
@@ -21439,7 +21417,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="C23">
         <v>3.1154231364886891E-5</v>
@@ -21465,7 +21443,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C24">
         <v>3.1154231364886891E-4</v>
@@ -21491,7 +21469,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1">
-        <v>5.5555555555555558E-6</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="C25">
         <v>3.1154231364886891E-5</v>
@@ -21517,7 +21495,7 @@
         <v>36</v>
       </c>
       <c r="B26" s="1">
-        <v>5.5555555555555558E-5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="C26">
         <v>3.1154231364886891E-4</v>
@@ -21673,7 +21651,7 @@
         <v>326</v>
       </c>
       <c r="B32" s="1">
-        <v>-50000</v>
+        <v>0</v>
       </c>
       <c r="C32">
         <v>3.1154231364886891E-4</v>
@@ -21702,7 +21680,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
@@ -21736,10 +21714,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>67</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -21750,13 +21728,13 @@
         <v>83</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>67</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -21767,13 +21745,13 @@
         <v>83</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>67</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -21784,13 +21762,13 @@
         <v>83</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>67</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -21801,13 +21779,13 @@
         <v>83</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>67</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -21818,13 +21796,30 @@
         <v>335</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -21834,7 +21829,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -21868,13 +21863,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>66</v>
+        <v>299</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -21888,16 +21883,16 @@
         <v>3600000</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>66</v>
+        <v>299</v>
       </c>
       <c r="F3">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -21908,16 +21903,16 @@
         <v>400000000</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>66</v>
+        <v>299</v>
       </c>
       <c r="F4">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -21928,13 +21923,13 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>67</v>
+        <v>300</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -21948,16 +21943,16 @@
         <v>3600000</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>67</v>
+        <v>300</v>
       </c>
       <c r="F6">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -21968,16 +21963,16 @@
         <v>400000000</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>67</v>
+        <v>300</v>
       </c>
       <c r="F7">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -21988,13 +21983,13 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>68</v>
+        <v>301</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -22008,16 +22003,16 @@
         <v>3600000</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>68</v>
+        <v>301</v>
       </c>
       <c r="F9">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -22028,16 +22023,16 @@
         <v>400000000</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>68</v>
+        <v>301</v>
       </c>
       <c r="F10">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -22048,13 +22043,13 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>66</v>
+        <v>298</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -22068,16 +22063,16 @@
         <v>3600000</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>66</v>
+        <v>298</v>
       </c>
       <c r="F12">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -22088,16 +22083,16 @@
         <v>400000000</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>66</v>
+        <v>298</v>
       </c>
       <c r="F13">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -22108,13 +22103,13 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>67</v>
+        <v>302</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -22128,16 +22123,16 @@
         <v>3600000</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>67</v>
+        <v>302</v>
       </c>
       <c r="F15">
-        <v>-50000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -22148,257 +22143,29 @@
         <v>400000000</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>67</v>
+        <v>302</v>
       </c>
       <c r="F16">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17">
         <v>0</v>
       </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17">
-        <v>50</v>
-      </c>
-      <c r="E17">
-        <v>68</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-      <c r="D18">
-        <v>50</v>
-      </c>
-      <c r="E18">
-        <v>68</v>
-      </c>
-      <c r="F18">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19">
-        <v>400000000</v>
-      </c>
-      <c r="C19">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>50</v>
-      </c>
-      <c r="E19">
-        <v>68</v>
-      </c>
-      <c r="F19">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>7</v>
-      </c>
-      <c r="D20">
-        <v>51</v>
-      </c>
-      <c r="E20">
-        <v>66</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>336</v>
-      </c>
-      <c r="B21" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C21">
-        <v>7</v>
-      </c>
-      <c r="D21">
-        <v>51</v>
-      </c>
-      <c r="E21">
-        <v>66</v>
-      </c>
-      <c r="F21">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>336</v>
-      </c>
-      <c r="B22">
-        <v>400000000</v>
-      </c>
-      <c r="C22">
-        <v>7</v>
-      </c>
-      <c r="D22">
-        <v>51</v>
-      </c>
-      <c r="E22">
-        <v>66</v>
-      </c>
-      <c r="F22">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>337</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>7</v>
-      </c>
-      <c r="D23">
-        <v>51</v>
-      </c>
-      <c r="E23">
-        <v>67</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>337</v>
-      </c>
-      <c r="B24" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C24">
-        <v>7</v>
-      </c>
-      <c r="D24">
-        <v>51</v>
-      </c>
-      <c r="E24">
-        <v>67</v>
-      </c>
-      <c r="F24">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>337</v>
-      </c>
-      <c r="B25">
-        <v>400000000</v>
-      </c>
-      <c r="C25">
-        <v>7</v>
-      </c>
-      <c r="D25">
-        <v>51</v>
-      </c>
-      <c r="E25">
-        <v>67</v>
-      </c>
-      <c r="F25">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>338</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>7</v>
-      </c>
-      <c r="D26">
-        <v>51</v>
-      </c>
-      <c r="E26">
-        <v>68</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>338</v>
-      </c>
-      <c r="B27" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C27">
-        <v>7</v>
-      </c>
-      <c r="D27">
-        <v>51</v>
-      </c>
-      <c r="E27">
-        <v>68</v>
-      </c>
-      <c r="F27">
-        <v>-50000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B28">
-        <v>400000000</v>
-      </c>
-      <c r="C28">
-        <v>7</v>
-      </c>
-      <c r="D28">
-        <v>51</v>
-      </c>
-      <c r="E28">
-        <v>68</v>
-      </c>
-      <c r="F28">
-        <v>-50000</v>
-      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="6"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="6"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="6"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22407,7 +22174,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -22604,138 +22371,6 @@
         <v>-20</v>
       </c>
       <c r="J6">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <f t="shared" ref="C7:C10" si="0">D7/2</f>
-        <v>-1</v>
-      </c>
-      <c r="D7">
-        <v>-2</v>
-      </c>
-      <c r="E7">
-        <v>-4</v>
-      </c>
-      <c r="F7">
-        <v>-6</v>
-      </c>
-      <c r="G7">
-        <v>-8</v>
-      </c>
-      <c r="H7">
-        <v>-10</v>
-      </c>
-      <c r="I7">
-        <v>-20</v>
-      </c>
-      <c r="J7">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="D8">
-        <v>-2</v>
-      </c>
-      <c r="E8">
-        <v>-4</v>
-      </c>
-      <c r="F8">
-        <v>-6</v>
-      </c>
-      <c r="G8">
-        <v>-8</v>
-      </c>
-      <c r="H8">
-        <v>-10</v>
-      </c>
-      <c r="I8">
-        <v>-20</v>
-      </c>
-      <c r="J8">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>337</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="D9">
-        <v>-2</v>
-      </c>
-      <c r="E9">
-        <v>-4</v>
-      </c>
-      <c r="F9">
-        <v>-6</v>
-      </c>
-      <c r="G9">
-        <v>-8</v>
-      </c>
-      <c r="H9">
-        <v>-10</v>
-      </c>
-      <c r="I9">
-        <v>-20</v>
-      </c>
-      <c r="J9">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>338</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="D10">
-        <v>-2</v>
-      </c>
-      <c r="E10">
-        <v>-4</v>
-      </c>
-      <c r="F10">
-        <v>-6</v>
-      </c>
-      <c r="G10">
-        <v>-8</v>
-      </c>
-      <c r="H10">
-        <v>-10</v>
-      </c>
-      <c r="I10">
-        <v>-20</v>
-      </c>
-      <c r="J10">
         <v>-30</v>
       </c>
     </row>
@@ -22747,7 +22382,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -23310,425 +22945,17 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>-1</v>
-      </c>
-      <c r="E18">
-        <v>-2</v>
-      </c>
-      <c r="F18">
-        <v>-4</v>
-      </c>
-      <c r="G18">
-        <v>-6</v>
-      </c>
-      <c r="H18">
-        <v>-8</v>
-      </c>
-      <c r="I18">
-        <v>-10</v>
-      </c>
-      <c r="J18">
-        <v>-20</v>
-      </c>
-      <c r="K18">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19">
-        <v>400000000</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>-1</v>
-      </c>
-      <c r="E19">
-        <v>-2</v>
-      </c>
-      <c r="F19">
-        <v>-4</v>
-      </c>
-      <c r="G19">
-        <v>-6</v>
-      </c>
-      <c r="H19">
-        <v>-8</v>
-      </c>
-      <c r="I19">
-        <v>-10</v>
-      </c>
-      <c r="J19">
-        <v>-20</v>
-      </c>
-      <c r="K19">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>336</v>
-      </c>
-      <c r="B21" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>-1</v>
-      </c>
-      <c r="E21">
-        <v>-2</v>
-      </c>
-      <c r="F21">
-        <v>-4</v>
-      </c>
-      <c r="G21">
-        <v>-6</v>
-      </c>
-      <c r="H21">
-        <v>-8</v>
-      </c>
-      <c r="I21">
-        <v>-10</v>
-      </c>
-      <c r="J21">
-        <v>-20</v>
-      </c>
-      <c r="K21">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>336</v>
-      </c>
-      <c r="B22">
-        <v>400000000</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>-1</v>
-      </c>
-      <c r="E22">
-        <v>-2</v>
-      </c>
-      <c r="F22">
-        <v>-4</v>
-      </c>
-      <c r="G22">
-        <v>-6</v>
-      </c>
-      <c r="H22">
-        <v>-8</v>
-      </c>
-      <c r="I22">
-        <v>-10</v>
-      </c>
-      <c r="J22">
-        <v>-20</v>
-      </c>
-      <c r="K22">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>337</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>337</v>
-      </c>
-      <c r="B24" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>-1</v>
-      </c>
-      <c r="E24">
-        <v>-2</v>
-      </c>
-      <c r="F24">
-        <v>-4</v>
-      </c>
-      <c r="G24">
-        <v>-6</v>
-      </c>
-      <c r="H24">
-        <v>-8</v>
-      </c>
-      <c r="I24">
-        <v>-10</v>
-      </c>
-      <c r="J24">
-        <v>-20</v>
-      </c>
-      <c r="K24">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>337</v>
-      </c>
-      <c r="B25">
-        <v>400000000</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>-1</v>
-      </c>
-      <c r="E25">
-        <v>-2</v>
-      </c>
-      <c r="F25">
-        <v>-4</v>
-      </c>
-      <c r="G25">
-        <v>-6</v>
-      </c>
-      <c r="H25">
-        <v>-8</v>
-      </c>
-      <c r="I25">
-        <v>-10</v>
-      </c>
-      <c r="J25">
-        <v>-20</v>
-      </c>
-      <c r="K25">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>338</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>338</v>
-      </c>
-      <c r="B27" s="6">
-        <v>3600000</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>-1</v>
-      </c>
-      <c r="E27">
-        <v>-2</v>
-      </c>
-      <c r="F27">
-        <v>-4</v>
-      </c>
-      <c r="G27">
-        <v>-6</v>
-      </c>
-      <c r="H27">
-        <v>-8</v>
-      </c>
-      <c r="I27">
-        <v>-10</v>
-      </c>
-      <c r="J27">
-        <v>-20</v>
-      </c>
-      <c r="K27">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>338</v>
-      </c>
-      <c r="B28">
-        <v>400000000</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>-1</v>
-      </c>
-      <c r="E28">
-        <v>-2</v>
-      </c>
-      <c r="F28">
-        <v>-4</v>
-      </c>
-      <c r="G28">
-        <v>-6</v>
-      </c>
-      <c r="H28">
-        <v>-8</v>
-      </c>
-      <c r="I28">
-        <v>-10</v>
-      </c>
-      <c r="J28">
-        <v>-20</v>
-      </c>
-      <c r="K28">
-        <v>-30</v>
-      </c>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="6"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="6"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="6"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8003329C-1995-40ED-BA0D-098451C1DA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018E0D94-7410-4978-BC62-6014EF51136D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4178" windowWidth="21600" windowHeight="11422" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -23074,7 +23074,7 @@
         <v>71</v>
       </c>
       <c r="B17" s="1">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C17">
         <v>9.0000000000000002E-6</v>
@@ -23100,7 +23100,7 @@
         <v>72</v>
       </c>
       <c r="B18" s="1">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C18">
         <v>9.0000000000000002E-6</v>
@@ -23126,7 +23126,7 @@
         <v>73</v>
       </c>
       <c r="B19" s="1">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C19">
         <v>9.0000000000000002E-6</v>
@@ -23152,7 +23152,7 @@
         <v>74</v>
       </c>
       <c r="B20" s="1">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C20">
         <v>9.0000000000000002E-6</v>
@@ -23178,7 +23178,7 @@
         <v>75</v>
       </c>
       <c r="B21" s="1">
-        <v>1E-4</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="C21">
         <v>9.0000000000000002E-6</v>
@@ -28066,7 +28066,7 @@
       <c r="E2">
         <v>400</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="4">
         <v>0</v>
       </c>
     </row>
@@ -28087,7 +28087,7 @@
         <v>400</v>
       </c>
       <c r="F3" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -28107,7 +28107,7 @@
         <v>400</v>
       </c>
       <c r="F4" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -28147,7 +28147,7 @@
         <v>399</v>
       </c>
       <c r="F6" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -28167,7 +28167,7 @@
         <v>399</v>
       </c>
       <c r="F7" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -28207,7 +28207,7 @@
         <v>401</v>
       </c>
       <c r="F9" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -28227,7 +28227,7 @@
         <v>401</v>
       </c>
       <c r="F10" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -28267,7 +28267,7 @@
         <v>402</v>
       </c>
       <c r="F12" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -28287,7 +28287,7 @@
         <v>402</v>
       </c>
       <c r="F13" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -28327,7 +28327,7 @@
         <v>398</v>
       </c>
       <c r="F15" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -28347,7 +28347,7 @@
         <v>398</v>
       </c>
       <c r="F16" s="4">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05EA8D0-995C-4015-A8D7-B23A07312039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566D8907-7F27-48FB-83A0-CB2391BF6ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="11483" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14168" yWindow="2107" windowWidth="21599" windowHeight="11423" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="1191">
   <si>
     <t>nlay</t>
   </si>
@@ -3616,21 +3616,6 @@
   </si>
   <si>
     <t>kv_1E-08_kh_1E-03</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-07</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-06</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-05</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-04</t>
-  </si>
-  <si>
-    <t>kv_1E-06_kh_1E-03</t>
   </si>
   <si>
     <t>Run03</t>
@@ -4432,12 +4417,8 @@
       <c r="K1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1124</v>
-      </c>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
@@ -4473,12 +4454,8 @@
       <c r="K2" s="4">
         <v>0</v>
       </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
@@ -4491,35 +4468,31 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E3" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F3" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G3" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H3" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I3" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J3" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K3" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L3" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M3" s="4">
         <v>-600000</v>
       </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
@@ -4532,35 +4505,31 @@
         <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E4" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F4" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G4" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H4" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I4" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J4" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K4" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L4" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M4" s="4">
         <v>-600000</v>
       </c>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
@@ -4596,12 +4565,8 @@
       <c r="K5" s="4">
         <v>0</v>
       </c>
-      <c r="L5" s="4">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4">
-        <v>0</v>
-      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
@@ -4614,35 +4579,31 @@
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E6" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F6" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G6" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H6" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I6" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J6" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K6" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L6" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M6" s="4">
         <v>-600000</v>
       </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
@@ -4655,35 +4616,31 @@
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E7" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F7" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G7" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H7" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I7" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J7" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K7" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L7" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M7" s="4">
         <v>-600000</v>
       </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
@@ -4719,12 +4676,8 @@
       <c r="K8" s="4">
         <v>0</v>
       </c>
-      <c r="L8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <v>0</v>
-      </c>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
@@ -4737,35 +4690,31 @@
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E9" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F9" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G9" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H9" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I9" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J9" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K9" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L9" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M9" s="4">
         <v>-600000</v>
       </c>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
@@ -4778,35 +4727,31 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E10" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F10" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G10" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H10" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I10" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J10" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K10" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L10" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M10" s="4">
         <v>-600000</v>
       </c>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
@@ -4842,12 +4787,8 @@
       <c r="K11" s="4">
         <v>0</v>
       </c>
-      <c r="L11" s="4">
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
@@ -4860,35 +4801,31 @@
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E12" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F12" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G12" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H12" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I12" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J12" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K12" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L12" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M12" s="4">
         <v>-600000</v>
       </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
@@ -4901,35 +4838,31 @@
         <v>0</v>
       </c>
       <c r="D13" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E13" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F13" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G13" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H13" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I13" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J13" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K13" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L13" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M13" s="4">
         <v>-600000</v>
       </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
@@ -4965,12 +4898,8 @@
       <c r="K14" s="4">
         <v>0</v>
       </c>
-      <c r="L14" s="4">
-        <v>0</v>
-      </c>
-      <c r="M14" s="4">
-        <v>0</v>
-      </c>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
@@ -4983,35 +4912,31 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E15" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F15" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G15" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H15" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I15" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J15" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K15" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L15" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M15" s="4">
         <v>-600000</v>
       </c>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
@@ -5024,35 +4949,31 @@
         <v>0</v>
       </c>
       <c r="D16" s="4">
-        <v>-10</v>
+        <v>-100</v>
       </c>
       <c r="E16" s="4">
-        <v>-50</v>
+        <v>-200</v>
       </c>
       <c r="F16" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="G16" s="4">
-        <v>-200</v>
+        <v>-2000</v>
       </c>
       <c r="H16" s="4">
-        <v>-1000</v>
+        <v>-20000</v>
       </c>
       <c r="I16" s="4">
-        <v>-2000</v>
+        <v>-100000</v>
       </c>
       <c r="J16" s="4">
-        <v>-20000</v>
+        <v>-200000</v>
       </c>
       <c r="K16" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="L16" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="M16" s="4">
         <v>-600000</v>
       </c>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
@@ -5297,63 +5218,76 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:AO11"/>
+  <dimension ref="A1:AO41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="21" width="17.06640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1153</v>
+        <v>1180</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1154</v>
+        <v>1181</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1155</v>
+        <v>1182</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1156</v>
+        <v>1183</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>1176</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>1177</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>1178</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1179</v>
+        <v>1184</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>1166</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>1167</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>1158</v>
+        <v>1185</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>1159</v>
+        <v>1186</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>1160</v>
+        <v>1187</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>1161</v>
+        <v>1188</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>1162</v>
-      </c>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
+        <v>1189</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>1169</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>1171</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>1172</v>
+      </c>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
@@ -5394,19 +5328,19 @@
       <c r="F2" s="1">
         <v>86.4</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="20">
         <v>8.64</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="20">
         <v>86.4</v>
       </c>
       <c r="L2" s="1">
@@ -5424,11 +5358,21 @@
       <c r="P2" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="Q2" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R2" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S2" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="T2" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="U2" s="20">
+        <v>86.4</v>
+      </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -5455,55 +5399,65 @@
         <v>54</v>
       </c>
       <c r="B3" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="C3" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="D3" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="E3" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="F3" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="H3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J3" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K3" s="15">
-        <v>8.6400000000000006E-8</v>
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="G3" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="H3" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="I3" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="J3" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="K3" s="21">
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="L3" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="M3" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="N3" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="O3" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="P3" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="Q3" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R3" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="S3" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="T3" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="U3" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -5544,19 +5498,19 @@
       <c r="F4" s="1">
         <v>86.4</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="20">
         <v>8.64</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="20">
         <v>86.4</v>
       </c>
       <c r="L4" s="1">
@@ -5574,11 +5528,21 @@
       <c r="P4" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
+      <c r="Q4" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R4" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S4" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="T4" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="U4" s="20">
+        <v>86.4</v>
+      </c>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -5605,55 +5569,65 @@
         <v>58</v>
       </c>
       <c r="B5" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="C5" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="D5" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="E5" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="F5" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="H5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J5" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K5" s="15">
-        <v>8.6400000000000006E-8</v>
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="G5" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="H5" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="I5" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="J5" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="K5" s="21">
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="L5" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="M5" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="N5" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="O5" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="P5" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="Q5" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R5" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="S5" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="T5" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="U5" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
@@ -5694,19 +5668,19 @@
       <c r="F6" s="1">
         <v>86.4</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="20">
         <v>8.64</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="20">
         <v>86.4</v>
       </c>
       <c r="L6" s="1">
@@ -5724,11 +5698,21 @@
       <c r="P6" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
+      <c r="Q6" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R6" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S6" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="T6" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="U6" s="20">
+        <v>86.4</v>
+      </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -5769,19 +5753,19 @@
       <c r="F7" s="1">
         <v>86.4</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="20">
         <v>8.64</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="20">
         <v>86.4</v>
       </c>
       <c r="L7" s="1">
@@ -5799,11 +5783,21 @@
       <c r="P7" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
+      <c r="Q7" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R7" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S7" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="T7" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="U7" s="20">
+        <v>86.4</v>
+      </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
@@ -5830,55 +5824,65 @@
         <v>63</v>
       </c>
       <c r="B8" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="C8" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="D8" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="E8" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="F8" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="H8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J8" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K8" s="15">
-        <v>8.6400000000000006E-8</v>
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="G8" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="H8" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="I8" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="J8" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="K8" s="21">
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="L8" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="M8" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="N8" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="O8" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="P8" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="13"/>
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="Q8" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R8" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="S8" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="T8" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="U8" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
@@ -5919,19 +5923,19 @@
       <c r="F9" s="1">
         <v>86.4</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="20">
         <v>8.64</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="20">
         <v>86.4</v>
       </c>
       <c r="L9" s="1">
@@ -5949,11 +5953,21 @@
       <c r="P9" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
+      <c r="Q9" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R9" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S9" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="T9" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="U9" s="20">
+        <v>86.4</v>
+      </c>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -5980,55 +5994,65 @@
         <v>65</v>
       </c>
       <c r="B10" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="C10" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="D10" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="E10" s="13">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6400000000000003E-6</v>
       </c>
       <c r="F10" s="13">
-        <v>8.6399999999999999E-9</v>
-      </c>
-      <c r="G10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="H10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="I10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="J10" s="15">
-        <v>8.6400000000000006E-8</v>
-      </c>
-      <c r="K10" s="15">
-        <v>8.6400000000000006E-8</v>
+        <v>8.6400000000000003E-6</v>
+      </c>
+      <c r="G10" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="H10" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="I10" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="J10" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="K10" s="21">
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="L10" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="M10" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="N10" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="O10" s="13">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6399999999999997E-4</v>
       </c>
       <c r="P10" s="13">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
-      <c r="U10" s="13"/>
+        <v>8.6399999999999997E-4</v>
+      </c>
+      <c r="Q10" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R10" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="S10" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="T10" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="U10" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
@@ -6069,19 +6093,19 @@
       <c r="F11" s="1">
         <v>86.4</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="20">
         <v>8.64</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="20">
         <v>86.4</v>
       </c>
       <c r="L11" s="1">
@@ -6099,11 +6123,21 @@
       <c r="P11" s="1">
         <v>86.4</v>
       </c>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
+      <c r="Q11" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="R11" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="S11" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="T11" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="U11" s="20">
+        <v>86.4</v>
+      </c>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
@@ -6125,6 +6159,481 @@
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
     </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="13"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.45">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6134,7 +6643,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:BO364"/>
+  <dimension ref="A1:BZ364"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.46484375" style="4" bestFit="1" customWidth="1"/>
@@ -12052,7 +12561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>200</v>
       </c>
@@ -12145,7 +12654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>201</v>
       </c>
@@ -12250,7 +12759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>202</v>
       </c>
@@ -12356,7 +12865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>203</v>
       </c>
@@ -12462,7 +12971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>204</v>
       </c>
@@ -12535,7 +13044,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="86" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>205</v>
       </c>
@@ -12608,7 +13117,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="87" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>206</v>
       </c>
@@ -12681,7 +13190,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="88" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>207</v>
       </c>
@@ -12735,7 +13244,7 @@
         <v>6.7755654381398901E-4</v>
       </c>
     </row>
-    <row r="89" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>208</v>
       </c>
@@ -12788,11 +13297,11 @@
         <f t="shared" si="11"/>
         <v>9.4339543613295384E-4</v>
       </c>
-      <c r="BC89" t="s">
+      <c r="BN89" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="90" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -12848,47 +13357,47 @@
       <c r="AE90" t="s">
         <v>1173</v>
       </c>
-      <c r="BC90" s="4" t="s">
+      <c r="BN90" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="BD90" s="4" t="s">
+      <c r="BO90" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="BE90" s="4" t="s">
+      <c r="BP90" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="BF90" s="4" t="s">
+      <c r="BQ90" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="BG90" s="4" t="s">
+      <c r="BR90" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="BH90" s="4" t="s">
+      <c r="BS90" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="BI90" s="4" t="s">
+      <c r="BT90" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="BJ90" s="4" t="s">
+      <c r="BU90" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="BK90" s="4" t="s">
+      <c r="BV90" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="BL90" s="4" t="s">
+      <c r="BW90" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="BM90" s="4" t="s">
+      <c r="BX90" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="BN90" s="4" t="s">
+      <c r="BY90" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="BO90" s="4" t="s">
+      <c r="BZ90" s="4" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="91" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>210</v>
       </c>
@@ -13004,47 +13513,47 @@
       <c r="AY91" s="19" t="s">
         <v>1172</v>
       </c>
-      <c r="BC91" s="4" t="s">
+      <c r="BN91" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="BD91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM91" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN91" s="4">
-        <v>0</v>
       </c>
       <c r="BO91" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY91" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ91" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>211</v>
       </c>
@@ -13160,47 +13669,47 @@
       <c r="AY92" s="20">
         <v>86.4</v>
       </c>
-      <c r="BC92" s="4" t="s">
+      <c r="BN92" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD92" s="3">
+      <c r="BO92" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE92" s="4">
+      <c r="BP92" s="4">
         <v>0</v>
       </c>
-      <c r="BF92" s="4">
+      <c r="BQ92" s="4">
         <v>-100</v>
       </c>
-      <c r="BG92" s="4">
+      <c r="BR92" s="4">
         <v>-200</v>
       </c>
-      <c r="BH92" s="4">
+      <c r="BS92" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI92" s="4">
+      <c r="BT92" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ92" s="4">
+      <c r="BU92" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK92" s="4">
+      <c r="BV92" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL92" s="4">
+      <c r="BW92" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM92" s="4">
+      <c r="BX92" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN92" s="4">
+      <c r="BY92" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO92" s="4">
+      <c r="BZ92" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="93" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>212</v>
       </c>
@@ -13316,47 +13825,47 @@
       <c r="AY93" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="BC93" s="4" t="s">
+      <c r="BN93" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD93" s="3">
+      <c r="BO93" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE93" s="4">
+      <c r="BP93" s="4">
         <v>0</v>
       </c>
-      <c r="BF93" s="4">
+      <c r="BQ93" s="4">
         <v>-100</v>
       </c>
-      <c r="BG93" s="4">
+      <c r="BR93" s="4">
         <v>-200</v>
       </c>
-      <c r="BH93" s="4">
+      <c r="BS93" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI93" s="4">
+      <c r="BT93" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ93" s="4">
+      <c r="BU93" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK93" s="4">
+      <c r="BV93" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL93" s="4">
+      <c r="BW93" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM93" s="4">
+      <c r="BX93" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN93" s="4">
+      <c r="BY93" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO93" s="4">
+      <c r="BZ93" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="94" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>213</v>
       </c>
@@ -13472,47 +13981,47 @@
       <c r="AY94" s="20">
         <v>86.4</v>
       </c>
-      <c r="BC94" s="4" t="s">
+      <c r="BN94" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="BD94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM94" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN94" s="4">
-        <v>0</v>
       </c>
       <c r="BO94" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY94" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ94" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>214</v>
       </c>
@@ -13628,47 +14137,47 @@
       <c r="AY95" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="BC95" s="4" t="s">
+      <c r="BN95" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD95" s="3">
+      <c r="BO95" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE95" s="4">
+      <c r="BP95" s="4">
         <v>0</v>
       </c>
-      <c r="BF95" s="4">
+      <c r="BQ95" s="4">
         <v>-100</v>
       </c>
-      <c r="BG95" s="4">
+      <c r="BR95" s="4">
         <v>-200</v>
       </c>
-      <c r="BH95" s="4">
+      <c r="BS95" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI95" s="4">
+      <c r="BT95" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ95" s="4">
+      <c r="BU95" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK95" s="4">
+      <c r="BV95" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL95" s="4">
+      <c r="BW95" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM95" s="4">
+      <c r="BX95" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN95" s="4">
+      <c r="BY95" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO95" s="4">
+      <c r="BZ95" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="96" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>215</v>
       </c>
@@ -13784,47 +14293,47 @@
       <c r="AY96" s="20">
         <v>86.4</v>
       </c>
-      <c r="BC96" s="4" t="s">
+      <c r="BN96" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD96" s="3">
+      <c r="BO96" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE96" s="4">
+      <c r="BP96" s="4">
         <v>0</v>
       </c>
-      <c r="BF96" s="4">
+      <c r="BQ96" s="4">
         <v>-100</v>
       </c>
-      <c r="BG96" s="4">
+      <c r="BR96" s="4">
         <v>-200</v>
       </c>
-      <c r="BH96" s="4">
+      <c r="BS96" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI96" s="4">
+      <c r="BT96" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ96" s="4">
+      <c r="BU96" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK96" s="4">
+      <c r="BV96" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL96" s="4">
+      <c r="BW96" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM96" s="4">
+      <c r="BX96" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN96" s="4">
+      <c r="BY96" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO96" s="4">
+      <c r="BZ96" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="97" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>216</v>
       </c>
@@ -13940,47 +14449,47 @@
       <c r="AY97" s="20">
         <v>86.4</v>
       </c>
-      <c r="BC97" s="4" t="s">
+      <c r="BN97" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="BD97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM97" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN97" s="4">
-        <v>0</v>
       </c>
       <c r="BO97" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY97" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ97" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>217</v>
       </c>
@@ -14096,47 +14605,47 @@
       <c r="AY98" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="BC98" s="4" t="s">
+      <c r="BN98" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD98" s="3">
+      <c r="BO98" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE98" s="4">
+      <c r="BP98" s="4">
         <v>0</v>
       </c>
-      <c r="BF98" s="4">
+      <c r="BQ98" s="4">
         <v>-100</v>
       </c>
-      <c r="BG98" s="4">
+      <c r="BR98" s="4">
         <v>-200</v>
       </c>
-      <c r="BH98" s="4">
+      <c r="BS98" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI98" s="4">
+      <c r="BT98" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ98" s="4">
+      <c r="BU98" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK98" s="4">
+      <c r="BV98" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL98" s="4">
+      <c r="BW98" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM98" s="4">
+      <c r="BX98" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN98" s="4">
+      <c r="BY98" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO98" s="4">
+      <c r="BZ98" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="99" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>218</v>
       </c>
@@ -14252,47 +14761,47 @@
       <c r="AY99" s="20">
         <v>86.4</v>
       </c>
-      <c r="BC99" s="4" t="s">
+      <c r="BN99" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD99" s="3">
+      <c r="BO99" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE99" s="4">
+      <c r="BP99" s="4">
         <v>0</v>
       </c>
-      <c r="BF99" s="4">
+      <c r="BQ99" s="4">
         <v>-100</v>
       </c>
-      <c r="BG99" s="4">
+      <c r="BR99" s="4">
         <v>-200</v>
       </c>
-      <c r="BH99" s="4">
+      <c r="BS99" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI99" s="4">
+      <c r="BT99" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ99" s="4">
+      <c r="BU99" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK99" s="4">
+      <c r="BV99" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL99" s="4">
+      <c r="BW99" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM99" s="4">
+      <c r="BX99" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN99" s="4">
+      <c r="BY99" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO99" s="4">
+      <c r="BZ99" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="100" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>219</v>
       </c>
@@ -14408,47 +14917,47 @@
       <c r="AY100" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="BC100" s="4" t="s">
+      <c r="BN100" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="BD100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM100" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN100" s="4">
-        <v>0</v>
       </c>
       <c r="BO100" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY100" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ100" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>220</v>
       </c>
@@ -14564,47 +15073,47 @@
       <c r="AY101" s="20">
         <v>86.4</v>
       </c>
-      <c r="BC101" s="4" t="s">
+      <c r="BN101" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD101" s="3">
+      <c r="BO101" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE101" s="4">
+      <c r="BP101" s="4">
         <v>0</v>
       </c>
-      <c r="BF101" s="4">
+      <c r="BQ101" s="4">
         <v>-100</v>
       </c>
-      <c r="BG101" s="4">
+      <c r="BR101" s="4">
         <v>-200</v>
       </c>
-      <c r="BH101" s="4">
+      <c r="BS101" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI101" s="4">
+      <c r="BT101" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ101" s="4">
+      <c r="BU101" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK101" s="4">
+      <c r="BV101" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL101" s="4">
+      <c r="BW101" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM101" s="4">
+      <c r="BX101" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN101" s="4">
+      <c r="BY101" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO101" s="4">
+      <c r="BZ101" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="102" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -14657,47 +15166,47 @@
         <f t="shared" si="15"/>
         <v>4.7180228576033662E-4</v>
       </c>
-      <c r="BC102" s="4" t="s">
+      <c r="BN102" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD102" s="3">
+      <c r="BO102" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE102" s="4">
+      <c r="BP102" s="4">
         <v>0</v>
       </c>
-      <c r="BF102" s="4">
+      <c r="BQ102" s="4">
         <v>-100</v>
       </c>
-      <c r="BG102" s="4">
+      <c r="BR102" s="4">
         <v>-200</v>
       </c>
-      <c r="BH102" s="4">
+      <c r="BS102" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI102" s="4">
+      <c r="BT102" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ102" s="4">
+      <c r="BU102" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK102" s="4">
+      <c r="BV102" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL102" s="4">
+      <c r="BW102" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM102" s="4">
+      <c r="BX102" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN102" s="4">
+      <c r="BY102" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO102" s="4">
+      <c r="BZ102" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="103" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>222</v>
       </c>
@@ -14753,47 +15262,47 @@
       <c r="AE103" s="14" t="s">
         <v>1174</v>
       </c>
-      <c r="BC103" s="4" t="s">
+      <c r="BN103" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="BD103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM103" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN103" s="4">
-        <v>0</v>
       </c>
       <c r="BO103" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY103" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ103" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>223</v>
       </c>
@@ -14894,47 +15403,47 @@
       <c r="AT104" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="BC104" s="4" t="s">
+      <c r="BN104" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD104" s="3">
+      <c r="BO104" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE104" s="4">
+      <c r="BP104" s="4">
         <v>0</v>
       </c>
-      <c r="BF104" s="4">
+      <c r="BQ104" s="4">
         <v>-100</v>
       </c>
-      <c r="BG104" s="4">
+      <c r="BR104" s="4">
         <v>-200</v>
       </c>
-      <c r="BH104" s="4">
+      <c r="BS104" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI104" s="4">
+      <c r="BT104" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ104" s="4">
+      <c r="BU104" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK104" s="4">
+      <c r="BV104" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL104" s="4">
+      <c r="BW104" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM104" s="4">
+      <c r="BX104" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN104" s="4">
+      <c r="BY104" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO104" s="4">
+      <c r="BZ104" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="105" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>224</v>
       </c>
@@ -15035,47 +15544,47 @@
       <c r="AT105" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC105" s="4" t="s">
+      <c r="BN105" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD105" s="3">
+      <c r="BO105" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE105" s="4">
+      <c r="BP105" s="4">
         <v>0</v>
       </c>
-      <c r="BF105" s="4">
+      <c r="BQ105" s="4">
         <v>-100</v>
       </c>
-      <c r="BG105" s="4">
+      <c r="BR105" s="4">
         <v>-200</v>
       </c>
-      <c r="BH105" s="4">
+      <c r="BS105" s="4">
         <v>-1000</v>
       </c>
-      <c r="BI105" s="4">
+      <c r="BT105" s="4">
         <v>-2000</v>
       </c>
-      <c r="BJ105" s="4">
+      <c r="BU105" s="4">
         <v>-20000</v>
       </c>
-      <c r="BK105" s="4">
+      <c r="BV105" s="4">
         <v>-100000</v>
       </c>
-      <c r="BL105" s="4">
+      <c r="BW105" s="4">
         <v>-200000</v>
       </c>
-      <c r="BM105" s="4">
+      <c r="BX105" s="4">
         <v>-600000</v>
       </c>
-      <c r="BN105" s="4">
+      <c r="BY105" s="4">
         <v>-1200000</v>
       </c>
-      <c r="BO105" s="4">
+      <c r="BZ105" s="4">
         <v>-2400000</v>
       </c>
     </row>
-    <row r="106" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>225</v>
       </c>
@@ -15177,7 +15686,7 @@
         <v>8.6400000000000001E-7</v>
       </c>
     </row>
-    <row r="107" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -15279,7 +15788,7 @@
         <v>86.4</v>
       </c>
     </row>
-    <row r="108" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>227</v>
       </c>
@@ -15380,11 +15889,11 @@
       <c r="AT108" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="BC108" t="s">
+      <c r="BN108" t="s">
         <v>1174</v>
       </c>
     </row>
-    <row r="109" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>228</v>
       </c>
@@ -15485,47 +15994,47 @@
       <c r="AT109" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC109" s="4" t="s">
+      <c r="BN109" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="BD109" s="4" t="s">
+      <c r="BO109" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="BE109" s="4" t="s">
+      <c r="BP109" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="BF109" s="4" t="s">
+      <c r="BQ109" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="BG109" s="4" t="s">
+      <c r="BR109" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="BH109" s="4" t="s">
+      <c r="BS109" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="BI109" s="4" t="s">
+      <c r="BT109" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="BJ109" s="4" t="s">
+      <c r="BU109" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="BK109" s="4" t="s">
+      <c r="BV109" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="BL109" s="4" t="s">
+      <c r="BW109" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="BM109" s="4" t="s">
+      <c r="BX109" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="BN109" s="4" t="s">
+      <c r="BY109" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="BO109" s="4" t="s">
+      <c r="BZ109" s="4" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="110" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>229</v>
       </c>
@@ -15626,47 +16135,47 @@
       <c r="AT110" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC110" s="4" t="s">
+      <c r="BN110" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="BD110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM110" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN110" s="4">
-        <v>0</v>
       </c>
       <c r="BO110" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY110" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ110" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>230</v>
       </c>
@@ -15767,47 +16276,47 @@
       <c r="AT111" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="BC111" s="4" t="s">
+      <c r="BN111" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD111" s="3">
+      <c r="BO111" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE111" s="4">
+      <c r="BP111" s="4">
         <v>0</v>
       </c>
-      <c r="BF111" s="4">
+      <c r="BQ111" s="4">
         <v>-10</v>
       </c>
-      <c r="BG111" s="4">
+      <c r="BR111" s="4">
         <v>-50</v>
       </c>
-      <c r="BH111" s="4">
+      <c r="BS111" s="4">
         <v>-100</v>
       </c>
-      <c r="BI111" s="4">
+      <c r="BT111" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ111" s="4">
+      <c r="BU111" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK111" s="4">
+      <c r="BV111" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL111" s="4">
+      <c r="BW111" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM111" s="4">
+      <c r="BX111" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN111" s="4">
+      <c r="BY111" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO111" s="4">
+      <c r="BZ111" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="112" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>231</v>
       </c>
@@ -15908,47 +16417,47 @@
       <c r="AT112" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC112" s="4" t="s">
+      <c r="BN112" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="BD112" s="3">
+      <c r="BO112" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE112" s="4">
+      <c r="BP112" s="4">
         <v>0</v>
       </c>
-      <c r="BF112" s="4">
+      <c r="BQ112" s="4">
         <v>-10</v>
       </c>
-      <c r="BG112" s="4">
+      <c r="BR112" s="4">
         <v>-50</v>
       </c>
-      <c r="BH112" s="4">
+      <c r="BS112" s="4">
         <v>-100</v>
       </c>
-      <c r="BI112" s="4">
+      <c r="BT112" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ112" s="4">
+      <c r="BU112" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK112" s="4">
+      <c r="BV112" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL112" s="4">
+      <c r="BW112" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM112" s="4">
+      <c r="BX112" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN112" s="4">
+      <c r="BY112" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO112" s="4">
+      <c r="BZ112" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="113" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>232</v>
       </c>
@@ -16049,47 +16558,47 @@
       <c r="AT113" s="13">
         <v>8.6400000000000001E-7</v>
       </c>
-      <c r="BC113" s="4" t="s">
+      <c r="BN113" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="BD113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM113" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN113" s="4">
-        <v>0</v>
       </c>
       <c r="BO113" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY113" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ113" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>233</v>
       </c>
@@ -16190,47 +16699,47 @@
       <c r="AT114" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC114" s="4" t="s">
+      <c r="BN114" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD114" s="3">
+      <c r="BO114" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE114" s="4">
+      <c r="BP114" s="4">
         <v>0</v>
       </c>
-      <c r="BF114" s="4">
+      <c r="BQ114" s="4">
         <v>-10</v>
       </c>
-      <c r="BG114" s="4">
+      <c r="BR114" s="4">
         <v>-50</v>
       </c>
-      <c r="BH114" s="4">
+      <c r="BS114" s="4">
         <v>-100</v>
       </c>
-      <c r="BI114" s="4">
+      <c r="BT114" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ114" s="4">
+      <c r="BU114" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK114" s="4">
+      <c r="BV114" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL114" s="4">
+      <c r="BW114" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM114" s="4">
+      <c r="BX114" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN114" s="4">
+      <c r="BY114" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO114" s="4">
+      <c r="BZ114" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="115" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>234</v>
       </c>
@@ -16283,47 +16792,47 @@
         <f t="shared" si="15"/>
         <v>5.5438130895789643E-4</v>
       </c>
-      <c r="BC115" s="4" t="s">
+      <c r="BN115" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="BD115" s="3">
+      <c r="BO115" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE115" s="4">
+      <c r="BP115" s="4">
         <v>0</v>
       </c>
-      <c r="BF115" s="4">
+      <c r="BQ115" s="4">
         <v>-10</v>
       </c>
-      <c r="BG115" s="4">
+      <c r="BR115" s="4">
         <v>-50</v>
       </c>
-      <c r="BH115" s="4">
+      <c r="BS115" s="4">
         <v>-100</v>
       </c>
-      <c r="BI115" s="4">
+      <c r="BT115" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ115" s="4">
+      <c r="BU115" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK115" s="4">
+      <c r="BV115" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL115" s="4">
+      <c r="BW115" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM115" s="4">
+      <c r="BX115" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN115" s="4">
+      <c r="BY115" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO115" s="4">
+      <c r="BZ115" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="116" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>235</v>
       </c>
@@ -16377,54 +16886,54 @@
         <v>9.0184342071178349E-4</v>
       </c>
       <c r="AE116" s="14" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
       <c r="AH116" s="4"/>
       <c r="AI116" s="4"/>
       <c r="AJ116" s="4"/>
-      <c r="BC116" s="4" t="s">
+      <c r="BN116" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="BD116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM116" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN116" s="4">
-        <v>0</v>
       </c>
       <c r="BO116" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY116" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ116" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>236</v>
       </c>
@@ -16495,77 +17004,97 @@
       <c r="AJ117" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="AK117" s="4" t="s">
+      <c r="AK117" s="19" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AL117" s="19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AM117" s="19" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AN117" s="19" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AO117" s="19" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AP117" s="4" t="s">
         <v>1185</v>
       </c>
-      <c r="AL117" s="4" t="s">
+      <c r="AQ117" s="4" t="s">
         <v>1186</v>
       </c>
-      <c r="AM117" s="4" t="s">
+      <c r="AR117" s="4" t="s">
         <v>1187</v>
       </c>
-      <c r="AN117" s="4" t="s">
+      <c r="AS117" s="4" t="s">
         <v>1188</v>
       </c>
-      <c r="AO117" s="4" t="s">
+      <c r="AT117" s="4" t="s">
         <v>1189</v>
       </c>
-      <c r="AP117" s="4" t="s">
-        <v>1190</v>
-      </c>
-      <c r="AQ117" s="4" t="s">
-        <v>1191</v>
-      </c>
-      <c r="AR117" s="4" t="s">
-        <v>1192</v>
-      </c>
-      <c r="AS117" s="4" t="s">
-        <v>1193</v>
-      </c>
-      <c r="AT117" s="4" t="s">
-        <v>1194</v>
-      </c>
-      <c r="BC117" s="4" t="s">
+      <c r="AU117" s="19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="AV117" s="19" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AW117" s="19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="AX117" s="19" t="s">
+        <v>1171</v>
+      </c>
+      <c r="AY117" s="19" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AZ117" s="4"/>
+      <c r="BA117" s="4"/>
+      <c r="BB117" s="4"/>
+      <c r="BC117" s="4"/>
+      <c r="BD117" s="4"/>
+      <c r="BN117" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD117" s="3">
+      <c r="BO117" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE117" s="4">
+      <c r="BP117" s="4">
         <v>0</v>
       </c>
-      <c r="BF117" s="4">
+      <c r="BQ117" s="4">
         <v>-10</v>
       </c>
-      <c r="BG117" s="4">
+      <c r="BR117" s="4">
         <v>-50</v>
       </c>
-      <c r="BH117" s="4">
+      <c r="BS117" s="4">
         <v>-100</v>
       </c>
-      <c r="BI117" s="4">
+      <c r="BT117" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ117" s="4">
+      <c r="BU117" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK117" s="4">
+      <c r="BV117" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL117" s="4">
+      <c r="BW117" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM117" s="4">
+      <c r="BX117" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN117" s="4">
+      <c r="BY117" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO117" s="4">
+      <c r="BZ117" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="118" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>237</v>
       </c>
@@ -16636,19 +17165,19 @@
       <c r="AJ118" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK118" s="1">
+      <c r="AK118" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL118" s="1">
+      <c r="AL118" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM118" s="1">
+      <c r="AM118" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN118" s="1">
+      <c r="AN118" s="20">
         <v>8.64</v>
       </c>
-      <c r="AO118" s="1">
+      <c r="AO118" s="20">
         <v>86.4</v>
       </c>
       <c r="AP118" s="1">
@@ -16666,47 +17195,67 @@
       <c r="AT118" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC118" s="4" t="s">
+      <c r="AU118" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV118" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW118" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX118" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY118" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AZ118" s="1"/>
+      <c r="BA118" s="1"/>
+      <c r="BB118" s="1"/>
+      <c r="BC118" s="1"/>
+      <c r="BD118" s="1"/>
+      <c r="BN118" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="BD118" s="3">
+      <c r="BO118" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE118" s="4">
+      <c r="BP118" s="4">
         <v>0</v>
       </c>
-      <c r="BF118" s="4">
+      <c r="BQ118" s="4">
         <v>-10</v>
       </c>
-      <c r="BG118" s="4">
+      <c r="BR118" s="4">
         <v>-50</v>
       </c>
-      <c r="BH118" s="4">
+      <c r="BS118" s="4">
         <v>-100</v>
       </c>
-      <c r="BI118" s="4">
+      <c r="BT118" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ118" s="4">
+      <c r="BU118" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK118" s="4">
+      <c r="BV118" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL118" s="4">
+      <c r="BW118" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM118" s="4">
+      <c r="BX118" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN118" s="4">
+      <c r="BY118" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO118" s="4">
+      <c r="BZ118" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="119" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>238</v>
       </c>
@@ -16777,77 +17326,97 @@
       <c r="AJ119" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK119" s="13">
+      <c r="AK119" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL119" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM119" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN119" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO119" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL119" s="13">
+      <c r="AQ119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM119" s="13">
+      <c r="AR119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN119" s="13">
+      <c r="AS119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO119" s="13">
+      <c r="AT119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT119" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="BC119" s="4" t="s">
+      <c r="AU119" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV119" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW119" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX119" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY119" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ119" s="13"/>
+      <c r="BA119" s="13"/>
+      <c r="BB119" s="13"/>
+      <c r="BC119" s="13"/>
+      <c r="BD119" s="13"/>
+      <c r="BN119" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="BD119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM119" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN119" s="4">
-        <v>0</v>
       </c>
       <c r="BO119" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY119" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ119" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>239</v>
       </c>
@@ -16918,19 +17487,19 @@
       <c r="AJ120" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK120" s="1">
+      <c r="AK120" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL120" s="1">
+      <c r="AL120" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM120" s="1">
+      <c r="AM120" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN120" s="1">
+      <c r="AN120" s="20">
         <v>8.64</v>
       </c>
-      <c r="AO120" s="1">
+      <c r="AO120" s="20">
         <v>86.4</v>
       </c>
       <c r="AP120" s="1">
@@ -16948,47 +17517,67 @@
       <c r="AT120" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC120" s="4" t="s">
+      <c r="AU120" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV120" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW120" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX120" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY120" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AZ120" s="1"/>
+      <c r="BA120" s="1"/>
+      <c r="BB120" s="1"/>
+      <c r="BC120" s="1"/>
+      <c r="BD120" s="1"/>
+      <c r="BN120" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD120" s="3">
+      <c r="BO120" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE120" s="4">
+      <c r="BP120" s="4">
         <v>0</v>
       </c>
-      <c r="BF120" s="4">
+      <c r="BQ120" s="4">
         <v>-10</v>
       </c>
-      <c r="BG120" s="4">
+      <c r="BR120" s="4">
         <v>-50</v>
       </c>
-      <c r="BH120" s="4">
+      <c r="BS120" s="4">
         <v>-100</v>
       </c>
-      <c r="BI120" s="4">
+      <c r="BT120" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ120" s="4">
+      <c r="BU120" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK120" s="4">
+      <c r="BV120" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL120" s="4">
+      <c r="BW120" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM120" s="4">
+      <c r="BX120" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN120" s="4">
+      <c r="BY120" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO120" s="4">
+      <c r="BZ120" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="121" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -17059,77 +17648,97 @@
       <c r="AJ121" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK121" s="13">
+      <c r="AK121" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL121" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM121" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN121" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO121" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL121" s="13">
+      <c r="AQ121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM121" s="13">
+      <c r="AR121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN121" s="13">
+      <c r="AS121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO121" s="13">
+      <c r="AT121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT121" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="BC121" s="4" t="s">
+      <c r="AU121" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV121" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW121" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX121" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY121" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ121" s="13"/>
+      <c r="BA121" s="13"/>
+      <c r="BB121" s="13"/>
+      <c r="BC121" s="13"/>
+      <c r="BD121" s="13"/>
+      <c r="BN121" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="BD121" s="3">
+      <c r="BO121" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE121" s="4">
+      <c r="BP121" s="4">
         <v>0</v>
       </c>
-      <c r="BF121" s="4">
+      <c r="BQ121" s="4">
         <v>-10</v>
       </c>
-      <c r="BG121" s="4">
+      <c r="BR121" s="4">
         <v>-50</v>
       </c>
-      <c r="BH121" s="4">
+      <c r="BS121" s="4">
         <v>-100</v>
       </c>
-      <c r="BI121" s="4">
+      <c r="BT121" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ121" s="4">
+      <c r="BU121" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK121" s="4">
+      <c r="BV121" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL121" s="4">
+      <c r="BW121" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM121" s="4">
+      <c r="BX121" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN121" s="4">
+      <c r="BY121" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO121" s="4">
+      <c r="BZ121" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="122" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>241</v>
       </c>
@@ -17200,19 +17809,19 @@
       <c r="AJ122" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK122" s="1">
+      <c r="AK122" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL122" s="1">
+      <c r="AL122" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM122" s="1">
+      <c r="AM122" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN122" s="1">
+      <c r="AN122" s="20">
         <v>8.64</v>
       </c>
-      <c r="AO122" s="1">
+      <c r="AO122" s="20">
         <v>86.4</v>
       </c>
       <c r="AP122" s="1">
@@ -17230,47 +17839,67 @@
       <c r="AT122" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC122" s="4" t="s">
+      <c r="AU122" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV122" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW122" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX122" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY122" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AZ122" s="1"/>
+      <c r="BA122" s="1"/>
+      <c r="BB122" s="1"/>
+      <c r="BC122" s="1"/>
+      <c r="BD122" s="1"/>
+      <c r="BN122" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="BD122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BE122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BF122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BG122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BH122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BI122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BJ122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BK122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BL122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BM122" s="4">
-        <v>0</v>
-      </c>
-      <c r="BN122" s="4">
-        <v>0</v>
       </c>
       <c r="BO122" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="BP122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BY122" s="4">
+        <v>0</v>
+      </c>
+      <c r="BZ122" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>242</v>
       </c>
@@ -17341,19 +17970,19 @@
       <c r="AJ123" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK123" s="1">
+      <c r="AK123" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL123" s="1">
+      <c r="AL123" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM123" s="1">
+      <c r="AM123" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN123" s="1">
+      <c r="AN123" s="20">
         <v>8.64</v>
       </c>
-      <c r="AO123" s="1">
+      <c r="AO123" s="20">
         <v>86.4</v>
       </c>
       <c r="AP123" s="1">
@@ -17371,47 +18000,67 @@
       <c r="AT123" s="1">
         <v>86.4</v>
       </c>
-      <c r="BC123" s="4" t="s">
+      <c r="AU123" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV123" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW123" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX123" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY123" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AZ123" s="1"/>
+      <c r="BA123" s="1"/>
+      <c r="BB123" s="1"/>
+      <c r="BC123" s="1"/>
+      <c r="BD123" s="1"/>
+      <c r="BN123" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD123" s="3">
+      <c r="BO123" s="3">
         <v>3600000</v>
       </c>
-      <c r="BE123" s="4">
+      <c r="BP123" s="4">
         <v>0</v>
       </c>
-      <c r="BF123" s="4">
+      <c r="BQ123" s="4">
         <v>-10</v>
       </c>
-      <c r="BG123" s="4">
+      <c r="BR123" s="4">
         <v>-50</v>
       </c>
-      <c r="BH123" s="4">
+      <c r="BS123" s="4">
         <v>-100</v>
       </c>
-      <c r="BI123" s="4">
+      <c r="BT123" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ123" s="4">
+      <c r="BU123" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK123" s="4">
+      <c r="BV123" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL123" s="4">
+      <c r="BW123" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM123" s="4">
+      <c r="BX123" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN123" s="4">
+      <c r="BY123" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO123" s="4">
+      <c r="BZ123" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="124" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>243</v>
       </c>
@@ -17482,77 +18131,97 @@
       <c r="AJ124" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK124" s="13">
+      <c r="AK124" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL124" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM124" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN124" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO124" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL124" s="13">
+      <c r="AQ124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM124" s="13">
+      <c r="AR124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN124" s="13">
+      <c r="AS124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO124" s="13">
+      <c r="AT124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT124" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="BC124" s="4" t="s">
+      <c r="AU124" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV124" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW124" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX124" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY124" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ124" s="13"/>
+      <c r="BA124" s="13"/>
+      <c r="BB124" s="13"/>
+      <c r="BC124" s="13"/>
+      <c r="BD124" s="13"/>
+      <c r="BN124" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="BD124" s="3">
+      <c r="BO124" s="3">
         <v>800000000</v>
       </c>
-      <c r="BE124" s="4">
+      <c r="BP124" s="4">
         <v>0</v>
       </c>
-      <c r="BF124" s="4">
+      <c r="BQ124" s="4">
         <v>-10</v>
       </c>
-      <c r="BG124" s="4">
+      <c r="BR124" s="4">
         <v>-50</v>
       </c>
-      <c r="BH124" s="4">
+      <c r="BS124" s="4">
         <v>-100</v>
       </c>
-      <c r="BI124" s="4">
+      <c r="BT124" s="4">
         <v>-200</v>
       </c>
-      <c r="BJ124" s="4">
+      <c r="BU124" s="4">
         <v>-1000</v>
       </c>
-      <c r="BK124" s="4">
+      <c r="BV124" s="4">
         <v>-2000</v>
       </c>
-      <c r="BL124" s="4">
+      <c r="BW124" s="4">
         <v>-20000</v>
       </c>
-      <c r="BM124" s="4">
+      <c r="BX124" s="4">
         <v>-100000</v>
       </c>
-      <c r="BN124" s="4">
+      <c r="BY124" s="4">
         <v>-200000</v>
       </c>
-      <c r="BO124" s="4">
+      <c r="BZ124" s="4">
         <v>-600000</v>
       </c>
     </row>
-    <row r="125" spans="1:67" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -17623,19 +18292,19 @@
       <c r="AJ125" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK125" s="1">
+      <c r="AK125" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL125" s="1">
+      <c r="AL125" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM125" s="1">
+      <c r="AM125" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN125" s="1">
+      <c r="AN125" s="20">
         <v>8.64</v>
       </c>
-      <c r="AO125" s="1">
+      <c r="AO125" s="20">
         <v>86.4</v>
       </c>
       <c r="AP125" s="1">
@@ -17653,8 +18322,28 @@
       <c r="AT125" s="1">
         <v>86.4</v>
       </c>
-    </row>
-    <row r="126" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="AU125" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV125" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW125" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX125" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY125" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AZ125" s="1"/>
+      <c r="BA125" s="1"/>
+      <c r="BB125" s="1"/>
+      <c r="BC125" s="1"/>
+      <c r="BD125" s="1"/>
+    </row>
+    <row r="126" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>245</v>
       </c>
@@ -17725,38 +18414,58 @@
       <c r="AJ126" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK126" s="13">
+      <c r="AK126" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AL126" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AM126" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AN126" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AO126" s="21">
+        <v>8.6399999999999999E-5</v>
+      </c>
+      <c r="AP126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AL126" s="13">
+      <c r="AQ126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AM126" s="13">
+      <c r="AR126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AN126" s="13">
+      <c r="AS126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AO126" s="13">
+      <c r="AT126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AP126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AQ126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AS126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AT126" s="13">
-        <v>8.6400000000000005E-2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="AU126" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV126" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AW126" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AX126" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AY126" s="21">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AZ126" s="13"/>
+      <c r="BA126" s="13"/>
+      <c r="BB126" s="13"/>
+      <c r="BC126" s="13"/>
+      <c r="BD126" s="13"/>
+    </row>
+    <row r="127" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>246</v>
       </c>
@@ -17827,19 +18536,19 @@
       <c r="AJ127" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK127" s="1">
+      <c r="AK127" s="20">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL127" s="1">
+      <c r="AL127" s="20">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM127" s="1">
+      <c r="AM127" s="20">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN127" s="1">
+      <c r="AN127" s="20">
         <v>8.64</v>
       </c>
-      <c r="AO127" s="1">
+      <c r="AO127" s="20">
         <v>86.4</v>
       </c>
       <c r="AP127" s="1">
@@ -17857,8 +18566,31 @@
       <c r="AT127" s="1">
         <v>86.4</v>
       </c>
-    </row>
-    <row r="128" spans="1:67" x14ac:dyDescent="0.45">
+      <c r="AU127" s="20">
+        <v>8.6400000000000001E-3</v>
+      </c>
+      <c r="AV127" s="20">
+        <v>8.6400000000000005E-2</v>
+      </c>
+      <c r="AW127" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="AX127" s="20">
+        <v>8.64</v>
+      </c>
+      <c r="AY127" s="20">
+        <v>86.4</v>
+      </c>
+      <c r="AZ127" s="1"/>
+      <c r="BA127" s="1"/>
+      <c r="BB127" s="1"/>
+      <c r="BC127" s="1"/>
+      <c r="BD127" s="1"/>
+      <c r="BN127" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="128" spans="1:78" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>247</v>
       </c>
@@ -17911,8 +18643,43 @@
         <f t="shared" si="15"/>
         <v>7.1160228947361758E-4</v>
       </c>
-    </row>
-    <row r="129" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN128" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO128" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="BP128" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ128" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BR128" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BS128" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BT128" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BU128" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BV128" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="BW128" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="BX128" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BY128" s="4"/>
+      <c r="BZ128" s="4"/>
+    </row>
+    <row r="129" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>248</v>
       </c>
@@ -17980,8 +18747,41 @@
       <c r="AR129" s="1"/>
       <c r="AS129" s="1"/>
       <c r="AT129" s="1"/>
-    </row>
-    <row r="130" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN129" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW129" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX129" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>249</v>
       </c>
@@ -18049,8 +18849,41 @@
       <c r="AR130" s="1"/>
       <c r="AS130" s="1"/>
       <c r="AT130" s="1"/>
-    </row>
-    <row r="131" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN130" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO130" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP130" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ130" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR130" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS130" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT130" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU130" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV130" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW130" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX130" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>250</v>
       </c>
@@ -18118,8 +18951,41 @@
       <c r="AR131" s="1"/>
       <c r="AS131" s="1"/>
       <c r="AT131" s="1"/>
-    </row>
-    <row r="132" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN131" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO131" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP131" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ131" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR131" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS131" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT131" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU131" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV131" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW131" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX131" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>251</v>
       </c>
@@ -18172,8 +19038,41 @@
         <f t="shared" si="19"/>
         <v>6.8958168854050443E-4</v>
       </c>
-    </row>
-    <row r="133" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN132" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW132" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX132" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>252</v>
       </c>
@@ -18226,8 +19125,41 @@
         <f t="shared" si="19"/>
         <v>7.0175093423377206E-4</v>
       </c>
-    </row>
-    <row r="134" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN133" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO133" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP133" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ133" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR133" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS133" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT133" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU133" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV133" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW133" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX133" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>253</v>
       </c>
@@ -18280,8 +19212,41 @@
         <f t="shared" si="19"/>
         <v>9.24392529713391E-4</v>
       </c>
-    </row>
-    <row r="135" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN134" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO134" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP134" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ134" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR134" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS134" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT134" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU134" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV134" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW134" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX134" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>254</v>
       </c>
@@ -18334,8 +19299,41 @@
         <f t="shared" si="19"/>
         <v>4.2679489394130968E-4</v>
       </c>
-    </row>
-    <row r="136" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN135" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW135" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX135" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>255</v>
       </c>
@@ -18388,8 +19386,41 @@
         <f t="shared" si="19"/>
         <v>7.0492044974188462E-4</v>
       </c>
-    </row>
-    <row r="137" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN136" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO136" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP136" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ136" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR136" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS136" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT136" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU136" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV136" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW136" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX136" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>256</v>
       </c>
@@ -18442,8 +19473,41 @@
         <f t="shared" si="19"/>
         <v>6.0317831663807579E-4</v>
       </c>
-    </row>
-    <row r="138" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN137" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO137" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP137" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ137" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR137" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS137" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT137" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU137" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV137" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW137" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX137" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>257</v>
       </c>
@@ -18496,8 +19560,41 @@
         <f t="shared" si="19"/>
         <v>5.3431529879549361E-4</v>
       </c>
-    </row>
-    <row r="139" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN138" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW138" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX138" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>258</v>
       </c>
@@ -18550,8 +19647,41 @@
         <f t="shared" si="19"/>
         <v>9.2650687165257131E-4</v>
       </c>
-    </row>
-    <row r="140" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN139" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO139" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP139" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ139" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR139" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS139" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT139" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU139" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV139" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW139" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX139" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>259</v>
       </c>
@@ -18604,8 +19734,41 @@
         <f t="shared" si="19"/>
         <v>4.9093461376614072E-4</v>
       </c>
-    </row>
-    <row r="141" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN140" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO140" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP140" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ140" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR140" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS140" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT140" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU140" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV140" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW140" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX140" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>260</v>
       </c>
@@ -18658,8 +19821,41 @@
         <f t="shared" si="19"/>
         <v>4.6471042769603648E-4</v>
       </c>
-    </row>
-    <row r="142" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN141" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BV141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BW141" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX141" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>261</v>
       </c>
@@ -18712,8 +19908,41 @@
         <f t="shared" si="19"/>
         <v>3.9116170433328728E-4</v>
       </c>
-    </row>
-    <row r="143" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN142" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO142" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP142" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ142" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR142" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS142" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT142" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU142" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV142" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW142" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX142" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="143" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>262</v>
       </c>
@@ -18766,8 +19995,41 @@
         <f t="shared" si="19"/>
         <v>4.0431038289007962E-4</v>
       </c>
-    </row>
-    <row r="144" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="BN143" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO143" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP143" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ143" s="4">
+        <v>-100</v>
+      </c>
+      <c r="BR143" s="4">
+        <v>-200</v>
+      </c>
+      <c r="BS143" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BT143" s="4">
+        <v>-2000</v>
+      </c>
+      <c r="BU143" s="4">
+        <v>-20000</v>
+      </c>
+      <c r="BV143" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BW143" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BX143" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="144" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>263</v>
       </c>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566D8907-7F27-48FB-83A0-CB2391BF6ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C894EEF-4FCA-4C26-ACA8-FCE6993622AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14168" yWindow="2107" windowWidth="21599" windowHeight="11423" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2459" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="1192">
   <si>
     <t>nlay</t>
   </si>
@@ -3570,9 +3570,6 @@
     <t>Run01</t>
   </si>
   <si>
-    <t>Run02</t>
-  </si>
-  <si>
     <t>kv_1E-12_kh_1E-07</t>
   </si>
   <si>
@@ -3619,6 +3616,12 @@
   </si>
   <si>
     <t>Run03</t>
+  </si>
+  <si>
+    <t>Run02.1</t>
+  </si>
+  <si>
+    <t>Run02.2</t>
   </si>
 </sst>
 </file>
@@ -3675,18 +3678,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -3732,7 +3729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3759,9 +3756,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="11" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="11" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -5229,65 +5223,27 @@
         <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>1184</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>1164</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>1165</v>
-      </c>
-      <c r="J1" s="19" t="s">
-        <v>1166</v>
-      </c>
-      <c r="K1" s="19" t="s">
-        <v>1167</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>1185</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>1186</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>1187</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>1188</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>1189</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>1168</v>
-      </c>
-      <c r="R1" s="19" t="s">
-        <v>1169</v>
-      </c>
-      <c r="S1" s="19" t="s">
-        <v>1170</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>1171</v>
-      </c>
-      <c r="U1" s="19" t="s">
-        <v>1172</v>
-      </c>
+        <v>1157</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
       <c r="V1" s="4"/>
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
@@ -5314,65 +5270,27 @@
         <v>50</v>
       </c>
       <c r="B2" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E2" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F2" s="1">
         <v>86.4</v>
       </c>
-      <c r="G2" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H2" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I2" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J2" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="K2" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="L2" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M2" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O2" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P2" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q2" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R2" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S2" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T2" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="U2" s="20">
-        <v>86.4</v>
-      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -5399,65 +5317,27 @@
         <v>54</v>
       </c>
       <c r="B3" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="C3" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="D3" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="E3" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="F3" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="G3" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="H3" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="I3" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="J3" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="K3" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="L3" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="M3" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="N3" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="O3" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="P3" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="Q3" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R3" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S3" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T3" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U3" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="18"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
@@ -5484,65 +5364,27 @@
         <v>56</v>
       </c>
       <c r="B4" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E4" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F4" s="1">
         <v>86.4</v>
       </c>
-      <c r="G4" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H4" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I4" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J4" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="K4" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="L4" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M4" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N4" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O4" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P4" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q4" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R4" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S4" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T4" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="U4" s="20">
-        <v>86.4</v>
-      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -5569,65 +5411,27 @@
         <v>58</v>
       </c>
       <c r="B5" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="C5" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="D5" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="E5" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="F5" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="G5" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="H5" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="I5" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="J5" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="K5" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="L5" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="M5" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="N5" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="O5" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="P5" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="Q5" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R5" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S5" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T5" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U5" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18"/>
+      <c r="S5" s="18"/>
+      <c r="T5" s="18"/>
+      <c r="U5" s="18"/>
       <c r="V5" s="13"/>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
@@ -5654,65 +5458,27 @@
         <v>60</v>
       </c>
       <c r="B6" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F6" s="1">
         <v>86.4</v>
       </c>
-      <c r="G6" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H6" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I6" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J6" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="K6" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="L6" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M6" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O6" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P6" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q6" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R6" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S6" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T6" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="U6" s="20">
-        <v>86.4</v>
-      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -5739,65 +5505,27 @@
         <v>62</v>
       </c>
       <c r="B7" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E7" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F7" s="1">
         <v>86.4</v>
       </c>
-      <c r="G7" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H7" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I7" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J7" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="K7" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="L7" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M7" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O7" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P7" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q7" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R7" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S7" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T7" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="U7" s="20">
-        <v>86.4</v>
-      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
@@ -5824,65 +5552,27 @@
         <v>63</v>
       </c>
       <c r="B8" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="C8" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="D8" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="E8" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="F8" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="G8" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="H8" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="I8" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="J8" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="K8" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="L8" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="M8" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="N8" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="O8" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="P8" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="Q8" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R8" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S8" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T8" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U8" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
@@ -5909,65 +5599,27 @@
         <v>64</v>
       </c>
       <c r="B9" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F9" s="1">
         <v>86.4</v>
       </c>
-      <c r="G9" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H9" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I9" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J9" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="K9" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="L9" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M9" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O9" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P9" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q9" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R9" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S9" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T9" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="U9" s="20">
-        <v>86.4</v>
-      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -5994,65 +5646,27 @@
         <v>65</v>
       </c>
       <c r="B10" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="C10" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="D10" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="E10" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="F10" s="13">
-        <v>8.6400000000000003E-6</v>
-      </c>
-      <c r="G10" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="H10" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="I10" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="J10" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="K10" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="L10" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="M10" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="N10" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="O10" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="P10" s="13">
-        <v>8.6399999999999997E-4</v>
-      </c>
-      <c r="Q10" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R10" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="S10" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="T10" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="U10" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
@@ -6079,65 +5693,27 @@
         <v>66</v>
       </c>
       <c r="B11" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="F11" s="1">
         <v>86.4</v>
       </c>
-      <c r="G11" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="H11" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="I11" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="J11" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="K11" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="L11" s="1">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="M11" s="1">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="O11" s="1">
-        <v>8.64</v>
-      </c>
-      <c r="P11" s="1">
-        <v>86.4</v>
-      </c>
-      <c r="Q11" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="R11" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="S11" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="T11" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="U11" s="20">
-        <v>86.4</v>
-      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
@@ -6648,6 +6224,7 @@
   <cols>
     <col min="1" max="1" width="15.46484375" style="4" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="27.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.45">
@@ -13454,63 +13031,33 @@
         <v>43</v>
       </c>
       <c r="AF91" s="16" t="s">
-        <v>1153</v>
+        <v>1163</v>
       </c>
       <c r="AG91" s="16" t="s">
-        <v>1154</v>
+        <v>1164</v>
       </c>
       <c r="AH91" s="16" t="s">
-        <v>1155</v>
+        <v>1165</v>
       </c>
       <c r="AI91" s="16" t="s">
-        <v>1156</v>
+        <v>1166</v>
       </c>
       <c r="AJ91" s="16" t="s">
-        <v>1157</v>
+        <v>1167</v>
       </c>
       <c r="AK91" s="16" t="s">
-        <v>1158</v>
+        <v>1168</v>
       </c>
       <c r="AL91" s="16" t="s">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="AM91" s="16" t="s">
-        <v>1160</v>
+        <v>1170</v>
       </c>
       <c r="AN91" s="16" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="AO91" s="16" t="s">
-        <v>1162</v>
-      </c>
-      <c r="AP91" s="19" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AQ91" s="19" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AR91" s="19" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AS91" s="19" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AT91" s="19" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AU91" s="19" t="s">
-        <v>1168</v>
-      </c>
-      <c r="AV91" s="19" t="s">
-        <v>1169</v>
-      </c>
-      <c r="AW91" s="19" t="s">
-        <v>1170</v>
-      </c>
-      <c r="AX91" s="19" t="s">
-        <v>1171</v>
-      </c>
-      <c r="AY91" s="19" t="s">
         <v>1172</v>
       </c>
       <c r="BN91" s="4" t="s">
@@ -13639,36 +13186,6 @@
       <c r="AO92" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP92" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ92" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR92" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS92" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT92" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU92" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV92" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW92" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX92" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY92" s="20">
-        <v>86.4</v>
-      </c>
       <c r="BN92" s="4" t="s">
         <v>93</v>
       </c>
@@ -13766,63 +13283,33 @@
         <v>54</v>
       </c>
       <c r="AF93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ93" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN93" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO93" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT93" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX93" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY93" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="BN93" s="4" t="s">
@@ -13951,36 +13438,6 @@
       <c r="AO94" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP94" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ94" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR94" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS94" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT94" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU94" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV94" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW94" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX94" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY94" s="20">
-        <v>86.4</v>
-      </c>
       <c r="BN94" s="4" t="s">
         <v>94</v>
       </c>
@@ -14078,63 +13535,33 @@
         <v>58</v>
       </c>
       <c r="AF95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ95" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN95" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO95" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT95" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX95" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY95" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="BN95" s="4" t="s">
@@ -14263,36 +13690,6 @@
       <c r="AO96" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP96" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ96" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR96" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS96" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT96" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU96" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV96" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW96" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX96" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY96" s="20">
-        <v>86.4</v>
-      </c>
       <c r="BN96" s="4" t="s">
         <v>94</v>
       </c>
@@ -14419,36 +13816,6 @@
       <c r="AO97" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP97" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ97" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR97" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS97" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT97" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU97" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV97" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW97" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX97" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY97" s="20">
-        <v>86.4</v>
-      </c>
       <c r="BN97" s="4" t="s">
         <v>95</v>
       </c>
@@ -14546,63 +13913,33 @@
         <v>63</v>
       </c>
       <c r="AF98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ98" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN98" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO98" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT98" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX98" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY98" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="BN98" s="4" t="s">
@@ -14731,36 +14068,6 @@
       <c r="AO99" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP99" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ99" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR99" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS99" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT99" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU99" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV99" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW99" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX99" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY99" s="20">
-        <v>86.4</v>
-      </c>
       <c r="BN99" s="4" t="s">
         <v>95</v>
       </c>
@@ -14858,63 +14165,33 @@
         <v>65</v>
       </c>
       <c r="AF100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AG100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AH100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AI100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AJ100" s="18">
-        <v>8.6399999999999999E-9</v>
+        <v>8.6399999999999999E-5</v>
       </c>
       <c r="AK100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AL100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AM100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AN100" s="18">
-        <v>8.6400000000000001E-7</v>
+        <v>8.6400000000000001E-3</v>
       </c>
       <c r="AO100" s="18">
-        <v>8.6400000000000001E-7</v>
-      </c>
-      <c r="AP100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AQ100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AR100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AS100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AT100" s="21">
-        <v>8.6399999999999999E-5</v>
-      </c>
-      <c r="AU100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AW100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AX100" s="21">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AY100" s="21">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="BN100" s="4" t="s">
@@ -15043,36 +14320,6 @@
       <c r="AO101" s="17">
         <v>86.4</v>
       </c>
-      <c r="AP101" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AQ101" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AR101" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AS101" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AT101" s="20">
-        <v>86.4</v>
-      </c>
-      <c r="AU101" s="20">
-        <v>8.6400000000000001E-3</v>
-      </c>
-      <c r="AV101" s="20">
-        <v>8.6400000000000005E-2</v>
-      </c>
-      <c r="AW101" s="20">
-        <v>0.86399999999999999</v>
-      </c>
-      <c r="AX101" s="20">
-        <v>8.64</v>
-      </c>
-      <c r="AY101" s="20">
-        <v>86.4</v>
-      </c>
       <c r="BN101" s="4" t="s">
         <v>96</v>
       </c>
@@ -15260,7 +14507,7 @@
         <v>6.1373542849109256E-4</v>
       </c>
       <c r="AE103" s="14" t="s">
-        <v>1174</v>
+        <v>1190</v>
       </c>
       <c r="BN103" s="4" t="s">
         <v>97</v>
@@ -15374,19 +14621,19 @@
         <v>1157</v>
       </c>
       <c r="AK104" s="4" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AL104" s="4" t="s">
         <v>1175</v>
       </c>
-      <c r="AL104" s="4" t="s">
+      <c r="AM104" s="4" t="s">
         <v>1176</v>
       </c>
-      <c r="AM104" s="4" t="s">
+      <c r="AN104" s="4" t="s">
         <v>1177</v>
       </c>
-      <c r="AN104" s="4" t="s">
+      <c r="AO104" s="4" t="s">
         <v>1178</v>
-      </c>
-      <c r="AO104" s="4" t="s">
-        <v>1179</v>
       </c>
       <c r="AP104" s="4" t="s">
         <v>1158</v>
@@ -15890,7 +15137,7 @@
         <v>8.6400000000000001E-7</v>
       </c>
       <c r="BN108" t="s">
-        <v>1174</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="109" spans="1:78" x14ac:dyDescent="0.45">
@@ -16886,7 +16133,7 @@
         <v>9.0184342071178349E-4</v>
       </c>
       <c r="AE116" s="14" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="AF116" s="4"/>
       <c r="AG116" s="4"/>
@@ -16990,63 +16237,63 @@
         <v>43</v>
       </c>
       <c r="AF117" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="AG117" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="AG117" s="4" t="s">
+      <c r="AH117" s="4" t="s">
         <v>1181</v>
       </c>
-      <c r="AH117" s="4" t="s">
+      <c r="AI117" s="4" t="s">
         <v>1182</v>
       </c>
-      <c r="AI117" s="4" t="s">
+      <c r="AJ117" s="4" t="s">
         <v>1183</v>
       </c>
-      <c r="AJ117" s="4" t="s">
+      <c r="AK117" s="16" t="s">
+        <v>1163</v>
+      </c>
+      <c r="AL117" s="16" t="s">
+        <v>1164</v>
+      </c>
+      <c r="AM117" s="16" t="s">
+        <v>1165</v>
+      </c>
+      <c r="AN117" s="16" t="s">
+        <v>1166</v>
+      </c>
+      <c r="AO117" s="16" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AP117" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="AK117" s="19" t="s">
-        <v>1163</v>
-      </c>
-      <c r="AL117" s="19" t="s">
-        <v>1164</v>
-      </c>
-      <c r="AM117" s="19" t="s">
-        <v>1165</v>
-      </c>
-      <c r="AN117" s="19" t="s">
-        <v>1166</v>
-      </c>
-      <c r="AO117" s="19" t="s">
-        <v>1167</v>
-      </c>
-      <c r="AP117" s="4" t="s">
+      <c r="AQ117" s="4" t="s">
         <v>1185</v>
       </c>
-      <c r="AQ117" s="4" t="s">
+      <c r="AR117" s="4" t="s">
         <v>1186</v>
       </c>
-      <c r="AR117" s="4" t="s">
+      <c r="AS117" s="4" t="s">
         <v>1187</v>
       </c>
-      <c r="AS117" s="4" t="s">
+      <c r="AT117" s="4" t="s">
         <v>1188</v>
       </c>
-      <c r="AT117" s="4" t="s">
-        <v>1189</v>
-      </c>
-      <c r="AU117" s="19" t="s">
+      <c r="AU117" s="16" t="s">
         <v>1168</v>
       </c>
-      <c r="AV117" s="19" t="s">
+      <c r="AV117" s="16" t="s">
         <v>1169</v>
       </c>
-      <c r="AW117" s="19" t="s">
+      <c r="AW117" s="16" t="s">
         <v>1170</v>
       </c>
-      <c r="AX117" s="19" t="s">
+      <c r="AX117" s="16" t="s">
         <v>1171</v>
       </c>
-      <c r="AY117" s="19" t="s">
+      <c r="AY117" s="16" t="s">
         <v>1172</v>
       </c>
       <c r="AZ117" s="4"/>
@@ -17165,19 +16412,19 @@
       <c r="AJ118" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK118" s="20">
+      <c r="AK118" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL118" s="20">
+      <c r="AL118" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM118" s="20">
+      <c r="AM118" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN118" s="20">
+      <c r="AN118" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO118" s="20">
+      <c r="AO118" s="17">
         <v>86.4</v>
       </c>
       <c r="AP118" s="1">
@@ -17195,19 +16442,19 @@
       <c r="AT118" s="1">
         <v>86.4</v>
       </c>
-      <c r="AU118" s="20">
+      <c r="AU118" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV118" s="20">
+      <c r="AV118" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AW118" s="20">
+      <c r="AW118" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AX118" s="20">
+      <c r="AX118" s="17">
         <v>8.64</v>
       </c>
-      <c r="AY118" s="20">
+      <c r="AY118" s="17">
         <v>86.4</v>
       </c>
       <c r="AZ118" s="1"/>
@@ -17326,19 +16573,19 @@
       <c r="AJ119" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK119" s="21">
+      <c r="AK119" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AL119" s="21">
+      <c r="AL119" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AM119" s="21">
+      <c r="AM119" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AN119" s="21">
+      <c r="AN119" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AO119" s="21">
+      <c r="AO119" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
       <c r="AP119" s="13">
@@ -17356,19 +16603,19 @@
       <c r="AT119" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AU119" s="21">
+      <c r="AU119" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV119" s="21">
+      <c r="AV119" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AW119" s="21">
+      <c r="AW119" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AX119" s="21">
+      <c r="AX119" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AY119" s="21">
+      <c r="AY119" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="AZ119" s="13"/>
@@ -17487,19 +16734,19 @@
       <c r="AJ120" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK120" s="20">
+      <c r="AK120" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL120" s="20">
+      <c r="AL120" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM120" s="20">
+      <c r="AM120" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN120" s="20">
+      <c r="AN120" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO120" s="20">
+      <c r="AO120" s="17">
         <v>86.4</v>
       </c>
       <c r="AP120" s="1">
@@ -17517,19 +16764,19 @@
       <c r="AT120" s="1">
         <v>86.4</v>
       </c>
-      <c r="AU120" s="20">
+      <c r="AU120" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV120" s="20">
+      <c r="AV120" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AW120" s="20">
+      <c r="AW120" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AX120" s="20">
+      <c r="AX120" s="17">
         <v>8.64</v>
       </c>
-      <c r="AY120" s="20">
+      <c r="AY120" s="17">
         <v>86.4</v>
       </c>
       <c r="AZ120" s="1"/>
@@ -17648,19 +16895,19 @@
       <c r="AJ121" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK121" s="21">
+      <c r="AK121" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AL121" s="21">
+      <c r="AL121" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AM121" s="21">
+      <c r="AM121" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AN121" s="21">
+      <c r="AN121" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AO121" s="21">
+      <c r="AO121" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
       <c r="AP121" s="13">
@@ -17678,19 +16925,19 @@
       <c r="AT121" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AU121" s="21">
+      <c r="AU121" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV121" s="21">
+      <c r="AV121" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AW121" s="21">
+      <c r="AW121" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AX121" s="21">
+      <c r="AX121" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AY121" s="21">
+      <c r="AY121" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="AZ121" s="13"/>
@@ -17809,19 +17056,19 @@
       <c r="AJ122" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK122" s="20">
+      <c r="AK122" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL122" s="20">
+      <c r="AL122" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM122" s="20">
+      <c r="AM122" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN122" s="20">
+      <c r="AN122" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO122" s="20">
+      <c r="AO122" s="17">
         <v>86.4</v>
       </c>
       <c r="AP122" s="1">
@@ -17839,19 +17086,19 @@
       <c r="AT122" s="1">
         <v>86.4</v>
       </c>
-      <c r="AU122" s="20">
+      <c r="AU122" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV122" s="20">
+      <c r="AV122" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AW122" s="20">
+      <c r="AW122" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AX122" s="20">
+      <c r="AX122" s="17">
         <v>8.64</v>
       </c>
-      <c r="AY122" s="20">
+      <c r="AY122" s="17">
         <v>86.4</v>
       </c>
       <c r="AZ122" s="1"/>
@@ -17970,19 +17217,19 @@
       <c r="AJ123" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK123" s="20">
+      <c r="AK123" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL123" s="20">
+      <c r="AL123" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM123" s="20">
+      <c r="AM123" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN123" s="20">
+      <c r="AN123" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO123" s="20">
+      <c r="AO123" s="17">
         <v>86.4</v>
       </c>
       <c r="AP123" s="1">
@@ -18000,19 +17247,19 @@
       <c r="AT123" s="1">
         <v>86.4</v>
       </c>
-      <c r="AU123" s="20">
+      <c r="AU123" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV123" s="20">
+      <c r="AV123" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AW123" s="20">
+      <c r="AW123" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AX123" s="20">
+      <c r="AX123" s="17">
         <v>8.64</v>
       </c>
-      <c r="AY123" s="20">
+      <c r="AY123" s="17">
         <v>86.4</v>
       </c>
       <c r="AZ123" s="1"/>
@@ -18131,19 +17378,19 @@
       <c r="AJ124" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK124" s="21">
+      <c r="AK124" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AL124" s="21">
+      <c r="AL124" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AM124" s="21">
+      <c r="AM124" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AN124" s="21">
+      <c r="AN124" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AO124" s="21">
+      <c r="AO124" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
       <c r="AP124" s="13">
@@ -18161,19 +17408,19 @@
       <c r="AT124" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AU124" s="21">
+      <c r="AU124" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV124" s="21">
+      <c r="AV124" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AW124" s="21">
+      <c r="AW124" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AX124" s="21">
+      <c r="AX124" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AY124" s="21">
+      <c r="AY124" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="AZ124" s="13"/>
@@ -18292,19 +17539,19 @@
       <c r="AJ125" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK125" s="20">
+      <c r="AK125" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL125" s="20">
+      <c r="AL125" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM125" s="20">
+      <c r="AM125" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN125" s="20">
+      <c r="AN125" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO125" s="20">
+      <c r="AO125" s="17">
         <v>86.4</v>
       </c>
       <c r="AP125" s="1">
@@ -18322,19 +17569,19 @@
       <c r="AT125" s="1">
         <v>86.4</v>
       </c>
-      <c r="AU125" s="20">
+      <c r="AU125" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV125" s="20">
+      <c r="AV125" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AW125" s="20">
+      <c r="AW125" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AX125" s="20">
+      <c r="AX125" s="17">
         <v>8.64</v>
       </c>
-      <c r="AY125" s="20">
+      <c r="AY125" s="17">
         <v>86.4</v>
       </c>
       <c r="AZ125" s="1"/>
@@ -18414,19 +17661,19 @@
       <c r="AJ126" s="13">
         <v>8.6400000000000003E-6</v>
       </c>
-      <c r="AK126" s="21">
+      <c r="AK126" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AL126" s="21">
+      <c r="AL126" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AM126" s="21">
+      <c r="AM126" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AN126" s="21">
+      <c r="AN126" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
-      <c r="AO126" s="21">
+      <c r="AO126" s="18">
         <v>8.6399999999999999E-5</v>
       </c>
       <c r="AP126" s="13">
@@ -18444,19 +17691,19 @@
       <c r="AT126" s="13">
         <v>8.6399999999999997E-4</v>
       </c>
-      <c r="AU126" s="21">
+      <c r="AU126" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV126" s="21">
+      <c r="AV126" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AW126" s="21">
+      <c r="AW126" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AX126" s="21">
+      <c r="AX126" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AY126" s="21">
+      <c r="AY126" s="18">
         <v>8.6400000000000001E-3</v>
       </c>
       <c r="AZ126" s="13"/>
@@ -18536,19 +17783,19 @@
       <c r="AJ127" s="1">
         <v>86.4</v>
       </c>
-      <c r="AK127" s="20">
+      <c r="AK127" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AL127" s="20">
+      <c r="AL127" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AM127" s="20">
+      <c r="AM127" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AN127" s="20">
+      <c r="AN127" s="17">
         <v>8.64</v>
       </c>
-      <c r="AO127" s="20">
+      <c r="AO127" s="17">
         <v>86.4</v>
       </c>
       <c r="AP127" s="1">
@@ -18566,19 +17813,19 @@
       <c r="AT127" s="1">
         <v>86.4</v>
       </c>
-      <c r="AU127" s="20">
+      <c r="AU127" s="17">
         <v>8.6400000000000001E-3</v>
       </c>
-      <c r="AV127" s="20">
+      <c r="AV127" s="17">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="AW127" s="20">
+      <c r="AW127" s="17">
         <v>0.86399999999999999</v>
       </c>
-      <c r="AX127" s="20">
+      <c r="AX127" s="17">
         <v>8.64</v>
       </c>
-      <c r="AY127" s="20">
+      <c r="AY127" s="17">
         <v>86.4</v>
       </c>
       <c r="AZ127" s="1"/>
@@ -18587,7 +17834,7 @@
       <c r="BC127" s="1"/>
       <c r="BD127" s="1"/>
       <c r="BN127" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="128" spans="1:78" x14ac:dyDescent="0.45">
@@ -18731,6 +17978,9 @@
       <c r="AA129" s="1">
         <f t="shared" si="15"/>
         <v>6.7192904177343729E-4</v>
+      </c>
+      <c r="AE129" s="14" t="s">
+        <v>1189</v>
       </c>
       <c r="AF129" s="1"/>
       <c r="AG129" s="1"/>
@@ -18834,8 +18084,13 @@
         <f t="shared" ref="AA130:AA154" si="19">+W130</f>
         <v>6.8402164621609858E-4</v>
       </c>
-      <c r="AF130" s="1"/>
-      <c r="AG130" s="1"/>
+      <c r="AE130" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF130" s="4" t="s">
+        <v>1157</v>
+      </c>
+      <c r="AG130" s="4"/>
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
@@ -18936,7 +18191,12 @@
         <f t="shared" si="19"/>
         <v>7.3510433221211555E-4</v>
       </c>
-      <c r="AF131" s="1"/>
+      <c r="AE131" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF131" s="1">
+        <v>86.4</v>
+      </c>
       <c r="AG131" s="1"/>
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
@@ -19038,6 +18298,13 @@
         <f t="shared" si="19"/>
         <v>6.8958168854050443E-4</v>
       </c>
+      <c r="AE132" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF132" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG132" s="15"/>
       <c r="BN132" s="4" t="s">
         <v>94</v>
       </c>
@@ -19125,6 +18392,13 @@
         <f t="shared" si="19"/>
         <v>7.0175093423377206E-4</v>
       </c>
+      <c r="AE133" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF133" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG133" s="1"/>
       <c r="BN133" s="4" t="s">
         <v>94</v>
       </c>
@@ -19212,6 +18486,13 @@
         <f t="shared" si="19"/>
         <v>9.24392529713391E-4</v>
       </c>
+      <c r="AE134" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF134" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG134" s="15"/>
       <c r="BN134" s="4" t="s">
         <v>94</v>
       </c>
@@ -19299,6 +18580,13 @@
         <f t="shared" si="19"/>
         <v>4.2679489394130968E-4</v>
       </c>
+      <c r="AE135" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF135" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG135" s="1"/>
       <c r="BN135" s="4" t="s">
         <v>95</v>
       </c>
@@ -19386,6 +18674,13 @@
         <f t="shared" si="19"/>
         <v>7.0492044974188462E-4</v>
       </c>
+      <c r="AE136" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF136" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG136" s="1"/>
       <c r="BN136" s="4" t="s">
         <v>95</v>
       </c>
@@ -19473,6 +18768,13 @@
         <f t="shared" si="19"/>
         <v>6.0317831663807579E-4</v>
       </c>
+      <c r="AE137" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF137" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG137" s="15"/>
       <c r="BN137" s="4" t="s">
         <v>95</v>
       </c>
@@ -19560,6 +18862,13 @@
         <f t="shared" si="19"/>
         <v>5.3431529879549361E-4</v>
       </c>
+      <c r="AE138" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF138" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG138" s="1"/>
       <c r="BN138" s="4" t="s">
         <v>96</v>
       </c>
@@ -19647,6 +18956,13 @@
         <f t="shared" si="19"/>
         <v>9.2650687165257131E-4</v>
       </c>
+      <c r="AE139" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF139" s="13">
+        <v>8.6399999999999999E-9</v>
+      </c>
+      <c r="AG139" s="15"/>
       <c r="BN139" s="4" t="s">
         <v>96</v>
       </c>
@@ -19734,6 +19050,13 @@
         <f t="shared" si="19"/>
         <v>4.9093461376614072E-4</v>
       </c>
+      <c r="AE140" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF140" s="1">
+        <v>86.4</v>
+      </c>
+      <c r="AG140" s="1"/>
       <c r="BN140" s="4" t="s">
         <v>96</v>
       </c>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C894EEF-4FCA-4C26-ACA8-FCE6993622AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87682DB6-E830-4E8C-84C4-D2AEA9815CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -44650,7 +44650,7 @@
         <v>400</v>
       </c>
       <c r="F2" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -44670,7 +44670,7 @@
         <v>399</v>
       </c>
       <c r="F3" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -44690,7 +44690,7 @@
         <v>401</v>
       </c>
       <c r="F4" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -44710,7 +44710,7 @@
         <v>402</v>
       </c>
       <c r="F5" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -44730,7 +44730,7 @@
         <v>398</v>
       </c>
       <c r="F6" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -44804,7 +44804,7 @@
         <v>400</v>
       </c>
       <c r="F3" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -44824,7 +44824,7 @@
         <v>400</v>
       </c>
       <c r="F4" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -44864,7 +44864,7 @@
         <v>399</v>
       </c>
       <c r="F6" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -44884,7 +44884,7 @@
         <v>399</v>
       </c>
       <c r="F7" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -44924,7 +44924,7 @@
         <v>401</v>
       </c>
       <c r="F9" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.45">
@@ -44944,7 +44944,7 @@
         <v>401</v>
       </c>
       <c r="F10" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.45">
@@ -44984,7 +44984,7 @@
         <v>402</v>
       </c>
       <c r="F12" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
@@ -45004,7 +45004,7 @@
         <v>402</v>
       </c>
       <c r="F13" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
@@ -45044,7 +45044,7 @@
         <v>398</v>
       </c>
       <c r="F15" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.45">
@@ -45064,7 +45064,7 @@
         <v>398</v>
       </c>
       <c r="F16" s="4">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87682DB6-E830-4E8C-84C4-D2AEA9815CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8506B43F-7934-46F8-A247-74182959C85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -44650,7 +44650,7 @@
         <v>400</v>
       </c>
       <c r="F2" s="4">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -44670,7 +44670,7 @@
         <v>399</v>
       </c>
       <c r="F3" s="4">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -44690,7 +44690,7 @@
         <v>401</v>
       </c>
       <c r="F4" s="4">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -44710,7 +44710,7 @@
         <v>402</v>
       </c>
       <c r="F5" s="4">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -44730,7 +44730,7 @@
         <v>398</v>
       </c>
       <c r="F6" s="4">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
   </sheetData>
@@ -44741,13 +44741,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>91</v>
       </c>
@@ -44767,7 +44767,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -44786,8 +44786,9 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>93</v>
       </c>
@@ -44804,10 +44805,11 @@
         <v>400</v>
       </c>
       <c r="F3" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -44824,10 +44826,11 @@
         <v>400</v>
       </c>
       <c r="F4" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -44846,8 +44849,9 @@
       <c r="F5" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -44864,10 +44868,11 @@
         <v>399</v>
       </c>
       <c r="F6" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>94</v>
       </c>
@@ -44884,10 +44889,11 @@
         <v>399</v>
       </c>
       <c r="F7" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -44906,8 +44912,9 @@
       <c r="F8" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>95</v>
       </c>
@@ -44924,10 +44931,11 @@
         <v>401</v>
       </c>
       <c r="F9" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -44944,10 +44952,11 @@
         <v>401</v>
       </c>
       <c r="F10" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -44966,8 +44975,9 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -44984,10 +44994,11 @@
         <v>402</v>
       </c>
       <c r="F12" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -45004,10 +45015,11 @@
         <v>402</v>
       </c>
       <c r="F13" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>97</v>
       </c>
@@ -45026,8 +45038,9 @@
       <c r="F14" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>97</v>
       </c>
@@ -45044,10 +45057,11 @@
         <v>398</v>
       </c>
       <c r="F15" s="4">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+        <v>-50</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -45064,8 +45078,21 @@
         <v>398</v>
       </c>
       <c r="F16" s="4">
-        <v>-100</v>
-      </c>
+        <v>-50</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.45">
+      <c r="G20" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8506B43F-7934-46F8-A247-74182959C85A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D33F23-147F-4BEE-B880-E7460E9D6C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5250" yWindow="2775" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -26112,7 +26112,7 @@
         <v>70</v>
       </c>
       <c r="J2" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2" s="4">
         <v>1</v>
@@ -26147,7 +26147,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="4">
         <v>2</v>
@@ -26182,7 +26182,7 @@
         <v>70</v>
       </c>
       <c r="J4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -26217,7 +26217,7 @@
         <v>70</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -26252,7 +26252,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4">
         <v>5</v>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D33F23-147F-4BEE-B880-E7460E9D6C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753F2932-83FD-44A0-88BD-B0C0188D58DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5250" yWindow="2775" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26112,7 +26112,7 @@
         <v>70</v>
       </c>
       <c r="J2" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="4">
         <v>1</v>
@@ -26147,7 +26147,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="4">
         <v>2</v>
@@ -26182,7 +26182,7 @@
         <v>70</v>
       </c>
       <c r="J4" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -26217,7 +26217,7 @@
         <v>70</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -26252,7 +26252,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" s="4">
         <v>5</v>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753F2932-83FD-44A0-88BD-B0C0188D58DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC14C1F3-3894-466A-B410-8F6EE96B7693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="2775" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="1192">
   <si>
     <t>nlay</t>
   </si>
@@ -5225,7 +5225,9 @@
       <c r="B1" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="C1" s="4"/>
+      <c r="C1" s="4" t="s">
+        <v>1178</v>
+      </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -5272,7 +5274,9 @@
       <c r="B2" s="1">
         <v>86.4</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1">
+        <v>86.4</v>
+      </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -5319,7 +5323,9 @@
       <c r="B3" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C3" s="15"/>
+      <c r="C3" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
@@ -5366,7 +5372,9 @@
       <c r="B4" s="1">
         <v>86.4</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1">
+        <v>86.4</v>
+      </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
@@ -5413,7 +5421,9 @@
       <c r="B5" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C5" s="15"/>
+      <c r="C5" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -5460,7 +5470,9 @@
       <c r="B6" s="1">
         <v>86.4</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>86.4</v>
+      </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -5507,7 +5519,9 @@
       <c r="B7" s="1">
         <v>86.4</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>86.4</v>
+      </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -5554,7 +5568,9 @@
       <c r="B8" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C8" s="15"/>
+      <c r="C8" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
@@ -5601,7 +5617,9 @@
       <c r="B9" s="1">
         <v>86.4</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>86.4</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -5648,7 +5666,9 @@
       <c r="B10" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="C10" s="15"/>
+      <c r="C10" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
@@ -5695,7 +5715,9 @@
       <c r="B11" s="1">
         <v>86.4</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1">
+        <v>86.4</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -18090,7 +18112,9 @@
       <c r="AF130" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="AG130" s="4"/>
+      <c r="AG130" s="4" t="s">
+        <v>1178</v>
+      </c>
       <c r="AH130" s="1"/>
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
@@ -18197,7 +18221,9 @@
       <c r="AF131" s="1">
         <v>86.4</v>
       </c>
-      <c r="AG131" s="1"/>
+      <c r="AG131" s="1">
+        <v>86.4</v>
+      </c>
       <c r="AH131" s="1"/>
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1"/>
@@ -18304,7 +18330,9 @@
       <c r="AF132" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="AG132" s="15"/>
+      <c r="AG132" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="BN132" s="4" t="s">
         <v>94</v>
       </c>
@@ -18398,7 +18426,9 @@
       <c r="AF133" s="1">
         <v>86.4</v>
       </c>
-      <c r="AG133" s="1"/>
+      <c r="AG133" s="1">
+        <v>86.4</v>
+      </c>
       <c r="BN133" s="4" t="s">
         <v>94</v>
       </c>
@@ -18492,7 +18522,9 @@
       <c r="AF134" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="AG134" s="15"/>
+      <c r="AG134" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="BN134" s="4" t="s">
         <v>94</v>
       </c>
@@ -18586,7 +18618,9 @@
       <c r="AF135" s="1">
         <v>86.4</v>
       </c>
-      <c r="AG135" s="1"/>
+      <c r="AG135" s="1">
+        <v>86.4</v>
+      </c>
       <c r="BN135" s="4" t="s">
         <v>95</v>
       </c>
@@ -18680,7 +18714,9 @@
       <c r="AF136" s="1">
         <v>86.4</v>
       </c>
-      <c r="AG136" s="1"/>
+      <c r="AG136" s="1">
+        <v>86.4</v>
+      </c>
       <c r="BN136" s="4" t="s">
         <v>95</v>
       </c>
@@ -18774,7 +18810,9 @@
       <c r="AF137" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="AG137" s="15"/>
+      <c r="AG137" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="BN137" s="4" t="s">
         <v>95</v>
       </c>
@@ -18868,7 +18906,9 @@
       <c r="AF138" s="1">
         <v>86.4</v>
       </c>
-      <c r="AG138" s="1"/>
+      <c r="AG138" s="1">
+        <v>86.4</v>
+      </c>
       <c r="BN138" s="4" t="s">
         <v>96</v>
       </c>
@@ -18962,7 +19002,9 @@
       <c r="AF139" s="13">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="AG139" s="15"/>
+      <c r="AG139" s="15">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="BN139" s="4" t="s">
         <v>96</v>
       </c>
@@ -19056,7 +19098,9 @@
       <c r="AF140" s="1">
         <v>86.4</v>
       </c>
-      <c r="AG140" s="1"/>
+      <c r="AG140" s="1">
+        <v>86.4</v>
+      </c>
       <c r="BN140" s="4" t="s">
         <v>96</v>
       </c>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC14C1F3-3894-466A-B410-8F6EE96B7693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0891ED1-E2E2-4720-96CA-E52F8C90FE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2445" uniqueCount="1192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="1192">
   <si>
     <t>nlay</t>
   </si>
@@ -4402,15 +4402,8 @@
       <c r="H1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>106</v>
-      </c>
+      <c r="I1" s="4"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
     </row>
@@ -4439,15 +4432,8 @@
       <c r="H2" s="4">
         <v>0</v>
       </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
+      <c r="I2" s="4"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -4462,29 +4448,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E3" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F3" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G3" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H3" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I3" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J3" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K3" s="4">
         <v>-600000</v>
       </c>
+      <c r="I3" s="4"/>
+      <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
@@ -4499,29 +4478,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E4" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F4" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G4" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H4" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I4" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J4" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K4" s="4">
         <v>-600000</v>
       </c>
+      <c r="I4" s="4"/>
+      <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -4550,15 +4522,8 @@
       <c r="H5" s="4">
         <v>0</v>
       </c>
-      <c r="I5" s="4">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
+      <c r="I5" s="4"/>
+      <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -4573,29 +4538,22 @@
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E6" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F6" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G6" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H6" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I6" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J6" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K6" s="4">
         <v>-600000</v>
       </c>
+      <c r="I6" s="4"/>
+      <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -4610,29 +4568,22 @@
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E7" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F7" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G7" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H7" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I7" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J7" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K7" s="4">
         <v>-600000</v>
       </c>
+      <c r="I7" s="4"/>
+      <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -4661,15 +4612,8 @@
       <c r="H8" s="4">
         <v>0</v>
       </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
+      <c r="I8" s="4"/>
+      <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -4684,29 +4628,22 @@
         <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E9" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F9" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G9" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H9" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I9" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J9" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K9" s="4">
         <v>-600000</v>
       </c>
+      <c r="I9" s="4"/>
+      <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -4721,29 +4658,22 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E10" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F10" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G10" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H10" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I10" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J10" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K10" s="4">
         <v>-600000</v>
       </c>
+      <c r="I10" s="4"/>
+      <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -4772,15 +4702,8 @@
       <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
+      <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -4795,29 +4718,22 @@
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E12" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F12" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G12" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H12" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I12" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J12" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K12" s="4">
         <v>-600000</v>
       </c>
+      <c r="I12" s="4"/>
+      <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -4832,29 +4748,22 @@
         <v>0</v>
       </c>
       <c r="D13" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E13" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F13" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G13" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H13" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I13" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J13" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K13" s="4">
         <v>-600000</v>
       </c>
+      <c r="I13" s="4"/>
+      <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -4883,15 +4792,8 @@
       <c r="H14" s="4">
         <v>0</v>
       </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
+      <c r="I14" s="4"/>
+      <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
@@ -4906,29 +4808,22 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E15" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F15" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G15" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H15" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I15" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J15" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K15" s="4">
         <v>-600000</v>
       </c>
+      <c r="I15" s="4"/>
+      <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
@@ -4943,29 +4838,22 @@
         <v>0</v>
       </c>
       <c r="D16" s="4">
-        <v>-100</v>
+        <v>-1000</v>
       </c>
       <c r="E16" s="4">
-        <v>-200</v>
+        <v>-10000</v>
       </c>
       <c r="F16" s="4">
-        <v>-1000</v>
+        <v>-100000</v>
       </c>
       <c r="G16" s="4">
-        <v>-2000</v>
+        <v>-200000</v>
       </c>
       <c r="H16" s="4">
-        <v>-20000</v>
-      </c>
-      <c r="I16" s="4">
-        <v>-100000</v>
-      </c>
-      <c r="J16" s="4">
-        <v>-200000</v>
-      </c>
-      <c r="K16" s="4">
         <v>-600000</v>
       </c>
+      <c r="I16" s="4"/>
+      <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
@@ -19450,7 +19338,7 @@
         <v>6.785411243790979E-4</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>264</v>
       </c>
@@ -19504,7 +19392,7 @@
         <v>7.2348983877483703E-4</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>265</v>
       </c>
@@ -19557,8 +19445,11 @@
         <f t="shared" si="19"/>
         <v>6.5532909863160892E-4</v>
       </c>
-    </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN146" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="147" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>266</v>
       </c>
@@ -19611,8 +19502,35 @@
         <f t="shared" si="19"/>
         <v>7.5474341979737567E-4</v>
       </c>
-    </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN147" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="BO147" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="BP147" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="BQ147" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="BR147" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="BS147" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="BT147" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="BU147" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BV147" s="4"/>
+      <c r="BW147" s="4"/>
+      <c r="BX147" s="4"/>
+    </row>
+    <row r="148" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>267</v>
       </c>
@@ -19665,8 +19583,32 @@
         <f t="shared" si="19"/>
         <v>5.7669688744116539E-4</v>
       </c>
-    </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN148" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT148" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU148" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>268</v>
       </c>
@@ -19719,8 +19661,32 @@
         <f t="shared" si="19"/>
         <v>8.0697176066542612E-4</v>
       </c>
-    </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN149" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO149" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP149" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ149" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR149" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS149" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT149" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU149" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="150" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>269</v>
       </c>
@@ -19773,8 +19739,32 @@
         <f t="shared" si="19"/>
         <v>6.0999509381094925E-4</v>
       </c>
-    </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN150" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BO150" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP150" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ150" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR150" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS150" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT150" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU150" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="151" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>270</v>
       </c>
@@ -19827,8 +19817,32 @@
         <f t="shared" si="19"/>
         <v>5.3117803129513444E-4</v>
       </c>
-    </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN151" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT151" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU151" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>271</v>
       </c>
@@ -19881,8 +19895,32 @@
         <f t="shared" si="19"/>
         <v>6.8402085428227407E-4</v>
       </c>
-    </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN152" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO152" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP152" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ152" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR152" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS152" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT152" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU152" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>272</v>
       </c>
@@ -19935,8 +19973,32 @@
         <f t="shared" si="19"/>
         <v>5.6115552392589597E-4</v>
       </c>
-    </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN153" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="BO153" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP153" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ153" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR153" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS153" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT153" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU153" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>273</v>
       </c>
@@ -19989,8 +20051,32 @@
         <f t="shared" si="19"/>
         <v>5.6175108458420442E-4</v>
       </c>
-    </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN154" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT154" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU154" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>274</v>
       </c>
@@ -20018,8 +20104,32 @@
       <c r="I155">
         <v>36000</v>
       </c>
-    </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN155" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO155" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP155" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ155" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR155" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS155" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT155" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU155" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="156" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>275</v>
       </c>
@@ -20047,8 +20157,32 @@
       <c r="I156">
         <v>36000</v>
       </c>
-    </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN156" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="BO156" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP156" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ156" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR156" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS156" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT156" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU156" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="157" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>276</v>
       </c>
@@ -20076,8 +20210,32 @@
       <c r="I157">
         <v>36000</v>
       </c>
-    </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN157" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT157" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU157" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>277</v>
       </c>
@@ -20105,8 +20263,32 @@
       <c r="I158">
         <v>36000</v>
       </c>
-    </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN158" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO158" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP158" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ158" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR158" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS158" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT158" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU158" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="159" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>278</v>
       </c>
@@ -20134,8 +20316,32 @@
       <c r="I159">
         <v>36000</v>
       </c>
-    </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="BN159" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BO159" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP159" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ159" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR159" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS159" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT159" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU159" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="160" spans="1:76" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>279</v>
       </c>
@@ -20163,8 +20369,32 @@
       <c r="I160">
         <v>36000</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="BN160" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BP160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BR160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BS160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BT160" s="4">
+        <v>0</v>
+      </c>
+      <c r="BU160" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>280</v>
       </c>
@@ -20192,8 +20422,32 @@
       <c r="I161">
         <v>36000</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="BN161" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO161" s="3">
+        <v>3600000</v>
+      </c>
+      <c r="BP161" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ161" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR161" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS161" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT161" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU161" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="162" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>281</v>
       </c>
@@ -20221,8 +20475,32 @@
       <c r="I162">
         <v>36000</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="BN162" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="BO162" s="3">
+        <v>800000000</v>
+      </c>
+      <c r="BP162" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ162" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="BR162" s="4">
+        <v>-10000</v>
+      </c>
+      <c r="BS162" s="4">
+        <v>-100000</v>
+      </c>
+      <c r="BT162" s="4">
+        <v>-200000</v>
+      </c>
+      <c r="BU162" s="4">
+        <v>-600000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>282</v>
       </c>
@@ -20251,7 +20529,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>283</v>
       </c>
@@ -20280,7 +20558,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>284</v>
       </c>
@@ -20309,7 +20587,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>285</v>
       </c>
@@ -20338,7 +20616,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>286</v>
       </c>
@@ -20367,7 +20645,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>287</v>
       </c>
@@ -20396,7 +20674,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>288</v>
       </c>
@@ -20425,7 +20703,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>289</v>
       </c>
@@ -20454,7 +20732,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>290</v>
       </c>
@@ -20483,7 +20761,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>291</v>
       </c>
@@ -20512,7 +20790,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>292</v>
       </c>
@@ -20541,7 +20819,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>293</v>
       </c>
@@ -20570,7 +20848,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>294</v>
       </c>
@@ -20599,7 +20877,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>295</v>
       </c>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0891ED1-E2E2-4720-96CA-E52F8C90FE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DAAEDE-2FDB-45F4-B662-2017CFDA3D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DAAEDE-2FDB-45F4-B662-2017CFDA3D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FF981-8BC5-430B-B2D2-CF80F3D2C8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26434,7 +26434,7 @@
         <v>70</v>
       </c>
       <c r="J2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="4">
         <v>1</v>
@@ -26469,7 +26469,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="4">
         <v>2</v>
@@ -26504,7 +26504,7 @@
         <v>70</v>
       </c>
       <c r="J4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -26539,7 +26539,7 @@
         <v>70</v>
       </c>
       <c r="J5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -26574,7 +26574,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4">
         <v>5</v>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793FF981-8BC5-430B-B2D2-CF80F3D2C8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF998F78-E574-4901-9F1E-19BF24234160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26434,7 +26434,7 @@
         <v>70</v>
       </c>
       <c r="J2" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" s="4">
         <v>1</v>
@@ -26469,7 +26469,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="4">
         <v>2</v>
@@ -26504,7 +26504,7 @@
         <v>70</v>
       </c>
       <c r="J4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -26539,7 +26539,7 @@
         <v>70</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -26574,7 +26574,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" s="4">
         <v>5</v>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF998F78-E574-4901-9F1E-19BF24234160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D86B026-43E4-4661-A6BF-40A1B2BF9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26434,7 +26434,7 @@
         <v>70</v>
       </c>
       <c r="J2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" s="4">
         <v>1</v>
@@ -26469,7 +26469,7 @@
         <v>70</v>
       </c>
       <c r="J3" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" s="4">
         <v>2</v>
@@ -26504,7 +26504,7 @@
         <v>70</v>
       </c>
       <c r="J4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" s="4">
         <v>3</v>
@@ -26539,7 +26539,7 @@
         <v>70</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4">
         <v>4</v>
@@ -26574,7 +26574,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" s="4">
         <v>5</v>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D86B026-43E4-4661-A6BF-40A1B2BF9C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE76D5B-775C-4CA8-9DCA-352EC9C711FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28300,7 +28300,7 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C22">
         <v>3.1154231364886891E-4</v>
@@ -28325,8 +28325,8 @@
       <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23">
-        <v>5.5555555555555599E-4</v>
+      <c r="B23" s="4">
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C23">
         <v>3.1154231364886891E-5</v>
@@ -28351,8 +28351,8 @@
       <c r="A24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24">
-        <v>5.5555555555555599E-4</v>
+      <c r="B24" s="4">
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C24">
         <v>3.1154231364886891E-4</v>
@@ -28377,8 +28377,8 @@
       <c r="A25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25">
-        <v>5.5555555555555599E-4</v>
+      <c r="B25" s="4">
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C25">
         <v>3.1154231364886891E-5</v>
@@ -28403,8 +28403,8 @@
       <c r="A26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26">
-        <v>5.5555555555555599E-4</v>
+      <c r="B26" s="4">
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C26">
         <v>3.1154231364886891E-4</v>
@@ -28590,19 +28590,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="D2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
@@ -28615,19 +28615,19 @@
         <v>3600000</v>
       </c>
       <c r="B3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="D3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="E3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
@@ -28640,19 +28640,19 @@
         <v>800000000</v>
       </c>
       <c r="B4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="C4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="D4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="E4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>5.5555555555555599E-4</v>
+        <v>5.5999999999999995E-4</v>
       </c>
       <c r="G4" s="1"/>
     </row>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE76D5B-775C-4CA8-9DCA-352EC9C711FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8DDE15-48D3-4D88-AC03-9B771B36F203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -28299,8 +28299,8 @@
       <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22">
-        <v>5.5999999999999995E-4</v>
+      <c r="B22" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C22">
         <v>3.1154231364886891E-4</v>
@@ -28325,8 +28325,8 @@
       <c r="A23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="4">
-        <v>5.5999999999999995E-4</v>
+      <c r="B23" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C23">
         <v>3.1154231364886891E-5</v>
@@ -28351,8 +28351,8 @@
       <c r="A24" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="4">
-        <v>5.5999999999999995E-4</v>
+      <c r="B24" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C24">
         <v>3.1154231364886891E-4</v>
@@ -28377,8 +28377,8 @@
       <c r="A25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="4">
-        <v>5.5999999999999995E-4</v>
+      <c r="B25" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C25">
         <v>3.1154231364886891E-5</v>
@@ -28403,8 +28403,8 @@
       <c r="A26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="4">
-        <v>5.5999999999999995E-4</v>
+      <c r="B26" s="1">
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C26">
         <v>3.1154231364886891E-4</v>
@@ -28590,19 +28590,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C2" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="D2" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E2" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G2" s="1"/>
       <c r="I2" s="1"/>
@@ -28615,19 +28615,19 @@
         <v>3600000</v>
       </c>
       <c r="B3" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C3" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="D3" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E3" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G3" s="1"/>
       <c r="I3" s="1"/>
@@ -28640,19 +28640,19 @@
         <v>800000000</v>
       </c>
       <c r="B4" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="C4" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="D4" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="E4" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>5.5999999999999995E-4</v>
+        <v>5.5555555555555556E-4</v>
       </c>
       <c r="G4" s="1"/>
     </row>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8DDE15-48D3-4D88-AC03-9B771B36F203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC066444-92B0-4760-8822-F320CCD2FE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\assets\3D\sust yield server\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7403F4B1-8A79-44A4-829C-6CC146A0529B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FCA7BF-8163-4B47-9558-247109C6C449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2541" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2542" uniqueCount="1194">
   <si>
     <t>nlay</t>
   </si>
@@ -3626,13 +3626,16 @@
   </si>
   <si>
     <t>q_init</t>
+  </si>
+  <si>
+    <t>qv_11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3679,6 +3682,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4402,7 +4411,7 @@
     <col min="10" max="10" width="10.9296875" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="12" t="s">
         <v>884</v>
       </c>
@@ -4442,8 +4451,11 @@
       <c r="M1" s="12" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N1" s="12" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="12" t="s">
         <v>886</v>
       </c>
@@ -4483,8 +4495,11 @@
       <c r="M2" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="12" t="s">
         <v>886</v>
       </c>
@@ -4495,37 +4510,40 @@
         <v>0</v>
       </c>
       <c r="D3" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E3" s="12">
         <v>-200</v>
       </c>
-      <c r="E3" s="12">
+      <c r="F3" s="12">
         <v>-1000</v>
       </c>
-      <c r="F3" s="12">
+      <c r="G3" s="12">
         <v>-2000</v>
       </c>
-      <c r="G3" s="12">
+      <c r="H3" s="12">
         <v>-20000</v>
       </c>
-      <c r="H3" s="12">
+      <c r="I3" s="12">
         <v>-100000</v>
       </c>
-      <c r="I3" s="12">
+      <c r="J3" s="12">
         <v>-200000</v>
       </c>
-      <c r="J3" s="12">
+      <c r="K3" s="12">
         <v>-600000</v>
       </c>
-      <c r="K3" s="12">
+      <c r="L3" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L3" s="12">
+      <c r="M3" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M3" s="12">
+      <c r="N3" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="12" t="s">
         <v>886</v>
       </c>
@@ -4536,37 +4554,40 @@
         <v>0</v>
       </c>
       <c r="D4" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E4" s="12">
         <v>-200</v>
       </c>
-      <c r="E4" s="12">
+      <c r="F4" s="12">
         <v>-1000</v>
       </c>
-      <c r="F4" s="12">
+      <c r="G4" s="12">
         <v>-2000</v>
       </c>
-      <c r="G4" s="12">
+      <c r="H4" s="12">
         <v>-20000</v>
       </c>
-      <c r="H4" s="12">
+      <c r="I4" s="12">
         <v>-100000</v>
       </c>
-      <c r="I4" s="12">
+      <c r="J4" s="12">
         <v>-200000</v>
       </c>
-      <c r="J4" s="12">
+      <c r="K4" s="12">
         <v>-600000</v>
       </c>
-      <c r="K4" s="12">
+      <c r="L4" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L4" s="12">
+      <c r="M4" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M4" s="12">
+      <c r="N4" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="12" t="s">
         <v>887</v>
       </c>
@@ -4606,8 +4627,11 @@
       <c r="M5" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="12" t="s">
         <v>887</v>
       </c>
@@ -4618,37 +4642,40 @@
         <v>0</v>
       </c>
       <c r="D6" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E6" s="12">
         <v>-200</v>
       </c>
-      <c r="E6" s="12">
+      <c r="F6" s="12">
         <v>-1000</v>
       </c>
-      <c r="F6" s="12">
+      <c r="G6" s="12">
         <v>-2000</v>
       </c>
-      <c r="G6" s="12">
+      <c r="H6" s="12">
         <v>-20000</v>
       </c>
-      <c r="H6" s="12">
+      <c r="I6" s="12">
         <v>-100000</v>
       </c>
-      <c r="I6" s="12">
+      <c r="J6" s="12">
         <v>-200000</v>
       </c>
-      <c r="J6" s="12">
+      <c r="K6" s="12">
         <v>-600000</v>
       </c>
-      <c r="K6" s="12">
+      <c r="L6" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L6" s="12">
+      <c r="M6" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M6" s="12">
+      <c r="N6" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
         <v>887</v>
       </c>
@@ -4659,37 +4686,40 @@
         <v>0</v>
       </c>
       <c r="D7" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E7" s="12">
         <v>-200</v>
       </c>
-      <c r="E7" s="12">
+      <c r="F7" s="12">
         <v>-1000</v>
       </c>
-      <c r="F7" s="12">
+      <c r="G7" s="12">
         <v>-2000</v>
       </c>
-      <c r="G7" s="12">
+      <c r="H7" s="12">
         <v>-20000</v>
       </c>
-      <c r="H7" s="12">
+      <c r="I7" s="12">
         <v>-100000</v>
       </c>
-      <c r="I7" s="12">
+      <c r="J7" s="12">
         <v>-200000</v>
       </c>
-      <c r="J7" s="12">
+      <c r="K7" s="12">
         <v>-600000</v>
       </c>
-      <c r="K7" s="12">
+      <c r="L7" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L7" s="12">
+      <c r="M7" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M7" s="12">
+      <c r="N7" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
         <v>888</v>
       </c>
@@ -4729,8 +4759,11 @@
       <c r="M8" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
         <v>888</v>
       </c>
@@ -4741,37 +4774,40 @@
         <v>0</v>
       </c>
       <c r="D9" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E9" s="12">
         <v>-200</v>
       </c>
-      <c r="E9" s="12">
+      <c r="F9" s="12">
         <v>-1000</v>
       </c>
-      <c r="F9" s="12">
+      <c r="G9" s="12">
         <v>-2000</v>
       </c>
-      <c r="G9" s="12">
+      <c r="H9" s="12">
         <v>-20000</v>
       </c>
-      <c r="H9" s="12">
+      <c r="I9" s="12">
         <v>-100000</v>
       </c>
-      <c r="I9" s="12">
+      <c r="J9" s="12">
         <v>-200000</v>
       </c>
-      <c r="J9" s="12">
+      <c r="K9" s="12">
         <v>-600000</v>
       </c>
-      <c r="K9" s="12">
+      <c r="L9" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L9" s="12">
+      <c r="M9" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M9" s="12">
+      <c r="N9" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
         <v>888</v>
       </c>
@@ -4782,37 +4818,40 @@
         <v>0</v>
       </c>
       <c r="D10" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E10" s="12">
         <v>-200</v>
       </c>
-      <c r="E10" s="12">
+      <c r="F10" s="12">
         <v>-1000</v>
       </c>
-      <c r="F10" s="12">
+      <c r="G10" s="12">
         <v>-2000</v>
       </c>
-      <c r="G10" s="12">
+      <c r="H10" s="12">
         <v>-20000</v>
       </c>
-      <c r="H10" s="12">
+      <c r="I10" s="12">
         <v>-100000</v>
       </c>
-      <c r="I10" s="12">
+      <c r="J10" s="12">
         <v>-200000</v>
       </c>
-      <c r="J10" s="12">
+      <c r="K10" s="12">
         <v>-600000</v>
       </c>
-      <c r="K10" s="12">
+      <c r="L10" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L10" s="12">
+      <c r="M10" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M10" s="12">
+      <c r="N10" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
         <v>889</v>
       </c>
@@ -4852,8 +4891,11 @@
       <c r="M11" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
         <v>889</v>
       </c>
@@ -4864,37 +4906,40 @@
         <v>0</v>
       </c>
       <c r="D12" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E12" s="12">
         <v>-200</v>
       </c>
-      <c r="E12" s="12">
+      <c r="F12" s="12">
         <v>-1000</v>
       </c>
-      <c r="F12" s="12">
+      <c r="G12" s="12">
         <v>-2000</v>
       </c>
-      <c r="G12" s="12">
+      <c r="H12" s="12">
         <v>-20000</v>
       </c>
-      <c r="H12" s="12">
+      <c r="I12" s="12">
         <v>-100000</v>
       </c>
-      <c r="I12" s="12">
+      <c r="J12" s="12">
         <v>-200000</v>
       </c>
-      <c r="J12" s="12">
+      <c r="K12" s="12">
         <v>-600000</v>
       </c>
-      <c r="K12" s="12">
+      <c r="L12" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L12" s="12">
+      <c r="M12" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M12" s="12">
+      <c r="N12" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
         <v>889</v>
       </c>
@@ -4905,37 +4950,40 @@
         <v>0</v>
       </c>
       <c r="D13" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E13" s="12">
         <v>-200</v>
       </c>
-      <c r="E13" s="12">
+      <c r="F13" s="12">
         <v>-1000</v>
       </c>
-      <c r="F13" s="12">
+      <c r="G13" s="12">
         <v>-2000</v>
       </c>
-      <c r="G13" s="12">
+      <c r="H13" s="12">
         <v>-20000</v>
       </c>
-      <c r="H13" s="12">
+      <c r="I13" s="12">
         <v>-100000</v>
       </c>
-      <c r="I13" s="12">
+      <c r="J13" s="12">
         <v>-200000</v>
       </c>
-      <c r="J13" s="12">
+      <c r="K13" s="12">
         <v>-600000</v>
       </c>
-      <c r="K13" s="12">
+      <c r="L13" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L13" s="12">
+      <c r="M13" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M13" s="12">
+      <c r="N13" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
         <v>890</v>
       </c>
@@ -4975,8 +5023,11 @@
       <c r="M14" s="12">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
         <v>890</v>
       </c>
@@ -4987,37 +5038,40 @@
         <v>0</v>
       </c>
       <c r="D15" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E15" s="12">
         <v>-200</v>
       </c>
-      <c r="E15" s="12">
+      <c r="F15" s="12">
         <v>-1000</v>
       </c>
-      <c r="F15" s="12">
+      <c r="G15" s="12">
         <v>-2000</v>
       </c>
-      <c r="G15" s="12">
+      <c r="H15" s="12">
         <v>-20000</v>
       </c>
-      <c r="H15" s="12">
+      <c r="I15" s="12">
         <v>-100000</v>
       </c>
-      <c r="I15" s="12">
+      <c r="J15" s="12">
         <v>-200000</v>
       </c>
-      <c r="J15" s="12">
+      <c r="K15" s="12">
         <v>-600000</v>
       </c>
-      <c r="K15" s="12">
+      <c r="L15" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L15" s="12">
+      <c r="M15" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M15" s="12">
+      <c r="N15" s="12">
         <v>-4800000</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
         <v>890</v>
       </c>
@@ -5028,33 +5082,36 @@
         <v>0</v>
       </c>
       <c r="D16" s="12">
+        <v>-100</v>
+      </c>
+      <c r="E16" s="12">
         <v>-200</v>
       </c>
-      <c r="E16" s="12">
+      <c r="F16" s="12">
         <v>-1000</v>
       </c>
-      <c r="F16" s="12">
+      <c r="G16" s="12">
         <v>-2000</v>
       </c>
-      <c r="G16" s="12">
+      <c r="H16" s="12">
         <v>-20000</v>
       </c>
-      <c r="H16" s="12">
+      <c r="I16" s="12">
         <v>-100000</v>
       </c>
-      <c r="I16" s="12">
+      <c r="J16" s="12">
         <v>-200000</v>
       </c>
-      <c r="J16" s="12">
+      <c r="K16" s="12">
         <v>-600000</v>
       </c>
-      <c r="K16" s="12">
+      <c r="L16" s="12">
         <v>-1200000</v>
       </c>
-      <c r="L16" s="12">
+      <c r="M16" s="12">
         <v>-2400000</v>
       </c>
-      <c r="M16" s="12">
+      <c r="N16" s="12">
         <v>-4800000</v>
       </c>
     </row>
@@ -5290,6 +5347,7 @@
       <c r="F44" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1659BF11-04CB-4C73-B3BA-9602F578E27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F187C1-EA2D-43FA-82CF-CA59FEFE8AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1440" windowWidth="21600" windowHeight="11423" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2509" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2510" uniqueCount="1194">
   <si>
     <t>nlay</t>
   </si>
@@ -5980,7 +5980,7 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="3" width="17.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="17.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -5993,6 +5993,9 @@
       <c r="C1" s="12" t="s">
         <v>920</v>
       </c>
+      <c r="D1" s="12" t="s">
+        <v>1066</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="16" t="s">
@@ -6004,7 +6007,9 @@
       <c r="C2" s="13">
         <v>86.4</v>
       </c>
-      <c r="D2" s="13"/>
+      <c r="D2" s="13">
+        <v>8.64</v>
+      </c>
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
@@ -6020,7 +6025,9 @@
       <c r="C3" s="14">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="11">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
@@ -6036,7 +6043,9 @@
       <c r="C4" s="13">
         <v>86.4</v>
       </c>
-      <c r="D4" s="13"/>
+      <c r="D4" s="13">
+        <v>8.64</v>
+      </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
@@ -6052,7 +6061,9 @@
       <c r="C5" s="14">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="D5" s="13"/>
+      <c r="D5" s="11">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
@@ -6068,7 +6079,9 @@
       <c r="C6" s="13">
         <v>86.4</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="13">
+        <v>8.64</v>
+      </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
@@ -6084,7 +6097,9 @@
       <c r="C7" s="13">
         <v>86.4</v>
       </c>
-      <c r="D7" s="13"/>
+      <c r="D7" s="13">
+        <v>8.64</v>
+      </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
@@ -6100,7 +6115,9 @@
       <c r="C8" s="14">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="D8" s="13"/>
+      <c r="D8" s="11">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
@@ -6116,7 +6133,9 @@
       <c r="C9" s="13">
         <v>86.4</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="13">
+        <v>8.64</v>
+      </c>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
@@ -6132,7 +6151,9 @@
       <c r="C10" s="14">
         <v>8.6399999999999999E-9</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="11">
+        <v>8.6400000000000006E-8</v>
+      </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -6148,7 +6169,9 @@
       <c r="C11" s="13">
         <v>86.4</v>
       </c>
-      <c r="D11" s="13"/>
+      <c r="D11" s="13">
+        <v>8.64</v>
+      </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
       <c r="G11" s="13"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{333348F1-96BA-4B7F-A3F1-49BDF61962B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3DF822-B830-401D-A82B-04341B42C5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -5443,7 +5443,7 @@
         <v>264</v>
       </c>
       <c r="B2" s="18">
-        <v>-6.666666666666667</v>
+        <v>-7</v>
       </c>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -5485,7 +5485,7 @@
         <v>265</v>
       </c>
       <c r="B3" s="18">
-        <v>-55.666666666666664</v>
+        <v>-56</v>
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="18"/>
@@ -5522,7 +5522,7 @@
         <v>266</v>
       </c>
       <c r="B4" s="18">
-        <v>-536.33333333333337</v>
+        <v>-536</v>
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="18"/>
@@ -5601,7 +5601,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="18">
-        <v>-53131.666666666664</v>
+        <v>-53132</v>
       </c>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -5685,7 +5685,7 @@
         <v>269</v>
       </c>
       <c r="B8" s="18">
-        <v>-66.666666666666671</v>
+        <v>-67</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -5863,7 +5863,7 @@
         <v>274</v>
       </c>
       <c r="B14" s="18">
-        <v>-663.66666666666663</v>
+        <v>-664</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -5873,7 +5873,7 @@
         <v>275</v>
       </c>
       <c r="B15" s="18">
-        <v>-5556.666666666667</v>
+        <v>-5557</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -5903,7 +5903,7 @@
         <v>292</v>
       </c>
       <c r="B18" s="18">
-        <v>-127.66666666666667</v>
+        <v>-128</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -5913,7 +5913,7 @@
         <v>293</v>
       </c>
       <c r="B19" s="18">
-        <v>-898.33333333333337</v>
+        <v>-898</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -5933,7 +5933,7 @@
         <v>295</v>
       </c>
       <c r="B21" s="18">
-        <v>-55480.666666666664</v>
+        <v>-55481</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -5963,7 +5963,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="18">
-        <v>-1274.3333333333333</v>
+        <v>-1274</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -5973,7 +5973,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="18">
-        <v>-8967.3333333333339</v>
+        <v>-8967</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -5993,7 +5993,7 @@
         <v>296</v>
       </c>
       <c r="B27" s="18">
-        <v>-150.66666666666666</v>
+        <v>-151</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -6023,7 +6023,7 @@
         <v>299</v>
       </c>
       <c r="B30" s="18">
-        <v>-12728.666666666666</v>
+        <v>-12729</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -6033,7 +6033,7 @@
         <v>300</v>
       </c>
       <c r="B31" s="18">
-        <v>-89361.333333333328</v>
+        <v>-89361</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -6043,7 +6043,7 @@
         <v>245</v>
       </c>
       <c r="B32" s="18">
-        <v>-458.33333333333331</v>
+        <v>-458</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
@@ -6053,7 +6053,7 @@
         <v>246</v>
       </c>
       <c r="B33" s="18">
-        <v>-1468.6666666666667</v>
+        <v>-1469</v>
       </c>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -6063,7 +6063,7 @@
         <v>247</v>
       </c>
       <c r="B34" s="18">
-        <v>-4507.333333333333</v>
+        <v>-4507</v>
       </c>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
@@ -6073,7 +6073,7 @@
         <v>248</v>
       </c>
       <c r="B35" s="18">
-        <v>-20684.333333333332</v>
+        <v>-20684</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -6083,7 +6083,7 @@
         <v>249</v>
       </c>
       <c r="B36" s="18">
-        <v>-126543.33333333333</v>
+        <v>-126543</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7969EB1-2877-467B-B226-29ECA8BC9604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641C5A-12B4-4CA8-9971-CE19F5130DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="1217">
   <si>
     <t>nlay</t>
   </si>
@@ -3695,6 +3695,9 @@
   </si>
   <si>
     <t>12_99_130</t>
+  </si>
+  <si>
+    <t>qv_11</t>
   </si>
 </sst>
 </file>
@@ -4221,7 +4224,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="8" width="10.73046875" bestFit="1" customWidth="1"/>
@@ -4229,7 +4232,7 @@
     <col min="12" max="12" width="11.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>89</v>
       </c>
@@ -4239,35 +4242,38 @@
       <c r="C1" t="s">
         <v>114</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="M1" s="11" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>91</v>
       </c>
@@ -4290,22 +4296,25 @@
         <v>-10000</v>
       </c>
       <c r="H2" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I2" s="11">
         <v>-50000</v>
       </c>
-      <c r="I2" s="11">
+      <c r="J2" s="11">
         <v>-100000</v>
       </c>
-      <c r="J2" s="11">
+      <c r="K2" s="11">
         <v>-200000</v>
       </c>
-      <c r="K2" s="11">
+      <c r="L2" s="11">
         <v>-500000</v>
       </c>
-      <c r="L2" s="11">
+      <c r="M2" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -4328,22 +4337,25 @@
         <v>-10000</v>
       </c>
       <c r="H3" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I3" s="11">
         <v>-50000</v>
       </c>
-      <c r="I3" s="11">
+      <c r="J3" s="11">
         <v>-100000</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="11">
         <v>-200000</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <v>-500000</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -4366,22 +4378,25 @@
         <v>-10000</v>
       </c>
       <c r="H4" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I4" s="11">
         <v>-50000</v>
       </c>
-      <c r="I4" s="11">
+      <c r="J4" s="11">
         <v>-100000</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="11">
         <v>-200000</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="11">
         <v>-500000</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -4404,22 +4419,25 @@
         <v>-10000</v>
       </c>
       <c r="H5" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I5" s="11">
         <v>-50000</v>
       </c>
-      <c r="I5" s="11">
+      <c r="J5" s="11">
         <v>-100000</v>
       </c>
-      <c r="J5" s="11">
+      <c r="K5" s="11">
         <v>-200000</v>
       </c>
-      <c r="K5" s="11">
+      <c r="L5" s="11">
         <v>-500000</v>
       </c>
-      <c r="L5" s="11">
+      <c r="M5" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -4442,22 +4460,25 @@
         <v>-10000</v>
       </c>
       <c r="H6" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I6" s="11">
         <v>-50000</v>
       </c>
-      <c r="I6" s="11">
+      <c r="J6" s="11">
         <v>-100000</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>-200000</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>-500000</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
         <v>147</v>
       </c>
@@ -4480,22 +4501,25 @@
         <v>-10000</v>
       </c>
       <c r="H7" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I7" s="11">
         <v>-50000</v>
       </c>
-      <c r="I7" s="11">
+      <c r="J7" s="11">
         <v>-100000</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>-200000</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>-500000</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>398</v>
       </c>
@@ -4518,22 +4542,25 @@
         <v>-10000</v>
       </c>
       <c r="H8" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I8" s="11">
         <v>-50000</v>
       </c>
-      <c r="I8" s="11">
+      <c r="J8" s="11">
         <v>-100000</v>
       </c>
-      <c r="J8" s="11">
+      <c r="K8" s="11">
         <v>-200000</v>
       </c>
-      <c r="K8" s="11">
+      <c r="L8" s="11">
         <v>-500000</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M8" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>399</v>
       </c>
@@ -4556,22 +4583,25 @@
         <v>-10000</v>
       </c>
       <c r="H9" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I9" s="11">
         <v>-50000</v>
       </c>
-      <c r="I9" s="11">
+      <c r="J9" s="11">
         <v>-100000</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>-200000</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="11">
         <v>-500000</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
         <v>400</v>
       </c>
@@ -4594,22 +4624,25 @@
         <v>-10000</v>
       </c>
       <c r="H10" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I10" s="11">
         <v>-50000</v>
       </c>
-      <c r="I10" s="11">
+      <c r="J10" s="11">
         <v>-100000</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>-200000</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="11">
         <v>-500000</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
         <v>401</v>
       </c>
@@ -4632,22 +4665,25 @@
         <v>-10000</v>
       </c>
       <c r="H11" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I11" s="11">
         <v>-50000</v>
       </c>
-      <c r="I11" s="11">
+      <c r="J11" s="11">
         <v>-100000</v>
       </c>
-      <c r="J11" s="11">
+      <c r="K11" s="11">
         <v>-200000</v>
       </c>
-      <c r="K11" s="11">
+      <c r="L11" s="11">
         <v>-500000</v>
       </c>
-      <c r="L11" s="11">
+      <c r="M11" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>402</v>
       </c>
@@ -4670,22 +4706,25 @@
         <v>-10000</v>
       </c>
       <c r="H12" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I12" s="11">
         <v>-50000</v>
       </c>
-      <c r="I12" s="11">
+      <c r="J12" s="11">
         <v>-100000</v>
       </c>
-      <c r="J12" s="11">
+      <c r="K12" s="11">
         <v>-200000</v>
       </c>
-      <c r="K12" s="11">
+      <c r="L12" s="11">
         <v>-500000</v>
       </c>
-      <c r="L12" s="11">
+      <c r="M12" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>403</v>
       </c>
@@ -4708,22 +4747,25 @@
         <v>-10000</v>
       </c>
       <c r="H13" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I13" s="11">
         <v>-50000</v>
       </c>
-      <c r="I13" s="11">
+      <c r="J13" s="11">
         <v>-100000</v>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="11">
         <v>-200000</v>
       </c>
-      <c r="K13" s="11">
+      <c r="L13" s="11">
         <v>-500000</v>
       </c>
-      <c r="L13" s="11">
+      <c r="M13" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>404</v>
       </c>
@@ -4746,22 +4788,25 @@
         <v>-10000</v>
       </c>
       <c r="H14" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I14" s="11">
         <v>-50000</v>
       </c>
-      <c r="I14" s="11">
+      <c r="J14" s="11">
         <v>-100000</v>
       </c>
-      <c r="J14" s="11">
+      <c r="K14" s="11">
         <v>-200000</v>
       </c>
-      <c r="K14" s="11">
+      <c r="L14" s="11">
         <v>-500000</v>
       </c>
-      <c r="L14" s="11">
+      <c r="M14" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>405</v>
       </c>
@@ -4784,22 +4829,25 @@
         <v>-10000</v>
       </c>
       <c r="H15" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I15" s="11">
         <v>-50000</v>
       </c>
-      <c r="I15" s="11">
+      <c r="J15" s="11">
         <v>-100000</v>
       </c>
-      <c r="J15" s="11">
+      <c r="K15" s="11">
         <v>-200000</v>
       </c>
-      <c r="K15" s="11">
+      <c r="L15" s="11">
         <v>-500000</v>
       </c>
-      <c r="L15" s="11">
+      <c r="M15" s="11">
         <v>-1000000</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>406</v>
       </c>
@@ -4822,18 +4870,21 @@
         <v>-10000</v>
       </c>
       <c r="H16" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="I16" s="11">
         <v>-50000</v>
       </c>
-      <c r="I16" s="11">
+      <c r="J16" s="11">
         <v>-100000</v>
       </c>
-      <c r="J16" s="11">
+      <c r="K16" s="11">
         <v>-200000</v>
       </c>
-      <c r="K16" s="11">
+      <c r="L16" s="11">
         <v>-500000</v>
       </c>
-      <c r="L16" s="11">
+      <c r="M16" s="11">
         <v>-1000000</v>
       </c>
     </row>
@@ -4870,16 +4921,17 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="12.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.9296875" style="11" customWidth="1"/>
     <col min="6" max="6" width="10.59765625" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.9296875" style="11" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" style="11"/>
+    <col min="11" max="11" width="10.9296875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>89</v>
       </c>
@@ -4919,8 +4971,11 @@
       <c r="M1" s="11" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="N1" s="11" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A2" s="11" t="s">
         <v>91</v>
       </c>
@@ -4960,7 +5015,9 @@
       <c r="M2" s="11">
         <v>0</v>
       </c>
-      <c r="P2" s="11"/>
+      <c r="N2" s="11">
+        <v>0</v>
+      </c>
       <c r="Q2" s="11"/>
       <c r="R2" s="11"/>
       <c r="S2" s="11"/>
@@ -4973,8 +5030,9 @@
       <c r="Z2" s="11"/>
       <c r="AA2" s="11"/>
       <c r="AB2" s="11"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC2" s="11"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
         <v>91</v>
       </c>
@@ -5000,21 +5058,23 @@
         <v>-10000</v>
       </c>
       <c r="I3" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J3" s="11">
         <v>-50000</v>
       </c>
-      <c r="J3" s="11">
+      <c r="K3" s="11">
         <v>-100000</v>
       </c>
-      <c r="K3" s="11">
+      <c r="L3" s="11">
         <v>-200000</v>
       </c>
-      <c r="L3" s="11">
+      <c r="M3" s="11">
         <v>-500000</v>
       </c>
-      <c r="M3" s="11">
+      <c r="N3" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O3" s="11"/>
       <c r="P3" s="11"/>
       <c r="Q3" s="11"/>
       <c r="R3" s="11"/>
@@ -5028,8 +5088,9 @@
       <c r="Z3" s="11"/>
       <c r="AA3" s="11"/>
       <c r="AB3" s="11"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC3" s="11"/>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>91</v>
       </c>
@@ -5055,21 +5116,23 @@
         <v>-10000</v>
       </c>
       <c r="I4" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J4" s="11">
         <v>-50000</v>
       </c>
-      <c r="J4" s="11">
+      <c r="K4" s="11">
         <v>-100000</v>
       </c>
-      <c r="K4" s="11">
+      <c r="L4" s="11">
         <v>-200000</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="11">
         <v>-500000</v>
       </c>
-      <c r="M4" s="11">
+      <c r="N4" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="11"/>
@@ -5083,8 +5146,9 @@
       <c r="Z4" s="11"/>
       <c r="AA4" s="11"/>
       <c r="AB4" s="11"/>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC4" s="11"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
         <v>92</v>
       </c>
@@ -5124,7 +5188,9 @@
       <c r="M5" s="11">
         <v>0</v>
       </c>
-      <c r="O5" s="11"/>
+      <c r="N5" s="11">
+        <v>0</v>
+      </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11"/>
       <c r="R5" s="11"/>
@@ -5138,8 +5204,9 @@
       <c r="Z5" s="11"/>
       <c r="AA5" s="11"/>
       <c r="AB5" s="11"/>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC5" s="11"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>92</v>
       </c>
@@ -5165,21 +5232,23 @@
         <v>-10000</v>
       </c>
       <c r="I6" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J6" s="11">
         <v>-50000</v>
       </c>
-      <c r="J6" s="11">
+      <c r="K6" s="11">
         <v>-100000</v>
       </c>
-      <c r="K6" s="11">
+      <c r="L6" s="11">
         <v>-200000</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <v>-500000</v>
       </c>
-      <c r="M6" s="11">
+      <c r="N6" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O6" s="11"/>
       <c r="P6" s="11"/>
       <c r="Q6" s="11"/>
       <c r="R6" s="11"/>
@@ -5193,8 +5262,9 @@
       <c r="Z6" s="11"/>
       <c r="AA6" s="11"/>
       <c r="AB6" s="11"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC6" s="11"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A7" s="11" t="s">
         <v>92</v>
       </c>
@@ -5220,21 +5290,23 @@
         <v>-10000</v>
       </c>
       <c r="I7" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J7" s="11">
         <v>-50000</v>
       </c>
-      <c r="J7" s="11">
+      <c r="K7" s="11">
         <v>-100000</v>
       </c>
-      <c r="K7" s="11">
+      <c r="L7" s="11">
         <v>-200000</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <v>-500000</v>
       </c>
-      <c r="M7" s="11">
+      <c r="N7" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O7" s="11"/>
       <c r="P7" s="11"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="11"/>
@@ -5248,8 +5320,9 @@
       <c r="Z7" s="11"/>
       <c r="AA7" s="11"/>
       <c r="AB7" s="11"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC7" s="11"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A8" s="11" t="s">
         <v>93</v>
       </c>
@@ -5289,7 +5362,9 @@
       <c r="M8" s="11">
         <v>0</v>
       </c>
-      <c r="O8" s="11"/>
+      <c r="N8" s="11">
+        <v>0</v>
+      </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11"/>
@@ -5303,8 +5378,9 @@
       <c r="Z8" s="11"/>
       <c r="AA8" s="11"/>
       <c r="AB8" s="11"/>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC8" s="11"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A9" s="11" t="s">
         <v>93</v>
       </c>
@@ -5330,21 +5406,23 @@
         <v>-10000</v>
       </c>
       <c r="I9" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J9" s="11">
         <v>-50000</v>
       </c>
-      <c r="J9" s="11">
+      <c r="K9" s="11">
         <v>-100000</v>
       </c>
-      <c r="K9" s="11">
+      <c r="L9" s="11">
         <v>-200000</v>
       </c>
-      <c r="L9" s="11">
+      <c r="M9" s="11">
         <v>-500000</v>
       </c>
-      <c r="M9" s="11">
+      <c r="N9" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O9" s="11"/>
       <c r="P9" s="11"/>
       <c r="Q9" s="11"/>
       <c r="R9" s="11"/>
@@ -5358,8 +5436,9 @@
       <c r="Z9" s="11"/>
       <c r="AA9" s="11"/>
       <c r="AB9" s="11"/>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC9" s="11"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A10" s="11" t="s">
         <v>93</v>
       </c>
@@ -5385,21 +5464,23 @@
         <v>-10000</v>
       </c>
       <c r="I10" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J10" s="11">
         <v>-50000</v>
       </c>
-      <c r="J10" s="11">
+      <c r="K10" s="11">
         <v>-100000</v>
       </c>
-      <c r="K10" s="11">
+      <c r="L10" s="11">
         <v>-200000</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M10" s="11">
         <v>-500000</v>
       </c>
-      <c r="M10" s="11">
+      <c r="N10" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O10" s="11"/>
       <c r="P10" s="11"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
@@ -5413,8 +5494,9 @@
       <c r="Z10" s="11"/>
       <c r="AA10" s="11"/>
       <c r="AB10" s="11"/>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC10" s="11"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
         <v>94</v>
       </c>
@@ -5454,7 +5536,9 @@
       <c r="M11" s="11">
         <v>0</v>
       </c>
-      <c r="O11" s="11"/>
+      <c r="N11" s="11">
+        <v>0</v>
+      </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="11"/>
@@ -5468,8 +5552,9 @@
       <c r="Z11" s="11"/>
       <c r="AA11" s="11"/>
       <c r="AB11" s="11"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC11" s="11"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>94</v>
       </c>
@@ -5495,21 +5580,23 @@
         <v>-10000</v>
       </c>
       <c r="I12" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J12" s="11">
         <v>-50000</v>
       </c>
-      <c r="J12" s="11">
+      <c r="K12" s="11">
         <v>-100000</v>
       </c>
-      <c r="K12" s="11">
+      <c r="L12" s="11">
         <v>-200000</v>
       </c>
-      <c r="L12" s="11">
+      <c r="M12" s="11">
         <v>-500000</v>
       </c>
-      <c r="M12" s="11">
+      <c r="N12" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O12" s="11"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="11"/>
@@ -5523,8 +5610,9 @@
       <c r="Z12" s="11"/>
       <c r="AA12" s="11"/>
       <c r="AB12" s="11"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC12" s="11"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>94</v>
       </c>
@@ -5550,21 +5638,23 @@
         <v>-10000</v>
       </c>
       <c r="I13" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J13" s="11">
         <v>-50000</v>
       </c>
-      <c r="J13" s="11">
+      <c r="K13" s="11">
         <v>-100000</v>
       </c>
-      <c r="K13" s="11">
+      <c r="L13" s="11">
         <v>-200000</v>
       </c>
-      <c r="L13" s="11">
+      <c r="M13" s="11">
         <v>-500000</v>
       </c>
-      <c r="M13" s="11">
+      <c r="N13" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O13" s="11"/>
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="11"/>
@@ -5578,8 +5668,9 @@
       <c r="Z13" s="11"/>
       <c r="AA13" s="11"/>
       <c r="AB13" s="11"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC13" s="11"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A14" s="11" t="s">
         <v>95</v>
       </c>
@@ -5619,7 +5710,9 @@
       <c r="M14" s="11">
         <v>0</v>
       </c>
-      <c r="O14" s="11"/>
+      <c r="N14" s="11">
+        <v>0</v>
+      </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="11"/>
@@ -5633,8 +5726,9 @@
       <c r="Z14" s="11"/>
       <c r="AA14" s="11"/>
       <c r="AB14" s="11"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC14" s="11"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>95</v>
       </c>
@@ -5660,21 +5754,23 @@
         <v>-10000</v>
       </c>
       <c r="I15" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J15" s="11">
         <v>-50000</v>
       </c>
-      <c r="J15" s="11">
+      <c r="K15" s="11">
         <v>-100000</v>
       </c>
-      <c r="K15" s="11">
+      <c r="L15" s="11">
         <v>-200000</v>
       </c>
-      <c r="L15" s="11">
+      <c r="M15" s="11">
         <v>-500000</v>
       </c>
-      <c r="M15" s="11">
+      <c r="N15" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O15" s="11"/>
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="11"/>
@@ -5688,8 +5784,9 @@
       <c r="Z15" s="11"/>
       <c r="AA15" s="11"/>
       <c r="AB15" s="11"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC15" s="11"/>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>95</v>
       </c>
@@ -5715,21 +5812,23 @@
         <v>-10000</v>
       </c>
       <c r="I16" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J16" s="11">
         <v>-50000</v>
       </c>
-      <c r="J16" s="11">
+      <c r="K16" s="11">
         <v>-100000</v>
       </c>
-      <c r="K16" s="11">
+      <c r="L16" s="11">
         <v>-200000</v>
       </c>
-      <c r="L16" s="11">
+      <c r="M16" s="11">
         <v>-500000</v>
       </c>
-      <c r="M16" s="11">
+      <c r="N16" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O16" s="11"/>
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="11"/>
@@ -5743,8 +5842,9 @@
       <c r="Z16" s="11"/>
       <c r="AA16" s="11"/>
       <c r="AB16" s="11"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC16" s="11"/>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A17" s="11" t="s">
         <v>147</v>
       </c>
@@ -5784,7 +5884,9 @@
       <c r="M17" s="11">
         <v>0</v>
       </c>
-      <c r="O17" s="11"/>
+      <c r="N17" s="11">
+        <v>0</v>
+      </c>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
       <c r="R17" s="11"/>
@@ -5798,8 +5900,9 @@
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
       <c r="AB17" s="11"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC17" s="11"/>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A18" s="11" t="s">
         <v>147</v>
       </c>
@@ -5825,22 +5928,24 @@
         <v>-10000</v>
       </c>
       <c r="I18" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J18" s="11">
         <v>-50000</v>
       </c>
-      <c r="J18" s="11">
+      <c r="K18" s="11">
         <v>-100000</v>
       </c>
-      <c r="K18" s="11">
+      <c r="L18" s="11">
         <v>-200000</v>
       </c>
-      <c r="L18" s="11">
+      <c r="M18" s="11">
         <v>-500000</v>
       </c>
-      <c r="M18" s="11">
+      <c r="N18" s="11">
         <v>-1000000</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="11"/>
+      <c r="O18" s="2"/>
       <c r="P18" s="11"/>
       <c r="Q18" s="11"/>
       <c r="R18" s="11"/>
@@ -5854,8 +5959,9 @@
       <c r="Z18" s="11"/>
       <c r="AA18" s="11"/>
       <c r="AB18" s="11"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC18" s="11"/>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A19" s="11" t="s">
         <v>147</v>
       </c>
@@ -5881,21 +5987,23 @@
         <v>-10000</v>
       </c>
       <c r="I19" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J19" s="11">
         <v>-50000</v>
       </c>
-      <c r="J19" s="11">
+      <c r="K19" s="11">
         <v>-100000</v>
       </c>
-      <c r="K19" s="11">
+      <c r="L19" s="11">
         <v>-200000</v>
       </c>
-      <c r="L19" s="11">
+      <c r="M19" s="11">
         <v>-500000</v>
       </c>
-      <c r="M19" s="11">
+      <c r="N19" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O19" s="11"/>
       <c r="P19" s="11"/>
       <c r="Q19" s="11"/>
       <c r="R19" s="11"/>
@@ -5909,8 +6017,9 @@
       <c r="Z19" s="11"/>
       <c r="AA19" s="11"/>
       <c r="AB19" s="11"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC19" s="11"/>
+    </row>
+    <row r="20" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A20" s="11" t="s">
         <v>398</v>
       </c>
@@ -5950,7 +6059,9 @@
       <c r="M20" s="11">
         <v>0</v>
       </c>
-      <c r="O20" s="11"/>
+      <c r="N20" s="11">
+        <v>0</v>
+      </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11"/>
       <c r="R20" s="11"/>
@@ -5964,8 +6075,9 @@
       <c r="Z20" s="11"/>
       <c r="AA20" s="11"/>
       <c r="AB20" s="11"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC20" s="11"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A21" s="11" t="s">
         <v>398</v>
       </c>
@@ -5991,21 +6103,23 @@
         <v>-10000</v>
       </c>
       <c r="I21" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J21" s="11">
         <v>-50000</v>
       </c>
-      <c r="J21" s="11">
+      <c r="K21" s="11">
         <v>-100000</v>
       </c>
-      <c r="K21" s="11">
+      <c r="L21" s="11">
         <v>-200000</v>
       </c>
-      <c r="L21" s="11">
+      <c r="M21" s="11">
         <v>-500000</v>
       </c>
-      <c r="M21" s="11">
+      <c r="N21" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O21" s="11"/>
       <c r="P21" s="11"/>
       <c r="Q21" s="11"/>
       <c r="R21" s="11"/>
@@ -6019,8 +6133,9 @@
       <c r="Z21" s="11"/>
       <c r="AA21" s="11"/>
       <c r="AB21" s="11"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC21" s="11"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A22" s="11" t="s">
         <v>398</v>
       </c>
@@ -6046,21 +6161,23 @@
         <v>-10000</v>
       </c>
       <c r="I22" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J22" s="11">
         <v>-50000</v>
       </c>
-      <c r="J22" s="11">
+      <c r="K22" s="11">
         <v>-100000</v>
       </c>
-      <c r="K22" s="11">
+      <c r="L22" s="11">
         <v>-200000</v>
       </c>
-      <c r="L22" s="11">
+      <c r="M22" s="11">
         <v>-500000</v>
       </c>
-      <c r="M22" s="11">
+      <c r="N22" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O22" s="11"/>
       <c r="P22" s="11"/>
       <c r="Q22" s="11"/>
       <c r="R22" s="11"/>
@@ -6074,8 +6191,9 @@
       <c r="Z22" s="11"/>
       <c r="AA22" s="11"/>
       <c r="AB22" s="11"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC22" s="11"/>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A23" s="11" t="s">
         <v>399</v>
       </c>
@@ -6115,7 +6233,9 @@
       <c r="M23" s="11">
         <v>0</v>
       </c>
-      <c r="O23" s="11"/>
+      <c r="N23" s="11">
+        <v>0</v>
+      </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="11"/>
       <c r="R23" s="11"/>
@@ -6129,8 +6249,9 @@
       <c r="Z23" s="11"/>
       <c r="AA23" s="11"/>
       <c r="AB23" s="11"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC23" s="11"/>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A24" s="11" t="s">
         <v>399</v>
       </c>
@@ -6156,21 +6277,23 @@
         <v>-10000</v>
       </c>
       <c r="I24" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J24" s="11">
         <v>-50000</v>
       </c>
-      <c r="J24" s="11">
+      <c r="K24" s="11">
         <v>-100000</v>
       </c>
-      <c r="K24" s="11">
+      <c r="L24" s="11">
         <v>-200000</v>
       </c>
-      <c r="L24" s="11">
+      <c r="M24" s="11">
         <v>-500000</v>
       </c>
-      <c r="M24" s="11">
+      <c r="N24" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O24" s="11"/>
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
       <c r="R24" s="11"/>
@@ -6184,8 +6307,9 @@
       <c r="Z24" s="11"/>
       <c r="AA24" s="11"/>
       <c r="AB24" s="11"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC24" s="11"/>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A25" s="11" t="s">
         <v>399</v>
       </c>
@@ -6211,21 +6335,23 @@
         <v>-10000</v>
       </c>
       <c r="I25" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J25" s="11">
         <v>-50000</v>
       </c>
-      <c r="J25" s="11">
+      <c r="K25" s="11">
         <v>-100000</v>
       </c>
-      <c r="K25" s="11">
+      <c r="L25" s="11">
         <v>-200000</v>
       </c>
-      <c r="L25" s="11">
+      <c r="M25" s="11">
         <v>-500000</v>
       </c>
-      <c r="M25" s="11">
+      <c r="N25" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O25" s="11"/>
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
@@ -6239,8 +6365,9 @@
       <c r="Z25" s="11"/>
       <c r="AA25" s="11"/>
       <c r="AB25" s="11"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC25" s="11"/>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" s="11" t="s">
         <v>400</v>
       </c>
@@ -6280,7 +6407,9 @@
       <c r="M26" s="11">
         <v>0</v>
       </c>
-      <c r="O26" s="11"/>
+      <c r="N26" s="11">
+        <v>0</v>
+      </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
       <c r="R26" s="11"/>
@@ -6294,8 +6423,9 @@
       <c r="Z26" s="11"/>
       <c r="AA26" s="11"/>
       <c r="AB26" s="11"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC26" s="11"/>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" s="11" t="s">
         <v>400</v>
       </c>
@@ -6321,21 +6451,23 @@
         <v>-10000</v>
       </c>
       <c r="I27" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J27" s="11">
         <v>-50000</v>
       </c>
-      <c r="J27" s="11">
+      <c r="K27" s="11">
         <v>-100000</v>
       </c>
-      <c r="K27" s="11">
+      <c r="L27" s="11">
         <v>-200000</v>
       </c>
-      <c r="L27" s="11">
+      <c r="M27" s="11">
         <v>-500000</v>
       </c>
-      <c r="M27" s="11">
+      <c r="N27" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O27" s="11"/>
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
       <c r="R27" s="11"/>
@@ -6349,8 +6481,9 @@
       <c r="Z27" s="11"/>
       <c r="AA27" s="11"/>
       <c r="AB27" s="11"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC27" s="11"/>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A28" s="11" t="s">
         <v>400</v>
       </c>
@@ -6376,21 +6509,23 @@
         <v>-10000</v>
       </c>
       <c r="I28" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J28" s="11">
         <v>-50000</v>
       </c>
-      <c r="J28" s="11">
+      <c r="K28" s="11">
         <v>-100000</v>
       </c>
-      <c r="K28" s="11">
+      <c r="L28" s="11">
         <v>-200000</v>
       </c>
-      <c r="L28" s="11">
+      <c r="M28" s="11">
         <v>-500000</v>
       </c>
-      <c r="M28" s="11">
+      <c r="N28" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O28" s="11"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
       <c r="R28" s="11"/>
@@ -6404,8 +6539,9 @@
       <c r="Z28" s="11"/>
       <c r="AA28" s="11"/>
       <c r="AB28" s="11"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC28" s="11"/>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A29" s="11" t="s">
         <v>401</v>
       </c>
@@ -6445,7 +6581,9 @@
       <c r="M29" s="11">
         <v>0</v>
       </c>
-      <c r="O29" s="11"/>
+      <c r="N29" s="11">
+        <v>0</v>
+      </c>
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
       <c r="R29" s="11"/>
@@ -6459,8 +6597,9 @@
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
       <c r="AB29" s="11"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC29" s="11"/>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A30" s="11" t="s">
         <v>401</v>
       </c>
@@ -6486,21 +6625,23 @@
         <v>-10000</v>
       </c>
       <c r="I30" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J30" s="11">
         <v>-50000</v>
       </c>
-      <c r="J30" s="11">
+      <c r="K30" s="11">
         <v>-100000</v>
       </c>
-      <c r="K30" s="11">
+      <c r="L30" s="11">
         <v>-200000</v>
       </c>
-      <c r="L30" s="11">
+      <c r="M30" s="11">
         <v>-500000</v>
       </c>
-      <c r="M30" s="11">
+      <c r="N30" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O30" s="11"/>
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
       <c r="R30" s="11"/>
@@ -6514,8 +6655,9 @@
       <c r="Z30" s="11"/>
       <c r="AA30" s="11"/>
       <c r="AB30" s="11"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC30" s="11"/>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A31" s="11" t="s">
         <v>401</v>
       </c>
@@ -6541,21 +6683,23 @@
         <v>-10000</v>
       </c>
       <c r="I31" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J31" s="11">
         <v>-50000</v>
       </c>
-      <c r="J31" s="11">
+      <c r="K31" s="11">
         <v>-100000</v>
       </c>
-      <c r="K31" s="11">
+      <c r="L31" s="11">
         <v>-200000</v>
       </c>
-      <c r="L31" s="11">
+      <c r="M31" s="11">
         <v>-500000</v>
       </c>
-      <c r="M31" s="11">
+      <c r="N31" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O31" s="11"/>
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
       <c r="R31" s="11"/>
@@ -6569,8 +6713,9 @@
       <c r="Z31" s="11"/>
       <c r="AA31" s="11"/>
       <c r="AB31" s="11"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="AC31" s="11"/>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A32" s="11" t="s">
         <v>402</v>
       </c>
@@ -6610,7 +6755,9 @@
       <c r="M32" s="11">
         <v>0</v>
       </c>
-      <c r="O32" s="11"/>
+      <c r="N32" s="11">
+        <v>0</v>
+      </c>
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
       <c r="R32" s="11"/>
@@ -6624,8 +6771,9 @@
       <c r="Z32" s="11"/>
       <c r="AA32" s="11"/>
       <c r="AB32" s="11"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC32" s="11"/>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A33" s="11" t="s">
         <v>402</v>
       </c>
@@ -6651,21 +6799,23 @@
         <v>-10000</v>
       </c>
       <c r="I33" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J33" s="11">
         <v>-50000</v>
       </c>
-      <c r="J33" s="11">
+      <c r="K33" s="11">
         <v>-100000</v>
       </c>
-      <c r="K33" s="11">
+      <c r="L33" s="11">
         <v>-200000</v>
       </c>
-      <c r="L33" s="11">
+      <c r="M33" s="11">
         <v>-500000</v>
       </c>
-      <c r="M33" s="11">
+      <c r="N33" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O33" s="11"/>
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
       <c r="R33" s="11"/>
@@ -6679,8 +6829,9 @@
       <c r="Z33" s="11"/>
       <c r="AA33" s="11"/>
       <c r="AB33" s="11"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC33" s="11"/>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A34" s="11" t="s">
         <v>402</v>
       </c>
@@ -6706,21 +6857,23 @@
         <v>-10000</v>
       </c>
       <c r="I34" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J34" s="11">
         <v>-50000</v>
       </c>
-      <c r="J34" s="11">
+      <c r="K34" s="11">
         <v>-100000</v>
       </c>
-      <c r="K34" s="11">
+      <c r="L34" s="11">
         <v>-200000</v>
       </c>
-      <c r="L34" s="11">
+      <c r="M34" s="11">
         <v>-500000</v>
       </c>
-      <c r="M34" s="11">
+      <c r="N34" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O34" s="11"/>
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
       <c r="R34" s="11"/>
@@ -6734,8 +6887,9 @@
       <c r="Z34" s="11"/>
       <c r="AA34" s="11"/>
       <c r="AB34" s="11"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC34" s="11"/>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A35" s="11" t="s">
         <v>403</v>
       </c>
@@ -6775,7 +6929,9 @@
       <c r="M35" s="11">
         <v>0</v>
       </c>
-      <c r="O35" s="11"/>
+      <c r="N35" s="11">
+        <v>0</v>
+      </c>
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
       <c r="R35" s="11"/>
@@ -6790,8 +6946,9 @@
       <c r="AA35" s="11"/>
       <c r="AB35" s="11"/>
       <c r="AC35" s="11"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD35" s="11"/>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A36" s="11" t="s">
         <v>403</v>
       </c>
@@ -6817,21 +6974,23 @@
         <v>-10000</v>
       </c>
       <c r="I36" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J36" s="11">
         <v>-50000</v>
       </c>
-      <c r="J36" s="11">
+      <c r="K36" s="11">
         <v>-100000</v>
       </c>
-      <c r="K36" s="11">
+      <c r="L36" s="11">
         <v>-200000</v>
       </c>
-      <c r="L36" s="11">
+      <c r="M36" s="11">
         <v>-500000</v>
       </c>
-      <c r="M36" s="11">
+      <c r="N36" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O36" s="11"/>
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
       <c r="R36" s="11"/>
@@ -6846,8 +7005,9 @@
       <c r="AA36" s="11"/>
       <c r="AB36" s="11"/>
       <c r="AC36" s="11"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD36" s="11"/>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A37" s="11" t="s">
         <v>403</v>
       </c>
@@ -6873,21 +7033,23 @@
         <v>-10000</v>
       </c>
       <c r="I37" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J37" s="11">
         <v>-50000</v>
       </c>
-      <c r="J37" s="11">
+      <c r="K37" s="11">
         <v>-100000</v>
       </c>
-      <c r="K37" s="11">
+      <c r="L37" s="11">
         <v>-200000</v>
       </c>
-      <c r="L37" s="11">
+      <c r="M37" s="11">
         <v>-500000</v>
       </c>
-      <c r="M37" s="11">
+      <c r="N37" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O37" s="11"/>
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
       <c r="R37" s="11"/>
@@ -6902,8 +7064,9 @@
       <c r="AA37" s="11"/>
       <c r="AB37" s="11"/>
       <c r="AC37" s="11"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AD37" s="11"/>
+    </row>
+    <row r="38" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A38" s="11" t="s">
         <v>404</v>
       </c>
@@ -6943,7 +7106,9 @@
       <c r="M38" s="11">
         <v>0</v>
       </c>
-      <c r="O38" s="11"/>
+      <c r="N38" s="11">
+        <v>0</v>
+      </c>
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
       <c r="R38" s="11"/>
@@ -6957,8 +7122,9 @@
       <c r="Z38" s="11"/>
       <c r="AA38" s="11"/>
       <c r="AB38" s="11"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC38" s="11"/>
+    </row>
+    <row r="39" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
         <v>404</v>
       </c>
@@ -6984,21 +7150,23 @@
         <v>-10000</v>
       </c>
       <c r="I39" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J39" s="11">
         <v>-50000</v>
       </c>
-      <c r="J39" s="11">
+      <c r="K39" s="11">
         <v>-100000</v>
       </c>
-      <c r="K39" s="11">
+      <c r="L39" s="11">
         <v>-200000</v>
       </c>
-      <c r="L39" s="11">
+      <c r="M39" s="11">
         <v>-500000</v>
       </c>
-      <c r="M39" s="11">
+      <c r="N39" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O39" s="11"/>
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
@@ -7012,8 +7180,9 @@
       <c r="Z39" s="11"/>
       <c r="AA39" s="11"/>
       <c r="AB39" s="11"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC39" s="11"/>
+    </row>
+    <row r="40" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
         <v>404</v>
       </c>
@@ -7039,21 +7208,23 @@
         <v>-10000</v>
       </c>
       <c r="I40" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J40" s="11">
         <v>-50000</v>
       </c>
-      <c r="J40" s="11">
+      <c r="K40" s="11">
         <v>-100000</v>
       </c>
-      <c r="K40" s="11">
+      <c r="L40" s="11">
         <v>-200000</v>
       </c>
-      <c r="L40" s="11">
+      <c r="M40" s="11">
         <v>-500000</v>
       </c>
-      <c r="M40" s="11">
+      <c r="N40" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O40" s="11"/>
       <c r="P40" s="11"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="11"/>
@@ -7067,8 +7238,9 @@
       <c r="Z40" s="11"/>
       <c r="AA40" s="11"/>
       <c r="AB40" s="11"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC40" s="11"/>
+    </row>
+    <row r="41" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A41" s="11" t="s">
         <v>405</v>
       </c>
@@ -7108,7 +7280,9 @@
       <c r="M41" s="11">
         <v>0</v>
       </c>
-      <c r="O41" s="11"/>
+      <c r="N41" s="11">
+        <v>0</v>
+      </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
       <c r="R41" s="11"/>
@@ -7122,8 +7296,9 @@
       <c r="Z41" s="11"/>
       <c r="AA41" s="11"/>
       <c r="AB41" s="11"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC41" s="11"/>
+    </row>
+    <row r="42" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A42" s="11" t="s">
         <v>405</v>
       </c>
@@ -7149,21 +7324,23 @@
         <v>-10000</v>
       </c>
       <c r="I42" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J42" s="11">
         <v>-50000</v>
       </c>
-      <c r="J42" s="11">
+      <c r="K42" s="11">
         <v>-100000</v>
       </c>
-      <c r="K42" s="11">
+      <c r="L42" s="11">
         <v>-200000</v>
       </c>
-      <c r="L42" s="11">
+      <c r="M42" s="11">
         <v>-500000</v>
       </c>
-      <c r="M42" s="11">
+      <c r="N42" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O42" s="11"/>
       <c r="P42" s="11"/>
       <c r="Q42" s="11"/>
       <c r="R42" s="11"/>
@@ -7177,8 +7354,9 @@
       <c r="Z42" s="11"/>
       <c r="AA42" s="11"/>
       <c r="AB42" s="11"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC42" s="11"/>
+    </row>
+    <row r="43" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A43" s="11" t="s">
         <v>405</v>
       </c>
@@ -7204,21 +7382,23 @@
         <v>-10000</v>
       </c>
       <c r="I43" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J43" s="11">
         <v>-50000</v>
       </c>
-      <c r="J43" s="11">
+      <c r="K43" s="11">
         <v>-100000</v>
       </c>
-      <c r="K43" s="11">
+      <c r="L43" s="11">
         <v>-200000</v>
       </c>
-      <c r="L43" s="11">
+      <c r="M43" s="11">
         <v>-500000</v>
       </c>
-      <c r="M43" s="11">
+      <c r="N43" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O43" s="11"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
       <c r="R43" s="11"/>
@@ -7232,8 +7412,9 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="11"/>
       <c r="AB43" s="11"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC43" s="11"/>
+    </row>
+    <row r="44" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A44" s="11" t="s">
         <v>406</v>
       </c>
@@ -7273,7 +7454,9 @@
       <c r="M44" s="11">
         <v>0</v>
       </c>
-      <c r="O44" s="11"/>
+      <c r="N44" s="11">
+        <v>0</v>
+      </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11"/>
@@ -7287,8 +7470,9 @@
       <c r="Z44" s="11"/>
       <c r="AA44" s="11"/>
       <c r="AB44" s="11"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC44" s="11"/>
+    </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A45" s="11" t="s">
         <v>406</v>
       </c>
@@ -7314,21 +7498,23 @@
         <v>-10000</v>
       </c>
       <c r="I45" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J45" s="11">
         <v>-50000</v>
       </c>
-      <c r="J45" s="11">
+      <c r="K45" s="11">
         <v>-100000</v>
       </c>
-      <c r="K45" s="11">
+      <c r="L45" s="11">
         <v>-200000</v>
       </c>
-      <c r="L45" s="11">
+      <c r="M45" s="11">
         <v>-500000</v>
       </c>
-      <c r="M45" s="11">
+      <c r="N45" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O45" s="11"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="11"/>
@@ -7342,8 +7528,9 @@
       <c r="Z45" s="11"/>
       <c r="AA45" s="11"/>
       <c r="AB45" s="11"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC45" s="11"/>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A46" s="11" t="s">
         <v>406</v>
       </c>
@@ -7369,21 +7556,23 @@
         <v>-10000</v>
       </c>
       <c r="I46" s="11">
+        <v>-30000</v>
+      </c>
+      <c r="J46" s="11">
         <v>-50000</v>
       </c>
-      <c r="J46" s="11">
+      <c r="K46" s="11">
         <v>-100000</v>
       </c>
-      <c r="K46" s="11">
+      <c r="L46" s="11">
         <v>-200000</v>
       </c>
-      <c r="L46" s="11">
+      <c r="M46" s="11">
         <v>-500000</v>
       </c>
-      <c r="M46" s="11">
+      <c r="N46" s="11">
         <v>-1000000</v>
       </c>
-      <c r="O46" s="11"/>
       <c r="P46" s="11"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11"/>
@@ -7397,42 +7586,43 @@
       <c r="Z46" s="11"/>
       <c r="AA46" s="11"/>
       <c r="AB46" s="11"/>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="AC46" s="11"/>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.45">
       <c r="E47" s="11"/>
       <c r="G47" s="11"/>
       <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="K47" s="11"/>
+      <c r="J47" s="11"/>
       <c r="L47" s="11"/>
       <c r="M47" s="11"/>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.45">
+      <c r="N47" s="11"/>
+    </row>
+    <row r="48" spans="1:30" x14ac:dyDescent="0.45">
       <c r="E48" s="11"/>
       <c r="G48" s="11"/>
       <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="K48" s="11"/>
+      <c r="J48" s="11"/>
       <c r="L48" s="11"/>
       <c r="M48" s="11"/>
-    </row>
-    <row r="49" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="N48" s="11"/>
+    </row>
+    <row r="49" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E49" s="11"/>
       <c r="G49" s="11"/>
       <c r="H49" s="11"/>
-      <c r="I49" s="11"/>
-      <c r="K49" s="11"/>
+      <c r="J49" s="11"/>
       <c r="L49" s="11"/>
       <c r="M49" s="11"/>
-    </row>
-    <row r="51" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="N49" s="11"/>
+    </row>
+    <row r="51" spans="5:14" x14ac:dyDescent="0.45">
       <c r="E51" s="11"/>
       <c r="G51" s="11"/>
       <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="K51" s="11"/>
+      <c r="J51" s="11"/>
       <c r="L51" s="11"/>
       <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -7462,7 +7652,7 @@
         <v>264</v>
       </c>
       <c r="B2" s="17">
-        <v>-5</v>
+        <v>-2.7777777777777781</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -7504,7 +7694,7 @@
         <v>265</v>
       </c>
       <c r="B3" s="17">
-        <v>-51</v>
+        <v>-28.333333333333332</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -7541,7 +7731,7 @@
         <v>266</v>
       </c>
       <c r="B4" s="17">
-        <v>-512</v>
+        <v>-284.44444444444446</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -7583,7 +7773,7 @@
         <v>267</v>
       </c>
       <c r="B5" s="17">
-        <v>-5114</v>
+        <v>-2841.1111111111113</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
@@ -7620,7 +7810,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="17">
-        <v>-50376</v>
+        <v>-27986.666666666668</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -7662,7 +7852,7 @@
         <v>268</v>
       </c>
       <c r="B7" s="17">
-        <v>-6</v>
+        <v>-3.3333333333333335</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -7704,7 +7894,7 @@
         <v>269</v>
       </c>
       <c r="B8" s="17">
-        <v>-53</v>
+        <v>-29.444444444444443</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -7741,7 +7931,7 @@
         <v>270</v>
       </c>
       <c r="B9" s="17">
-        <v>-514</v>
+        <v>-285.55555555555554</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -7783,7 +7973,7 @@
         <v>271</v>
       </c>
       <c r="B10" s="17">
-        <v>-5116</v>
+        <v>-2842.2222222222217</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -7820,7 +8010,7 @@
         <v>126</v>
       </c>
       <c r="B11" s="17">
-        <v>-50367</v>
+        <v>-27981.666666666668</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -7862,7 +8052,7 @@
         <v>272</v>
       </c>
       <c r="B12" s="17">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -7876,7 +8066,7 @@
         <v>273</v>
       </c>
       <c r="B13" s="17">
-        <v>-62</v>
+        <v>-34.444444444444443</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -7890,7 +8080,7 @@
         <v>274</v>
       </c>
       <c r="B14" s="17">
-        <v>-529</v>
+        <v>-293.88888888888886</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -7904,7 +8094,7 @@
         <v>275</v>
       </c>
       <c r="B15" s="17">
-        <v>-5132</v>
+        <v>-2851.1111111111113</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -7918,7 +8108,7 @@
         <v>276</v>
       </c>
       <c r="B16" s="17">
-        <v>-50257</v>
+        <v>-27920.555555555558</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -7932,7 +8122,7 @@
         <v>291</v>
       </c>
       <c r="B17" s="17">
-        <v>-16</v>
+        <v>-8.8888888888888893</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -7946,7 +8136,7 @@
         <v>292</v>
       </c>
       <c r="B18" s="17">
-        <v>-88</v>
+        <v>-48.888888888888886</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -7960,7 +8150,7 @@
         <v>293</v>
       </c>
       <c r="B19" s="17">
-        <v>-616</v>
+        <v>-342.22222222222229</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -7974,7 +8164,7 @@
         <v>294</v>
       </c>
       <c r="B20" s="17">
-        <v>-5283</v>
+        <v>-2935</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -7988,7 +8178,7 @@
         <v>295</v>
       </c>
       <c r="B21" s="17">
-        <v>-46061</v>
+        <v>-25589.444444444442</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -8002,7 +8192,7 @@
         <v>240</v>
       </c>
       <c r="B22" s="17">
-        <v>-41</v>
+        <v>-22.777777777777775</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -8016,7 +8206,7 @@
         <v>241</v>
       </c>
       <c r="B23" s="17">
-        <v>-156</v>
+        <v>-86.666666666666671</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -8030,7 +8220,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="17">
-        <v>-877</v>
+        <v>-487.22222222222229</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -8044,7 +8234,7 @@
         <v>243</v>
       </c>
       <c r="B25" s="17">
-        <v>-6156</v>
+        <v>-3420</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -8058,7 +8248,7 @@
         <v>244</v>
       </c>
       <c r="B26" s="17">
-        <v>-47658</v>
+        <v>-26476.666666666668</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -8072,7 +8262,7 @@
         <v>296</v>
       </c>
       <c r="B27" s="17">
-        <v>-179</v>
+        <v>-99.444444444444429</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -8086,7 +8276,7 @@
         <v>297</v>
       </c>
       <c r="B28" s="17">
-        <v>-413</v>
+        <v>-229.44444444444446</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -8100,7 +8290,7 @@
         <v>298</v>
       </c>
       <c r="B29" s="17">
-        <v>-1562</v>
+        <v>-867.77777777777783</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -8114,7 +8304,7 @@
         <v>299</v>
       </c>
       <c r="B30" s="17">
-        <v>-8763</v>
+        <v>-4868.333333333333</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -8128,7 +8318,7 @@
         <v>300</v>
       </c>
       <c r="B31" s="17">
-        <v>-60612</v>
+        <v>-33673.333333333336</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
@@ -8142,7 +8332,7 @@
         <v>245</v>
       </c>
       <c r="B32" s="17">
-        <v>-631</v>
+        <v>-350.5555555555556</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -8156,7 +8346,7 @@
         <v>246</v>
       </c>
       <c r="B33" s="17">
-        <v>-1733</v>
+        <v>-962.77777777777783</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -8170,7 +8360,7 @@
         <v>247</v>
       </c>
       <c r="B34" s="17">
-        <v>-4045</v>
+        <v>-2247.2222222222222</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -8184,7 +8374,7 @@
         <v>248</v>
       </c>
       <c r="B35" s="17">
-        <v>-15449</v>
+        <v>-8582.7777777777774</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -8198,7 +8388,7 @@
         <v>249</v>
       </c>
       <c r="B36" s="17">
-        <v>-86973</v>
+        <v>-48318.333333333336</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>

--- a/setup.xlsx
+++ b/setup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmarinriver\Projects\ConfinedLab\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B641C5A-12B4-4CA8-9971-CE19F5130DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F928BB2A-1145-4D23-9B85-DDBC27CD0ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grid" sheetId="1" r:id="rId1"/>
@@ -7652,7 +7652,7 @@
         <v>264</v>
       </c>
       <c r="B2" s="17">
-        <v>-2.7777777777777781</v>
+        <v>-3</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -7694,7 +7694,7 @@
         <v>265</v>
       </c>
       <c r="B3" s="17">
-        <v>-28.333333333333332</v>
+        <v>-28</v>
       </c>
       <c r="C3" s="17"/>
       <c r="D3" s="17"/>
@@ -7731,7 +7731,7 @@
         <v>266</v>
       </c>
       <c r="B4" s="17">
-        <v>-284.44444444444446</v>
+        <v>-284</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17"/>
@@ -7773,7 +7773,7 @@
         <v>267</v>
       </c>
       <c r="B5" s="17">
-        <v>-2841.1111111111113</v>
+        <v>-2841</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
@@ -7810,7 +7810,7 @@
         <v>125</v>
       </c>
       <c r="B6" s="17">
-        <v>-27986.666666666668</v>
+        <v>-27987</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -7852,7 +7852,7 @@
         <v>268</v>
       </c>
       <c r="B7" s="17">
-        <v>-3.3333333333333335</v>
+        <v>-3</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -7894,7 +7894,7 @@
         <v>269</v>
       </c>
       <c r="B8" s="17">
-        <v>-29.444444444444443</v>
+        <v>-29</v>
       </c>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -7931,7 +7931,7 @@
         <v>270</v>
       </c>
       <c r="B9" s="17">
-        <v>-285.55555555555554</v>
+        <v>-286</v>
       </c>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -7973,7 +7973,7 @@
         <v>271</v>
       </c>
       <c r="B10" s="17">
-        <v>-2842.2222222222217</v>
+        <v>-2842</v>
       </c>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -8010,7 +8010,7 @@
         <v>126</v>
       </c>
       <c r="B11" s="17">
-        <v>-27981.666666666668</v>
+        <v>-27982</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -8066,7 +8066,7 @@
         <v>273</v>
       </c>
       <c r="B13" s="17">
-        <v>-34.444444444444443</v>
+        <v>-34</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -8080,7 +8080,7 @@
         <v>274</v>
       </c>
       <c r="B14" s="17">
-        <v>-293.88888888888886</v>
+        <v>-294</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -8094,7 +8094,7 @@
         <v>275</v>
       </c>
       <c r="B15" s="17">
-        <v>-2851.1111111111113</v>
+        <v>-2851</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -8108,7 +8108,7 @@
         <v>276</v>
       </c>
       <c r="B16" s="17">
-        <v>-27920.555555555558</v>
+        <v>-27921</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -8122,7 +8122,7 @@
         <v>291</v>
       </c>
       <c r="B17" s="17">
-        <v>-8.8888888888888893</v>
+        <v>-9</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -8136,7 +8136,7 @@
         <v>292</v>
       </c>
       <c r="B18" s="17">
-        <v>-48.888888888888886</v>
+        <v>-49</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -8150,7 +8150,7 @@
         <v>293</v>
       </c>
       <c r="B19" s="17">
-        <v>-342.22222222222229</v>
+        <v>-342</v>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -8178,7 +8178,7 @@
         <v>295</v>
       </c>
       <c r="B21" s="17">
-        <v>-25589.444444444442</v>
+        <v>-25589</v>
       </c>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -8192,7 +8192,7 @@
         <v>240</v>
       </c>
       <c r="B22" s="17">
-        <v>-22.777777777777775</v>
+        <v>-23</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -8206,7 +8206,7 @@
         <v>241</v>
       </c>
       <c r="B23" s="17">
-        <v>-86.666666666666671</v>
+        <v>-87</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -8220,7 +8220,7 @@
         <v>242</v>
       </c>
       <c r="B24" s="17">
-        <v>-487.22222222222229</v>
+        <v>-487</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -8248,7 +8248,7 @@
         <v>244</v>
       </c>
       <c r="B26" s="17">
-        <v>-26476.666666666668</v>
+        <v>-26477</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -8262,7 +8262,7 @@
         <v>296</v>
       </c>
       <c r="B27" s="17">
-        <v>-99.444444444444429</v>
+        <v>-99</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -8276,7 +8276,7 @@
         <v>297</v>
       </c>
       <c r="B28" s="17">
-        <v>-229.44444444444446</v>
+        <v>-229</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -8290,7 +8290,7 @@
         <v>298</v>
       </c>
       <c r="B29" s="17">
-        <v>-867.77777777777783</v>
+        <v>-868</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -8304,7 +8304,7 @@
         <v>299</v>
       </c>
       <c r="B30" s="17">
-        <v>-4868.333333333333</v>
+        <v>-4868</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -8318,7 +8318,7 @@
         <v>300</v>
       </c>
       <c r="B31" s="17">
-        <v>-33673.333333333336</v>
+        <v>-33673</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
@@ -8332,7 +8332,7 @@
         <v>245</v>
       </c>
       <c r="B32" s="17">
-        <v>-350.5555555555556</v>
+        <v>-351</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -8346,7 +8346,7 @@
         <v>246</v>
       </c>
       <c r="B33" s="17">
-        <v>-962.77777777777783</v>
+        <v>-963</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -8360,7 +8360,7 @@
         <v>247</v>
       </c>
       <c r="B34" s="17">
-        <v>-2247.2222222222222</v>
+        <v>-2247</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -8374,7 +8374,7 @@
         <v>248</v>
       </c>
       <c r="B35" s="17">
-        <v>-8582.7777777777774</v>
+        <v>-8583</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -8388,7 +8388,7 @@
         <v>249</v>
       </c>
       <c r="B36" s="17">
-        <v>-48318.333333333336</v>
+        <v>-48318</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
